--- a/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
@@ -5,18 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Sistema_Indicadores_Poli/data/raw/Plan de mejoramiento/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Plan de mejoramiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B6C3FBF-9B6A-4DC0-9F8B-BFCEC1DB2874}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5377319B-A2AF-4812-861F-3809BA79B2CB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD3A294A-1D13-4C18-8C58-F237245A6723}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores Plan de Mejor" sheetId="1" r:id="rId1"/>
+    <sheet name="Indicadores Real" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Indicadores Plan de Mejor'!$A$2:$W$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Indicadores Plan de Mejor'!$A$2:$S$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Indicadores Real'!$A$2:$S$68</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,14 +48,13 @@
   <authors>
     <author>tc={4BC1B9A5-27B6-4248-B1C1-C79208ED2EFC}</author>
     <author>tc={029006E9-4008-49E2-BAEE-4CC12F0054C4}</author>
-    <author>tc={B12753C2-722D-4114-B28C-A6F443B4ECEC}</author>
-    <author>tc={EF5E0CBC-6175-4664-A6AF-3994CA9A1DF3}</author>
+    <author>tc={76CD3EFC-5330-4BD0-A48D-F1E64F16B9AC}</author>
   </authors>
   <commentList>
-    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{4BC1B9A5-27B6-4248-B1C1-C79208ED2EFC}">
+    <comment ref="N7" authorId="0" shapeId="0" xr:uid="{4BC1B9A5-27B6-4248-B1C1-C79208ED2EFC}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Focus Group
 Estudiantes: 15
@@ -69,20 +70,72 @@
 Graduados: 150</t>
       </text>
     </comment>
-    <comment ref="Q13" authorId="1" shapeId="0" xr:uid="{029006E9-4008-49E2-BAEE-4CC12F0054C4}">
+    <comment ref="O12" authorId="1" shapeId="0" xr:uid="{029006E9-4008-49E2-BAEE-4CC12F0054C4}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Colaboradores: 63%
 Estudiantes: 18%
 Graduados:22%</t>
       </text>
     </comment>
-    <comment ref="R48" authorId="2" shapeId="0" xr:uid="{B12753C2-722D-4114-B28C-A6F443B4ECEC}">
+    <comment ref="O13" authorId="2" shapeId="0" xr:uid="{76CD3EFC-5330-4BD0-A48D-F1E64F16B9AC}">
+      <text>
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Colaboradores: 2% 
+Estudiantes: 3% 
+Graduados: 2%</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={FA05611A-1D16-4452-B93C-2E4DFFD86645}</author>
+    <author>tc={3F85CAB4-6021-44EC-B795-E932C183C912}</author>
+    <author>tc={242351BE-3094-4A32-A1BB-45F00F8A6CDF}</author>
+    <author>tc={89AA3457-36D7-4CDB-AC41-C208171F6214}</author>
+  </authors>
+  <commentList>
+    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{FA05611A-1D16-4452-B93C-2E4DFFD86645}">
+      <text>
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Focus Group
+Estudiantes: 15
+Profesores: 15
+Graduados: 15
+Empresarios: 15
+Administrativos: 15
+Proveedores: 15
+Encuestas
+Estudiantes: 1.500
+Profesores: 300
+Colaboradores: 300
+Graduados: 150</t>
+      </text>
+    </comment>
+    <comment ref="Q13" authorId="1" shapeId="0" xr:uid="{3F85CAB4-6021-44EC-B795-E932C183C912}">
+      <text>
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Colaboradores: 63%
+Estudiantes: 18%
+Graduados:22%</t>
+      </text>
+    </comment>
+    <comment ref="R48" authorId="2" shapeId="0" xr:uid="{242351BE-3094-4A32-A1BB-45F00F8A6CDF}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Nivel de satisfacción Estudiante Presencial: 100%
 Nivel de satisfacción Estudiante Virtual: 100%
@@ -91,10 +144,10 @@
 Nivel de satisfacción Externo: 100% </t>
       </text>
     </comment>
-    <comment ref="R49" authorId="3" shapeId="0" xr:uid="{EF5E0CBC-6175-4664-A6AF-3994CA9A1DF3}">
+    <comment ref="R49" authorId="3" shapeId="0" xr:uid="{89AA3457-36D7-4CDB-AC41-C208171F6214}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Nivel de satisfacción Estudiante presencial: 98,1%
 Nivel de satisfacción Estudiante Virtual: 95,4%
@@ -109,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="302">
   <si>
     <t>Metas Preliminares</t>
   </si>
@@ -1118,6 +1171,117 @@
   <si>
     <t>N de convenios con actividades en los ultimos 5 años / Total convenios</t>
   </si>
+  <si>
+    <t>% inversion misionales de la institución</t>
+  </si>
+  <si>
+    <t>Efectividad de las acciones derivadas de las oportunidades de mejora</t>
+  </si>
+  <si>
+    <t>(Acciones cerradas calificadas como efectivas ÷ Total de acciones cerradas y evaluadas) × 100</t>
+  </si>
+  <si>
+    <t>Director de control interno</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Por definir- Pendiente Implementación de instrumentos
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Inter"/>
+        <family val="2"/>
+      </rPr>
+      <t>Modelo de gestión, evaluación e innovación curricular</t>
+    </r>
+  </si>
+  <si>
+    <t>Número de programas con reforma curricular</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sesion para identificar medición con Maria Isabel y Maria del Socorro
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Inter"/>
+        <family val="2"/>
+      </rPr>
+      <t>se valida con Diana y los indicadores se asociaran al aspecto de mejora definido por el CNA en cuanto a la constitución del Modelo de evaluación del aprendizaje en la institución</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF002060"/>
+        <rFont val="Inter"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Inter"/>
+        <family val="2"/>
+      </rPr>
+      <t>28 septiembre</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sesion con Diana
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Inter"/>
+        <family val="2"/>
+      </rPr>
+      <t>se propone indicador asociado con la apropiación del modelo de gestión, evaluación e innovación curricular</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF002060"/>
+        <rFont val="Inter"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Inter"/>
+        <family val="2"/>
+      </rPr>
+      <t>28 septiembre</t>
+    </r>
+  </si>
+  <si>
+    <t>Dirección de curriculo</t>
+  </si>
+  <si>
+    <t>Valor agregado en la pruebas Saber Pro Institucional</t>
+  </si>
 </sst>
 </file>
 
@@ -1128,7 +1292,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1290,8 +1454,21 @@
       <name val="Inter"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Inter"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1406,6 +1583,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -1923,6 +2106,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="11" fillId="12" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1935,17 +2127,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="12" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1971,6 +2154,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Ximena Silva" id="{4069C3FC-DE77-490E-9BCA-D060BF504FA7}" userId="5f15395a9ed9a48f" providerId="Windows Live"/>
   <person displayName="Licec Ximena Silva Goyeneche" id="{41F01098-9674-497B-897D-AE27DFF4DD0D}" userId="S::lxisilva@poligran.edu.co::8288b16f-baeb-48ea-b2e7-c5e2177103dc" providerId="AD"/>
 </personList>
 </file>
@@ -2292,7 +2476,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="N8" dT="2026-09-08T19:52:01.45" personId="{41F01098-9674-497B-897D-AE27DFF4DD0D}" id="{4BC1B9A5-27B6-4248-B1C1-C79208ED2EFC}">
+  <threadedComment ref="N7" dT="2026-09-08T19:52:01.45" personId="{41F01098-9674-497B-897D-AE27DFF4DD0D}" id="{4BC1B9A5-27B6-4248-B1C1-C79208ED2EFC}">
     <text>Focus Group
 Estudiantes: 15
 Profesores: 15
@@ -2306,19 +2490,48 @@
 Colaboradores: 300
 Graduados: 150</text>
   </threadedComment>
-  <threadedComment ref="Q13" dT="2026-09-08T20:19:19.94" personId="{41F01098-9674-497B-897D-AE27DFF4DD0D}" id="{029006E9-4008-49E2-BAEE-4CC12F0054C4}">
+  <threadedComment ref="O12" dT="2026-09-08T20:19:19.94" personId="{41F01098-9674-497B-897D-AE27DFF4DD0D}" id="{029006E9-4008-49E2-BAEE-4CC12F0054C4}">
     <text>Colaboradores: 63%
 Estudiantes: 18%
 Graduados:22%</text>
   </threadedComment>
-  <threadedComment ref="R48" dT="2026-09-08T20:34:02.79" personId="{41F01098-9674-497B-897D-AE27DFF4DD0D}" id="{B12753C2-722D-4114-B28C-A6F443B4ECEC}">
+  <threadedComment ref="O13" dT="2026-09-18T13:35:03.40" personId="{4069C3FC-DE77-490E-9BCA-D060BF504FA7}" id="{76CD3EFC-5330-4BD0-A48D-F1E64F16B9AC}">
+    <text>Colaboradores: 2% 
+Estudiantes: 3% 
+Graduados: 2%</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="N8" dT="2026-09-08T19:52:01.45" personId="{41F01098-9674-497B-897D-AE27DFF4DD0D}" id="{FA05611A-1D16-4452-B93C-2E4DFFD86645}">
+    <text>Focus Group
+Estudiantes: 15
+Profesores: 15
+Graduados: 15
+Empresarios: 15
+Administrativos: 15
+Proveedores: 15
+Encuestas
+Estudiantes: 1.500
+Profesores: 300
+Colaboradores: 300
+Graduados: 150</text>
+  </threadedComment>
+  <threadedComment ref="Q13" dT="2026-09-08T20:19:19.94" personId="{41F01098-9674-497B-897D-AE27DFF4DD0D}" id="{3F85CAB4-6021-44EC-B795-E932C183C912}">
+    <text>Colaboradores: 63%
+Estudiantes: 18%
+Graduados:22%</text>
+  </threadedComment>
+  <threadedComment ref="R48" dT="2026-09-08T20:34:02.79" personId="{41F01098-9674-497B-897D-AE27DFF4DD0D}" id="{242351BE-3094-4A32-A1BB-45F00F8A6CDF}">
     <text xml:space="preserve">Nivel de satisfacción Estudiante Presencial: 100%
 Nivel de satisfacción Estudiante Virtual: 100%
 Nivel de satisfacción Profesor: 100%
 Nivel de satisfacción Administrativo: 100%
 Nivel de satisfacción Externo: 100% </text>
   </threadedComment>
-  <threadedComment ref="R49" dT="2026-09-08T20:47:16.92" personId="{41F01098-9674-497B-897D-AE27DFF4DD0D}" id="{EF5E0CBC-6175-4664-A6AF-3994CA9A1DF3}">
+  <threadedComment ref="R49" dT="2026-09-08T20:47:16.92" personId="{41F01098-9674-497B-897D-AE27DFF4DD0D}" id="{89AA3457-36D7-4CDB-AC41-C208171F6214}">
     <text xml:space="preserve">Nivel de satisfacción Estudiante presencial: 98,1%
 Nivel de satisfacción Estudiante Virtual: 95,4%
 Nivel de satisfacción Profesor: 100%
@@ -2334,8 +2547,8 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:W68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S66"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.5546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="30.88671875" style="2" customWidth="1"/>
@@ -2346,12 +2559,11 @@
     <col min="12" max="12" width="22.33203125" style="2" customWidth="1"/>
     <col min="13" max="13" width="27.21875" style="2" customWidth="1"/>
     <col min="14" max="14" width="13.77734375" style="2" customWidth="1"/>
-    <col min="15" max="16" width="11.5546875" style="2" customWidth="1"/>
-    <col min="17" max="23" width="16.5546875" style="2" customWidth="1"/>
-    <col min="24" max="16384" width="11.5546875" style="2"/>
+    <col min="15" max="19" width="16.5546875" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="46.2" customHeight="1">
+    <row r="1" spans="1:19" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2365,20 +2577,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="139" t="s">
+      <c r="N1" s="142" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="140"/>
-      <c r="W1" s="140"/>
-    </row>
-    <row r="2" spans="1:23" ht="36">
+      <c r="O1" s="143"/>
+      <c r="P1" s="143"/>
+      <c r="Q1" s="143"/>
+      <c r="R1" s="143"/>
+      <c r="S1" s="143"/>
+    </row>
+    <row r="2" spans="1:19" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2421,35 +2629,23 @@
       <c r="N2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" s="11" t="s">
+      <c r="O2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="T2" s="13">
+      <c r="P2" s="13">
         <v>2027</v>
       </c>
-      <c r="U2" s="13">
+      <c r="Q2" s="13">
         <v>2028</v>
       </c>
-      <c r="V2" s="13">
+      <c r="R2" s="13">
         <v>2029</v>
       </c>
-      <c r="W2" s="13">
+      <c r="S2" s="13">
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="75">
+    <row r="3" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>20</v>
       </c>
@@ -2488,6 +2684,3269 @@
       <c r="N3" s="21">
         <v>0.95</v>
       </c>
+      <c r="O3" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="21">
+        <v>0.95</v>
+      </c>
+      <c r="Q3" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="21">
+        <v>0.95</v>
+      </c>
+      <c r="S3" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="18"/>
+      <c r="K4" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="15"/>
+      <c r="N4" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" s="24">
+        <v>0.93</v>
+      </c>
+      <c r="P4" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="21">
+        <v>0.94</v>
+      </c>
+      <c r="R4" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S4" s="21">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+    </row>
+    <row r="6" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+    </row>
+    <row r="7" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="36">
+        <v>527</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="38"/>
+      <c r="H7" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="L7" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="34"/>
+      <c r="N7" s="40">
+        <v>3690</v>
+      </c>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+    </row>
+    <row r="8" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="36"/>
+      <c r="F8" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="38"/>
+      <c r="H8" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="O8" s="40"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="40"/>
+      <c r="S8" s="40"/>
+    </row>
+    <row r="9" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+      <c r="A9" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="36">
+        <v>528</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" s="39"/>
+      <c r="L9" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="N9" s="49">
+        <v>1158</v>
+      </c>
+      <c r="O9" s="51">
+        <v>1200</v>
+      </c>
+      <c r="P9" s="40">
+        <v>1212</v>
+      </c>
+      <c r="Q9" s="40">
+        <v>1224</v>
+      </c>
+      <c r="R9" s="40">
+        <v>1234</v>
+      </c>
+      <c r="S9" s="40">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="36"/>
+      <c r="F10" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="K10" s="39"/>
+      <c r="L10" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" s="52">
+        <v>0.85</v>
+      </c>
+      <c r="O10" s="55">
+        <v>0.9</v>
+      </c>
+      <c r="P10" s="55">
+        <v>0.9</v>
+      </c>
+      <c r="Q10" s="55">
+        <v>0.95</v>
+      </c>
+      <c r="R10" s="55">
+        <v>0.95</v>
+      </c>
+      <c r="S10" s="55">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+      <c r="A11" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="36"/>
+      <c r="F11" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="L11" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="N11" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="O11" s="40"/>
+      <c r="P11" s="40"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="40"/>
+      <c r="S11" s="40"/>
+    </row>
+    <row r="12" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="60" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="61">
+        <v>456</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="60" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="63"/>
+      <c r="K12" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="L12" s="144" t="s">
+        <v>82</v>
+      </c>
+      <c r="M12" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="N12" s="64">
+        <v>1</v>
+      </c>
+      <c r="O12" s="64">
+        <v>1</v>
+      </c>
+      <c r="P12" s="64">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="64">
+        <v>1</v>
+      </c>
+      <c r="R12" s="64">
+        <v>1</v>
+      </c>
+      <c r="S12" s="64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="57" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="61">
+        <v>457</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="60" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" s="67"/>
+      <c r="K13" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="L13" s="145"/>
+      <c r="M13" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" s="64">
+        <v>1</v>
+      </c>
+      <c r="O13" s="64">
+        <v>1</v>
+      </c>
+      <c r="P13" s="64">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="64">
+        <v>1</v>
+      </c>
+      <c r="R13" s="64">
+        <v>1</v>
+      </c>
+      <c r="S13" s="64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="57" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="61">
+        <v>524</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="60" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="67"/>
+      <c r="K14" s="68" t="s">
+        <v>86</v>
+      </c>
+      <c r="L14" s="68" t="s">
+        <v>86</v>
+      </c>
+      <c r="M14" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="N14" s="64">
+        <v>1</v>
+      </c>
+      <c r="O14" s="64">
+        <v>1</v>
+      </c>
+      <c r="P14" s="64">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="64">
+        <v>1</v>
+      </c>
+      <c r="R14" s="64">
+        <v>1</v>
+      </c>
+      <c r="S14" s="64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="70" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="70" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="72" t="s">
+        <v>89</v>
+      </c>
+      <c r="E15" s="61">
+        <v>626</v>
+      </c>
+      <c r="F15" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="72" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="M15" s="71" t="s">
+        <v>43</v>
+      </c>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+    </row>
+    <row r="16" spans="1:19" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="70" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="74" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="61">
+        <v>109</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="66"/>
+      <c r="K16" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="L16" s="19"/>
+      <c r="M16" s="75"/>
+      <c r="N16" s="64">
+        <v>0.8</v>
+      </c>
+      <c r="O16" s="21">
+        <v>0.85</v>
+      </c>
+      <c r="P16" s="21">
+        <v>0.85</v>
+      </c>
+      <c r="Q16" s="21">
+        <v>0.87</v>
+      </c>
+      <c r="R16" s="21">
+        <v>0.87</v>
+      </c>
+      <c r="S16" s="21">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="77" t="s">
+        <v>292</v>
+      </c>
+      <c r="E17" s="61"/>
+      <c r="F17" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="72"/>
+      <c r="H17" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I17" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="75" t="s">
+        <v>55</v>
+      </c>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="19"/>
+    </row>
+    <row r="18" spans="1:19" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="78" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" s="61"/>
+      <c r="F18" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="60" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I18" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="J18" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="K18" s="28"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="75" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+    </row>
+    <row r="19" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="80" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" s="17"/>
+      <c r="F19" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="H19" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I19" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" s="66" t="s">
+        <v>105</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="M19" s="34"/>
+      <c r="N19" s="64">
+        <v>0.95</v>
+      </c>
+      <c r="O19" s="64">
+        <v>0.95</v>
+      </c>
+      <c r="P19" s="64">
+        <v>0.95</v>
+      </c>
+      <c r="Q19" s="64">
+        <v>0.95</v>
+      </c>
+      <c r="R19" s="64">
+        <v>0.95</v>
+      </c>
+      <c r="S19" s="64">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+      <c r="A20" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="79" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="80" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="E20" s="17"/>
+      <c r="F20" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="H20" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I20" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="66" t="s">
+        <v>294</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="21">
+        <v>1</v>
+      </c>
+      <c r="P20" s="21">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="21">
+        <v>1</v>
+      </c>
+      <c r="R20" s="21">
+        <v>1</v>
+      </c>
+      <c r="S20" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+      <c r="A21" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="79" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="81" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="82" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="83" t="s">
+        <v>117</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="84" t="s">
+        <v>75</v>
+      </c>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="19"/>
+    </row>
+    <row r="22" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="79" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="80" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" s="85" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" s="85">
+        <v>339</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="85" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22" s="85" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="M22" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="N22" s="21">
+        <v>0.33</v>
+      </c>
+      <c r="O22" s="86">
+        <v>0.44</v>
+      </c>
+      <c r="P22" s="86">
+        <v>0.45</v>
+      </c>
+      <c r="Q22" s="86">
+        <v>0.5</v>
+      </c>
+      <c r="R22" s="86">
+        <v>0.53</v>
+      </c>
+      <c r="S22" s="86">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="80" t="s">
+        <v>126</v>
+      </c>
+      <c r="C23" s="80" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="85" t="s">
+        <v>128</v>
+      </c>
+      <c r="E23" s="88">
+        <v>334</v>
+      </c>
+      <c r="F23" s="89" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" s="89" t="s">
+        <v>129</v>
+      </c>
+      <c r="H23" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="I23" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="K23" s="18"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="N23" s="90">
+        <v>0.89</v>
+      </c>
+      <c r="O23" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
+    </row>
+    <row r="24" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="80" t="s">
+        <v>126</v>
+      </c>
+      <c r="C24" s="80" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="88" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="88">
+        <v>283</v>
+      </c>
+      <c r="F24" s="89" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="89" t="s">
+        <v>129</v>
+      </c>
+      <c r="H24" s="88" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="K24" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="M24" s="34"/>
+      <c r="N24" s="19">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O24" s="19">
+        <v>4.66</v>
+      </c>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="19"/>
+    </row>
+    <row r="25" spans="1:19" ht="218.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="79" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" s="79" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="113" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" s="146" t="s">
+        <v>296</v>
+      </c>
+      <c r="E25" s="17"/>
+      <c r="F25" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="H25" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I25" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="J25" s="63"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="M25" s="94"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+    </row>
+    <row r="26" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="79" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26" s="79" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" s="80" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="146" t="s">
+        <v>297</v>
+      </c>
+      <c r="E26" s="17"/>
+      <c r="F26" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="H26" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="J26" s="63"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="M26" s="94"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+    </row>
+    <row r="27" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="79" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" s="79" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="80" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="E27" s="17"/>
+      <c r="F27" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="82" t="s">
+        <v>143</v>
+      </c>
+      <c r="H27" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I27" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="J27" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="K27" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="L27" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="M27" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="N27" s="66"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+    </row>
+    <row r="28" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+      <c r="A28" s="79" t="s">
+        <v>135</v>
+      </c>
+      <c r="B28" s="79" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" s="80" t="s">
+        <v>148</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28" s="17"/>
+      <c r="F28" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="G28" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="H28" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I28" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="J28" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="K28" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="L28" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="M28" s="34"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19">
+        <v>23</v>
+      </c>
+      <c r="P28" s="19">
+        <v>28</v>
+      </c>
+      <c r="Q28" s="19">
+        <v>22</v>
+      </c>
+      <c r="R28" s="97">
+        <v>27</v>
+      </c>
+      <c r="S28" s="97">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="79" t="s">
+        <v>135</v>
+      </c>
+      <c r="B29" s="98" t="s">
+        <v>152</v>
+      </c>
+      <c r="C29" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="E29" s="17">
+        <v>325</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="I29" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="M29" s="34"/>
+      <c r="N29" s="19">
+        <v>12</v>
+      </c>
+      <c r="O29" s="19">
+        <v>7</v>
+      </c>
+      <c r="P29" s="19">
+        <v>11</v>
+      </c>
+      <c r="Q29" s="19">
+        <v>7</v>
+      </c>
+      <c r="R29" s="19">
+        <v>7</v>
+      </c>
+      <c r="S29" s="19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="79" t="s">
+        <v>135</v>
+      </c>
+      <c r="B30" s="98" t="s">
+        <v>152</v>
+      </c>
+      <c r="C30" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" s="17">
+        <v>323</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="I30" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="L30" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="M30" s="34"/>
+      <c r="N30" s="99">
+        <v>7</v>
+      </c>
+      <c r="O30" s="99">
+        <v>14</v>
+      </c>
+      <c r="P30" s="99">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="99">
+        <v>29</v>
+      </c>
+      <c r="R30" s="99">
+        <v>20</v>
+      </c>
+      <c r="S30" s="99">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+      <c r="A31" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="B31" s="48" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" s="100" t="s">
+        <v>158</v>
+      </c>
+      <c r="D31" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="E31" s="36">
+        <v>148</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="H31" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="I31" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="J31" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="K31" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="L31" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="M31" s="101" t="s">
+        <v>43</v>
+      </c>
+      <c r="N31" s="102">
+        <v>0.05</v>
+      </c>
+      <c r="O31" s="55">
+        <v>0.08</v>
+      </c>
+      <c r="P31" s="55">
+        <v>0.1</v>
+      </c>
+      <c r="Q31" s="55">
+        <v>0.12</v>
+      </c>
+      <c r="R31" s="55">
+        <v>0.13</v>
+      </c>
+      <c r="S31" s="55">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="B32" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" s="100" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="103" t="s">
+        <v>164</v>
+      </c>
+      <c r="E32" s="41"/>
+      <c r="F32" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="104" t="s">
+        <v>68</v>
+      </c>
+      <c r="H32" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I32" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="J32" s="42"/>
+      <c r="K32" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="L32" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="M32" s="101"/>
+      <c r="N32" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="O32" s="55">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P32" s="55">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="Q32" s="55">
+        <v>0.76</v>
+      </c>
+      <c r="R32" s="55">
+        <v>0.76</v>
+      </c>
+      <c r="S32" s="55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="B33" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="C33" s="100" t="s">
+        <v>158</v>
+      </c>
+      <c r="D33" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="E33" s="36"/>
+      <c r="F33" s="105" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" s="106" t="s">
+        <v>165</v>
+      </c>
+      <c r="H33" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I33" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="J33" s="39"/>
+      <c r="K33" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="L33" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="M33" s="101" t="s">
+        <v>166</v>
+      </c>
+      <c r="N33" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="O33" s="40">
+        <v>116</v>
+      </c>
+      <c r="P33" s="40">
+        <v>110</v>
+      </c>
+      <c r="Q33" s="40">
+        <v>110</v>
+      </c>
+      <c r="R33" s="40">
+        <v>115</v>
+      </c>
+      <c r="S33" s="40">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="B34" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="C34" s="100" t="s">
+        <v>158</v>
+      </c>
+      <c r="D34" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="E34" s="36"/>
+      <c r="F34" s="105" t="s">
+        <v>24</v>
+      </c>
+      <c r="G34" s="106" t="s">
+        <v>168</v>
+      </c>
+      <c r="H34" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I34" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="J34" s="39"/>
+      <c r="K34" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="L34" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="M34" s="101"/>
+      <c r="N34" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="O34" s="108">
+        <v>34</v>
+      </c>
+      <c r="P34" s="108">
+        <v>68</v>
+      </c>
+      <c r="Q34" s="108">
+        <v>102</v>
+      </c>
+      <c r="R34" s="108">
+        <v>136</v>
+      </c>
+      <c r="S34" s="108">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="C35" s="100" t="s">
+        <v>158</v>
+      </c>
+      <c r="D35" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="E35" s="41"/>
+      <c r="F35" s="105" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" s="104" t="s">
+        <v>68</v>
+      </c>
+      <c r="H35" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I35" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="J35" s="42"/>
+      <c r="K35" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="L35" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="M35" s="101" t="s">
+        <v>166</v>
+      </c>
+      <c r="N35" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="O35" s="55">
+        <v>0.44</v>
+      </c>
+      <c r="P35" s="55">
+        <v>0.44</v>
+      </c>
+      <c r="Q35" s="55">
+        <v>0.65</v>
+      </c>
+      <c r="R35" s="55">
+        <v>0.65</v>
+      </c>
+      <c r="S35" s="55">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="80" t="s">
+        <v>170</v>
+      </c>
+      <c r="B36" s="98" t="s">
+        <v>171</v>
+      </c>
+      <c r="C36" s="113" t="s">
+        <v>172</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36" s="17"/>
+      <c r="F36" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="G36" s="82" t="s">
+        <v>174</v>
+      </c>
+      <c r="H36" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I36" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J36" s="114" t="s">
+        <v>175</v>
+      </c>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="34"/>
+      <c r="N36" s="66"/>
+      <c r="O36" s="19"/>
+      <c r="P36" s="19"/>
+      <c r="Q36" s="19"/>
+      <c r="R36" s="19"/>
+      <c r="S36" s="19"/>
+    </row>
+    <row r="37" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="80" t="s">
+        <v>170</v>
+      </c>
+      <c r="B37" s="98" t="s">
+        <v>171</v>
+      </c>
+      <c r="C37" s="80" t="s">
+        <v>176</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="E37" s="17"/>
+      <c r="F37" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="G37" s="82" t="s">
+        <v>178</v>
+      </c>
+      <c r="H37" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I37" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J37" s="66" t="s">
+        <v>179</v>
+      </c>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="34"/>
+      <c r="N37" s="66"/>
+      <c r="O37" s="19"/>
+      <c r="P37" s="19"/>
+      <c r="Q37" s="19"/>
+      <c r="R37" s="19"/>
+      <c r="S37" s="19"/>
+    </row>
+    <row r="38" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="80" t="s">
+        <v>170</v>
+      </c>
+      <c r="B38" s="98" t="s">
+        <v>171</v>
+      </c>
+      <c r="C38" s="80" t="s">
+        <v>176</v>
+      </c>
+      <c r="D38" s="115" t="s">
+        <v>180</v>
+      </c>
+      <c r="E38" s="116"/>
+      <c r="F38" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="G38" s="73" t="s">
+        <v>181</v>
+      </c>
+      <c r="H38" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I38" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="19"/>
+      <c r="R38" s="19"/>
+      <c r="S38" s="19"/>
+    </row>
+    <row r="39" spans="1:19" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="93" t="s">
+        <v>182</v>
+      </c>
+      <c r="B39" s="117" t="s">
+        <v>183</v>
+      </c>
+      <c r="C39" s="93" t="s">
+        <v>184</v>
+      </c>
+      <c r="D39" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="17">
+        <v>318</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I39" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J39" s="63" t="s">
+        <v>291</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="L39" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="M39" s="94" t="s">
+        <v>55</v>
+      </c>
+      <c r="N39" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="O39" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="P39" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="Q39" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="R39" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="S39" s="120">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="93" t="s">
+        <v>182</v>
+      </c>
+      <c r="B40" s="119" t="s">
+        <v>183</v>
+      </c>
+      <c r="C40" s="113" t="s">
+        <v>186</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="E40" s="17">
+        <v>532</v>
+      </c>
+      <c r="F40" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I40" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J40" s="66" t="s">
+        <v>188</v>
+      </c>
+      <c r="K40" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="L40" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="M40" s="94" t="s">
+        <v>55</v>
+      </c>
+      <c r="N40" s="64">
+        <v>1</v>
+      </c>
+      <c r="O40" s="64">
+        <v>1</v>
+      </c>
+      <c r="P40" s="64">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="64">
+        <v>1</v>
+      </c>
+      <c r="R40" s="64">
+        <v>1</v>
+      </c>
+      <c r="S40" s="64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="93" t="s">
+        <v>182</v>
+      </c>
+      <c r="B41" s="98" t="s">
+        <v>190</v>
+      </c>
+      <c r="C41" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="E41" s="17">
+        <v>533</v>
+      </c>
+      <c r="F41" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G41" s="16"/>
+      <c r="H41" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I41" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J41" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="K41" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="L41" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="M41" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="N41" s="64">
+        <v>1</v>
+      </c>
+      <c r="O41" s="64">
+        <v>1</v>
+      </c>
+      <c r="P41" s="64">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="64">
+        <v>1</v>
+      </c>
+      <c r="R41" s="64">
+        <v>1</v>
+      </c>
+      <c r="S41" s="64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="93" t="s">
+        <v>182</v>
+      </c>
+      <c r="B42" s="98" t="s">
+        <v>190</v>
+      </c>
+      <c r="C42" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="E42" s="17">
+        <v>534</v>
+      </c>
+      <c r="F42" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I42" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J42" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="K42" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="L42" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="M42" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="N42" s="64">
+        <v>1</v>
+      </c>
+      <c r="O42" s="64">
+        <v>1</v>
+      </c>
+      <c r="P42" s="64">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="64">
+        <v>1</v>
+      </c>
+      <c r="R42" s="64">
+        <v>1</v>
+      </c>
+      <c r="S42" s="64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="93" t="s">
+        <v>182</v>
+      </c>
+      <c r="B43" s="98" t="s">
+        <v>190</v>
+      </c>
+      <c r="C43" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="E43" s="17">
+        <v>535</v>
+      </c>
+      <c r="F43" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="16"/>
+      <c r="H43" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I43" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J43" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="K43" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="L43" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="M43" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="N43" s="64">
+        <v>1</v>
+      </c>
+      <c r="O43" s="64">
+        <v>1</v>
+      </c>
+      <c r="P43" s="64">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="64">
+        <v>1</v>
+      </c>
+      <c r="R43" s="64">
+        <v>1</v>
+      </c>
+      <c r="S43" s="64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="93" t="s">
+        <v>182</v>
+      </c>
+      <c r="B44" s="98" t="s">
+        <v>190</v>
+      </c>
+      <c r="C44" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E44" s="17">
+        <v>536</v>
+      </c>
+      <c r="F44" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I44" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J44" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="K44" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="L44" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="M44" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="N44" s="64">
+        <v>1</v>
+      </c>
+      <c r="O44" s="64">
+        <v>1</v>
+      </c>
+      <c r="P44" s="64">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="64">
+        <v>1</v>
+      </c>
+      <c r="R44" s="64">
+        <v>1</v>
+      </c>
+      <c r="S44" s="64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="93" t="s">
+        <v>199</v>
+      </c>
+      <c r="B45" s="117" t="s">
+        <v>200</v>
+      </c>
+      <c r="C45" s="93" t="s">
+        <v>201</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="E45" s="17"/>
+      <c r="F45" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="H45" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I45" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="J45" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="K45" s="29"/>
+      <c r="L45" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="M45" s="94"/>
+      <c r="N45" s="63"/>
+      <c r="O45" s="29"/>
+      <c r="P45" s="29"/>
+      <c r="Q45" s="29"/>
+      <c r="R45" s="29"/>
+      <c r="S45" s="29"/>
+    </row>
+    <row r="46" spans="1:19" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="80" t="s">
+        <v>199</v>
+      </c>
+      <c r="B46" s="98" t="s">
+        <v>200</v>
+      </c>
+      <c r="C46" s="80" t="s">
+        <v>201</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="E46" s="17">
+        <v>597</v>
+      </c>
+      <c r="F46" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" s="82" t="s">
+        <v>68</v>
+      </c>
+      <c r="H46" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I46" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="J46" s="66" t="s">
+        <v>206</v>
+      </c>
+      <c r="K46" s="19"/>
+      <c r="L46" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="M46" s="34"/>
+      <c r="N46" s="66"/>
+      <c r="O46" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="P46" s="19"/>
+      <c r="Q46" s="19"/>
+      <c r="R46" s="19"/>
+      <c r="S46" s="19"/>
+    </row>
+    <row r="47" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="93" t="s">
+        <v>199</v>
+      </c>
+      <c r="B47" s="117" t="s">
+        <v>200</v>
+      </c>
+      <c r="C47" s="93" t="s">
+        <v>207</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="E47" s="17">
+        <v>500</v>
+      </c>
+      <c r="F47" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="82" t="s">
+        <v>209</v>
+      </c>
+      <c r="H47" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I47" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="J47" s="63" t="s">
+        <v>210</v>
+      </c>
+      <c r="K47" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="L47" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="M47" s="94"/>
+      <c r="N47" s="120">
+        <v>0.8</v>
+      </c>
+      <c r="O47" s="122">
+        <v>0.85</v>
+      </c>
+      <c r="P47" s="29"/>
+      <c r="Q47" s="29"/>
+      <c r="R47" s="29"/>
+      <c r="S47" s="29"/>
+    </row>
+    <row r="48" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="93" t="s">
+        <v>199</v>
+      </c>
+      <c r="B48" s="117" t="s">
+        <v>200</v>
+      </c>
+      <c r="C48" s="93" t="s">
+        <v>207</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="E48" s="17"/>
+      <c r="F48" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" s="82" t="s">
+        <v>209</v>
+      </c>
+      <c r="H48" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I48" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="J48" s="63" t="s">
+        <v>210</v>
+      </c>
+      <c r="K48" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="L48" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="M48" s="94"/>
+      <c r="N48" s="120">
+        <v>0.8</v>
+      </c>
+      <c r="O48" s="122">
+        <v>0.85</v>
+      </c>
+      <c r="P48" s="29"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="29"/>
+      <c r="S48" s="29"/>
+    </row>
+    <row r="49" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="80" t="s">
+        <v>199</v>
+      </c>
+      <c r="B49" s="98" t="s">
+        <v>200</v>
+      </c>
+      <c r="C49" s="80" t="s">
+        <v>207</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="E49" s="17"/>
+      <c r="F49" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="G49" s="82" t="s">
+        <v>68</v>
+      </c>
+      <c r="H49" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I49" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="J49" s="114" t="s">
+        <v>216</v>
+      </c>
+      <c r="K49" s="19"/>
+      <c r="L49" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="M49" s="34"/>
+      <c r="N49" s="66"/>
+      <c r="O49" s="19"/>
+      <c r="P49" s="19"/>
+      <c r="Q49" s="19"/>
+      <c r="R49" s="19"/>
+      <c r="S49" s="19"/>
+    </row>
+    <row r="50" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="80" t="s">
+        <v>217</v>
+      </c>
+      <c r="B50" s="125" t="s">
+        <v>218</v>
+      </c>
+      <c r="C50" s="126" t="s">
+        <v>219</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="E50" s="17">
+        <v>576</v>
+      </c>
+      <c r="F50" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G50" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="H50" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="I50" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="66" t="s">
+        <v>221</v>
+      </c>
+      <c r="K50" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="L50" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="M50" s="127"/>
+      <c r="N50" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="O50" s="21">
+        <v>1</v>
+      </c>
+      <c r="P50" s="21">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="21">
+        <v>1</v>
+      </c>
+      <c r="R50" s="21">
+        <v>1</v>
+      </c>
+      <c r="S50" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="93" t="s">
+        <v>217</v>
+      </c>
+      <c r="B51" s="93" t="s">
+        <v>222</v>
+      </c>
+      <c r="C51" s="128" t="s">
+        <v>223</v>
+      </c>
+      <c r="D51" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="E51" s="17">
+        <v>573</v>
+      </c>
+      <c r="F51" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G51" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="H51" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="I51" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J51" s="63" t="s">
+        <v>225</v>
+      </c>
+      <c r="K51" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="L51" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="M51" s="129"/>
+      <c r="N51" s="63"/>
+      <c r="O51" s="29">
+        <v>112</v>
+      </c>
+      <c r="P51" s="29">
+        <v>99</v>
+      </c>
+      <c r="Q51" s="29">
+        <v>88</v>
+      </c>
+      <c r="R51" s="29">
+        <v>75</v>
+      </c>
+      <c r="S51" s="29">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A52" s="80" t="s">
+        <v>217</v>
+      </c>
+      <c r="B52" s="80" t="s">
+        <v>222</v>
+      </c>
+      <c r="C52" s="126" t="s">
+        <v>223</v>
+      </c>
+      <c r="D52" s="88" t="s">
+        <v>230</v>
+      </c>
+      <c r="E52" s="88"/>
+      <c r="F52" s="89" t="s">
+        <v>51</v>
+      </c>
+      <c r="G52" s="89" t="s">
+        <v>68</v>
+      </c>
+      <c r="H52" s="73" t="s">
+        <v>227</v>
+      </c>
+      <c r="I52" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J52" s="130" t="s">
+        <v>231</v>
+      </c>
+      <c r="K52" s="131" t="s">
+        <v>134</v>
+      </c>
+      <c r="L52" s="131" t="s">
+        <v>134</v>
+      </c>
+      <c r="M52" s="127"/>
+      <c r="N52" s="64">
+        <v>0.8</v>
+      </c>
+      <c r="O52" s="64">
+        <v>0.8</v>
+      </c>
+      <c r="P52" s="64">
+        <v>0.8</v>
+      </c>
+      <c r="Q52" s="64">
+        <v>0.8</v>
+      </c>
+      <c r="R52" s="64">
+        <v>0.8</v>
+      </c>
+      <c r="S52" s="64">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="80" t="s">
+        <v>217</v>
+      </c>
+      <c r="B53" s="98" t="s">
+        <v>232</v>
+      </c>
+      <c r="C53" s="80" t="s">
+        <v>233</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="E53" s="17"/>
+      <c r="F53" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="G53" s="73" t="s">
+        <v>235</v>
+      </c>
+      <c r="H53" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I53" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J53" s="66" t="s">
+        <v>236</v>
+      </c>
+      <c r="K53" s="19"/>
+      <c r="L53" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="M53" s="34"/>
+      <c r="N53" s="64">
+        <v>1</v>
+      </c>
+      <c r="O53" s="64">
+        <v>1</v>
+      </c>
+      <c r="P53" s="64">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="64">
+        <v>1</v>
+      </c>
+      <c r="R53" s="64">
+        <v>1</v>
+      </c>
+      <c r="S53" s="64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="80" t="s">
+        <v>217</v>
+      </c>
+      <c r="B54" s="98" t="s">
+        <v>237</v>
+      </c>
+      <c r="C54" s="80" t="s">
+        <v>238</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="E54" s="17">
+        <v>460</v>
+      </c>
+      <c r="F54" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="G54" s="73" t="s">
+        <v>93</v>
+      </c>
+      <c r="H54" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="I54" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J54" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="K54" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="L54" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="M54" s="34"/>
+      <c r="N54" s="64">
+        <v>0.8</v>
+      </c>
+      <c r="O54" s="21">
+        <v>0.82</v>
+      </c>
+      <c r="P54" s="21">
+        <v>0.83</v>
+      </c>
+      <c r="Q54" s="21">
+        <v>0.83</v>
+      </c>
+      <c r="R54" s="21">
+        <v>0.84</v>
+      </c>
+      <c r="S54" s="21">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="80" t="s">
+        <v>217</v>
+      </c>
+      <c r="B55" s="98" t="s">
+        <v>242</v>
+      </c>
+      <c r="C55" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="D55" s="73" t="s">
+        <v>244</v>
+      </c>
+      <c r="E55" s="17"/>
+      <c r="F55" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="G55" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="H55" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I55" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J55" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="K55" s="19"/>
+      <c r="L55" s="19"/>
+      <c r="M55" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="N55" s="66"/>
+      <c r="O55" s="19"/>
+      <c r="P55" s="19"/>
+      <c r="Q55" s="19"/>
+      <c r="R55" s="19"/>
+      <c r="S55" s="19"/>
+    </row>
+    <row r="56" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="80" t="s">
+        <v>246</v>
+      </c>
+      <c r="B56" s="98" t="s">
+        <v>247</v>
+      </c>
+      <c r="C56" s="80" t="s">
+        <v>248</v>
+      </c>
+      <c r="D56" s="116" t="s">
+        <v>249</v>
+      </c>
+      <c r="E56" s="116"/>
+      <c r="F56" s="134" t="s">
+        <v>24</v>
+      </c>
+      <c r="G56" s="134" t="s">
+        <v>68</v>
+      </c>
+      <c r="H56" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I56" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J56" s="66" t="s">
+        <v>249</v>
+      </c>
+      <c r="K56" s="19"/>
+      <c r="L56" s="19"/>
+      <c r="M56" s="34"/>
+      <c r="N56" s="66"/>
+      <c r="O56" s="19"/>
+      <c r="P56" s="19"/>
+      <c r="Q56" s="19"/>
+      <c r="R56" s="19"/>
+      <c r="S56" s="19"/>
+    </row>
+    <row r="57" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="80" t="s">
+        <v>246</v>
+      </c>
+      <c r="B57" s="80" t="s">
+        <v>250</v>
+      </c>
+      <c r="C57" s="80" t="s">
+        <v>251</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="E57" s="17">
+        <v>553</v>
+      </c>
+      <c r="F57" s="134" t="s">
+        <v>24</v>
+      </c>
+      <c r="G57" s="82" t="s">
+        <v>68</v>
+      </c>
+      <c r="H57" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I57" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J57" s="66" t="s">
+        <v>253</v>
+      </c>
+      <c r="K57" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="L57" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="M57" s="34"/>
+      <c r="N57" s="66"/>
+      <c r="O57" s="21">
+        <v>0.85</v>
+      </c>
+      <c r="P57" s="19"/>
+      <c r="Q57" s="19"/>
+      <c r="R57" s="19"/>
+      <c r="S57" s="19"/>
+    </row>
+    <row r="58" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="80" t="s">
+        <v>246</v>
+      </c>
+      <c r="B58" s="80" t="s">
+        <v>250</v>
+      </c>
+      <c r="C58" s="135" t="s">
+        <v>256</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="E58" s="17"/>
+      <c r="F58" s="134" t="s">
+        <v>24</v>
+      </c>
+      <c r="G58" s="82" t="s">
+        <v>68</v>
+      </c>
+      <c r="H58" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="I58" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J58" s="66" t="s">
+        <v>258</v>
+      </c>
+      <c r="K58" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="L58" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="M58" s="136" t="s">
+        <v>260</v>
+      </c>
+      <c r="N58" s="66">
+        <v>86.1</v>
+      </c>
+      <c r="O58" s="19">
+        <v>86.6</v>
+      </c>
+      <c r="P58" s="19"/>
+      <c r="Q58" s="19"/>
+      <c r="R58" s="19"/>
+      <c r="S58" s="19"/>
+    </row>
+    <row r="59" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="80" t="s">
+        <v>246</v>
+      </c>
+      <c r="B59" s="80" t="s">
+        <v>250</v>
+      </c>
+      <c r="C59" s="135" t="s">
+        <v>256</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="E59" s="17"/>
+      <c r="F59" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="G59" s="82" t="s">
+        <v>68</v>
+      </c>
+      <c r="H59" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="I59" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J59" s="66" t="s">
+        <v>258</v>
+      </c>
+      <c r="K59" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="L59" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="M59" s="136" t="s">
+        <v>260</v>
+      </c>
+      <c r="N59" s="66"/>
+      <c r="O59" s="19"/>
+      <c r="P59" s="19"/>
+      <c r="Q59" s="19"/>
+      <c r="R59" s="19"/>
+      <c r="S59" s="19"/>
+    </row>
+    <row r="60" spans="1:19" ht="124.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="93" t="s">
+        <v>246</v>
+      </c>
+      <c r="B60" s="93" t="s">
+        <v>250</v>
+      </c>
+      <c r="C60" s="137" t="s">
+        <v>256</v>
+      </c>
+      <c r="D60" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="E60" s="17"/>
+      <c r="F60" s="134" t="s">
+        <v>51</v>
+      </c>
+      <c r="G60" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="H60" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I60" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J60" s="63"/>
+      <c r="K60" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="L60" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="M60" s="136" t="s">
+        <v>260</v>
+      </c>
+      <c r="N60" s="63"/>
+      <c r="O60" s="29"/>
+      <c r="P60" s="29"/>
+      <c r="Q60" s="29"/>
+      <c r="R60" s="29"/>
+      <c r="S60" s="29"/>
+    </row>
+    <row r="61" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="A61" s="80" t="s">
+        <v>246</v>
+      </c>
+      <c r="B61" s="80" t="s">
+        <v>250</v>
+      </c>
+      <c r="C61" s="135" t="s">
+        <v>256</v>
+      </c>
+      <c r="D61" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="E61" s="17"/>
+      <c r="F61" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G61" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="H61" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="I61" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J61" s="66" t="s">
+        <v>264</v>
+      </c>
+      <c r="K61" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="L61" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="M61" s="136"/>
+      <c r="N61" s="66"/>
+      <c r="O61" s="19"/>
+      <c r="P61" s="19"/>
+      <c r="Q61" s="19"/>
+      <c r="R61" s="19"/>
+      <c r="S61" s="19"/>
+    </row>
+    <row r="62" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="80" t="s">
+        <v>246</v>
+      </c>
+      <c r="B62" s="98" t="s">
+        <v>265</v>
+      </c>
+      <c r="C62" s="126" t="s">
+        <v>266</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="E62" s="17"/>
+      <c r="F62" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="G62" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="H62" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I62" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J62" s="66" t="s">
+        <v>268</v>
+      </c>
+      <c r="K62" s="19"/>
+      <c r="L62" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="M62" s="127" t="s">
+        <v>270</v>
+      </c>
+      <c r="N62" s="66"/>
+      <c r="O62" s="19"/>
+      <c r="P62" s="19"/>
+      <c r="Q62" s="19"/>
+      <c r="R62" s="19"/>
+      <c r="S62" s="19"/>
+    </row>
+    <row r="63" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+      <c r="A63" s="93" t="s">
+        <v>271</v>
+      </c>
+      <c r="B63" s="117" t="s">
+        <v>272</v>
+      </c>
+      <c r="C63" s="93" t="s">
+        <v>273</v>
+      </c>
+      <c r="D63" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="E63" s="17">
+        <v>546</v>
+      </c>
+      <c r="F63" s="134" t="s">
+        <v>24</v>
+      </c>
+      <c r="G63" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="H63" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="I63" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J63" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="K63" s="29" t="s">
+        <v>276</v>
+      </c>
+      <c r="L63" s="29" t="s">
+        <v>276</v>
+      </c>
+      <c r="M63" s="94"/>
+      <c r="N63" s="138" t="s">
+        <v>277</v>
+      </c>
+      <c r="O63" s="29"/>
+      <c r="P63" s="29"/>
+      <c r="Q63" s="29"/>
+      <c r="R63" s="29"/>
+      <c r="S63" s="29"/>
+    </row>
+    <row r="64" spans="1:19" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="93" t="s">
+        <v>271</v>
+      </c>
+      <c r="B64" s="117" t="s">
+        <v>278</v>
+      </c>
+      <c r="C64" s="93" t="s">
+        <v>279</v>
+      </c>
+      <c r="D64" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="E64" s="17">
+        <v>542</v>
+      </c>
+      <c r="F64" s="134" t="s">
+        <v>24</v>
+      </c>
+      <c r="G64" s="27"/>
+      <c r="H64" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="I64" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J64" s="28" t="s">
+        <v>281</v>
+      </c>
+      <c r="K64" s="29"/>
+      <c r="L64" s="29"/>
+      <c r="M64" s="118" t="s">
+        <v>55</v>
+      </c>
+      <c r="N64" s="63"/>
+      <c r="O64" s="29"/>
+      <c r="P64" s="29"/>
+      <c r="Q64" s="29"/>
+      <c r="R64" s="29"/>
+      <c r="S64" s="29"/>
+    </row>
+    <row r="65" spans="1:19" ht="171.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="93" t="s">
+        <v>271</v>
+      </c>
+      <c r="B65" s="117" t="s">
+        <v>278</v>
+      </c>
+      <c r="C65" s="93" t="s">
+        <v>282</v>
+      </c>
+      <c r="D65" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="E65" s="17">
+        <v>541</v>
+      </c>
+      <c r="F65" s="134" t="s">
+        <v>24</v>
+      </c>
+      <c r="G65" s="62" t="s">
+        <v>284</v>
+      </c>
+      <c r="H65" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="I65" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J65" s="63" t="s">
+        <v>285</v>
+      </c>
+      <c r="K65" s="29" t="s">
+        <v>276</v>
+      </c>
+      <c r="L65" s="29" t="s">
+        <v>276</v>
+      </c>
+      <c r="M65" s="94"/>
+      <c r="N65" s="63"/>
+      <c r="O65" s="29"/>
+      <c r="P65" s="29"/>
+      <c r="Q65" s="29"/>
+      <c r="R65" s="29"/>
+      <c r="S65" s="29"/>
+    </row>
+    <row r="66" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="80" t="s">
+        <v>271</v>
+      </c>
+      <c r="B66" s="98" t="s">
+        <v>286</v>
+      </c>
+      <c r="C66" s="80" t="s">
+        <v>287</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="E66" s="17">
+        <v>547</v>
+      </c>
+      <c r="F66" s="134" t="s">
+        <v>24</v>
+      </c>
+      <c r="G66" s="73"/>
+      <c r="H66" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="I66" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J66" s="66" t="s">
+        <v>289</v>
+      </c>
+      <c r="K66" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="L66" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="M66" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="N66" s="64">
+        <v>0.8</v>
+      </c>
+      <c r="O66" s="64">
+        <v>0.85</v>
+      </c>
+      <c r="P66" s="64">
+        <v>0.85</v>
+      </c>
+      <c r="Q66" s="64">
+        <v>0.87</v>
+      </c>
+      <c r="R66" s="64">
+        <v>0.87</v>
+      </c>
+      <c r="S66" s="64">
+        <v>0.87</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="N1:S1"/>
+    <mergeCell ref="L12:L13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C65FC67-03C0-423A-92BB-67DDC6589F1C}">
+  <sheetPr>
+    <tabColor theme="8" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:S68"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="39.5546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="58.6640625" style="2" customWidth="1"/>
+    <col min="4" max="9" width="34.5546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="23.6640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="26.44140625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="27.21875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="13.77734375" style="2" customWidth="1"/>
+    <col min="15" max="16" width="11.5546875" style="2" customWidth="1"/>
+    <col min="17" max="19" width="16.5546875" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="11.5546875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="142" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="143"/>
+      <c r="P1" s="143"/>
+      <c r="Q1" s="143"/>
+      <c r="R1" s="143"/>
+      <c r="S1" s="143"/>
+    </row>
+    <row r="2" spans="1:19" ht="36" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="18"/>
+      <c r="K3" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="21">
+        <v>0.95</v>
+      </c>
       <c r="O3" s="21">
         <v>0.98</v>
       </c>
@@ -2504,20 +5963,8 @@
       <c r="S3" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="T3" s="21">
-        <v>0.95</v>
-      </c>
-      <c r="U3" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="V3" s="21">
-        <v>0.95</v>
-      </c>
-      <c r="W3" s="19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="62.4">
+    </row>
+    <row r="4" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>20</v>
       </c>
@@ -2565,20 +6012,8 @@
       </c>
       <c r="R4" s="21"/>
       <c r="S4" s="22"/>
-      <c r="T4" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="U4" s="21">
-        <v>0.94</v>
-      </c>
-      <c r="V4" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="W4" s="21">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="46.8">
+    </row>
+    <row r="5" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>20</v>
       </c>
@@ -2620,12 +6055,8 @@
       <c r="Q5" s="29"/>
       <c r="R5" s="29"/>
       <c r="S5" s="31"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-    </row>
-    <row r="6" spans="1:23" ht="69" customHeight="1">
+    </row>
+    <row r="6" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>20</v>
       </c>
@@ -2667,12 +6098,8 @@
       <c r="Q6" s="29"/>
       <c r="R6" s="29"/>
       <c r="S6" s="31"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="29"/>
-      <c r="W6" s="29"/>
-    </row>
-    <row r="7" spans="1:23" ht="109.2">
+    </row>
+    <row r="7" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A7" s="32" t="s">
         <v>47</v>
       </c>
@@ -2718,12 +6145,8 @@
       <c r="Q7" s="40"/>
       <c r="R7" s="40"/>
       <c r="S7" s="44"/>
-      <c r="T7" s="40"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="40"/>
-      <c r="W7" s="40"/>
-    </row>
-    <row r="8" spans="1:23" ht="62.4">
+    </row>
+    <row r="8" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
         <v>47</v>
       </c>
@@ -2772,12 +6195,8 @@
       <c r="Q8" s="40"/>
       <c r="R8" s="40"/>
       <c r="S8" s="44"/>
-      <c r="T8" s="40"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="40"/>
-      <c r="W8" s="40"/>
-    </row>
-    <row r="9" spans="1:23" ht="93.6">
+    </row>
+    <row r="9" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A9" s="32" t="s">
         <v>47</v>
       </c>
@@ -2813,12 +6232,8 @@
       <c r="Q9" s="40"/>
       <c r="R9" s="40"/>
       <c r="S9" s="44"/>
-      <c r="T9" s="40"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="40"/>
-      <c r="W9" s="40"/>
-    </row>
-    <row r="10" spans="1:23" ht="75">
+    </row>
+    <row r="10" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
         <v>47</v>
       </c>
@@ -2876,12 +6291,8 @@
         <f>R10/Q10</f>
         <v>1.0608333333333333</v>
       </c>
-      <c r="T10" s="40"/>
-      <c r="U10" s="40"/>
-      <c r="V10" s="40"/>
-      <c r="W10" s="40"/>
-    </row>
-    <row r="11" spans="1:23" ht="46.8">
+    </row>
+    <row r="11" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A11" s="32" t="s">
         <v>47</v>
       </c>
@@ -2932,20 +6343,8 @@
       </c>
       <c r="R11" s="40"/>
       <c r="S11" s="44"/>
-      <c r="T11" s="55">
-        <v>0.9</v>
-      </c>
-      <c r="U11" s="55">
-        <v>0.95</v>
-      </c>
-      <c r="V11" s="55">
-        <v>0.95</v>
-      </c>
-      <c r="W11" s="55">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="60">
+    </row>
+    <row r="12" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A12" s="32" t="s">
         <v>47</v>
       </c>
@@ -2991,12 +6390,8 @@
       <c r="Q12" s="40"/>
       <c r="R12" s="40"/>
       <c r="S12" s="44"/>
-      <c r="T12" s="40"/>
-      <c r="U12" s="40"/>
-      <c r="V12" s="40"/>
-      <c r="W12" s="40"/>
-    </row>
-    <row r="13" spans="1:23" ht="46.8">
+    </row>
+    <row r="13" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A13" s="56" t="s">
         <v>76</v>
       </c>
@@ -3028,7 +6423,7 @@
       <c r="K13" s="63" t="s">
         <v>81</v>
       </c>
-      <c r="L13" s="141" t="s">
+      <c r="L13" s="144" t="s">
         <v>82</v>
       </c>
       <c r="M13" s="59" t="s">
@@ -3051,12 +6446,8 @@
         <f>R13/Q13</f>
         <v>1.22</v>
       </c>
-      <c r="T13" s="66"/>
-      <c r="U13" s="66"/>
-      <c r="V13" s="143"/>
-      <c r="W13" s="143"/>
-    </row>
-    <row r="14" spans="1:23" ht="75">
+    </row>
+    <row r="14" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A14" s="56" t="s">
         <v>76</v>
       </c>
@@ -3088,7 +6479,7 @@
       <c r="K14" s="63" t="s">
         <v>81</v>
       </c>
-      <c r="L14" s="142"/>
+      <c r="L14" s="145"/>
       <c r="M14" s="59" t="s">
         <v>43</v>
       </c>
@@ -3100,12 +6491,8 @@
       </c>
       <c r="R14" s="19"/>
       <c r="S14" s="23"/>
-      <c r="T14" s="66"/>
-      <c r="U14" s="66"/>
-      <c r="V14" s="143"/>
-      <c r="W14" s="143"/>
-    </row>
-    <row r="15" spans="1:23" ht="46.8">
+    </row>
+    <row r="15" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A15" s="56" t="s">
         <v>76</v>
       </c>
@@ -3149,12 +6536,8 @@
       <c r="Q15" s="68"/>
       <c r="R15" s="68"/>
       <c r="S15" s="69"/>
-      <c r="T15" s="68"/>
-      <c r="U15" s="68"/>
-      <c r="V15" s="68"/>
-      <c r="W15" s="68"/>
-    </row>
-    <row r="16" spans="1:23" ht="46.8">
+    </row>
+    <row r="16" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A16" s="56" t="s">
         <v>76</v>
       </c>
@@ -3196,12 +6579,8 @@
       <c r="Q16" s="19"/>
       <c r="R16" s="19"/>
       <c r="S16" s="23"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="19"/>
-    </row>
-    <row r="17" spans="1:23" ht="31.2">
+    </row>
+    <row r="17" spans="1:19" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A17" s="56" t="s">
         <v>76</v>
       </c>
@@ -3241,12 +6620,8 @@
       <c r="Q17" s="19"/>
       <c r="R17" s="19"/>
       <c r="S17" s="23"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="19"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="19"/>
-    </row>
-    <row r="18" spans="1:23" ht="62.4">
+    </row>
+    <row r="18" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A18" s="56" t="s">
         <v>76</v>
       </c>
@@ -3282,12 +6657,8 @@
       <c r="Q18" s="19"/>
       <c r="R18" s="19"/>
       <c r="S18" s="23"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-    </row>
-    <row r="19" spans="1:23" ht="150">
+    </row>
+    <row r="19" spans="1:19" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A19" s="56" t="s">
         <v>76</v>
       </c>
@@ -3327,12 +6698,8 @@
       <c r="Q19" s="29"/>
       <c r="R19" s="29"/>
       <c r="S19" s="31"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="29"/>
-      <c r="V19" s="29"/>
-      <c r="W19" s="29"/>
-    </row>
-    <row r="20" spans="1:23" ht="120">
+    </row>
+    <row r="20" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A20" s="79" t="s">
         <v>101</v>
       </c>
@@ -3374,12 +6741,8 @@
       <c r="Q20" s="19"/>
       <c r="R20" s="19"/>
       <c r="S20" s="23"/>
-      <c r="T20" s="19"/>
-      <c r="U20" s="19"/>
-      <c r="V20" s="19"/>
-      <c r="W20" s="19"/>
-    </row>
-    <row r="21" spans="1:23" ht="105">
+    </row>
+    <row r="21" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A21" s="79" t="s">
         <v>101</v>
       </c>
@@ -3425,20 +6788,8 @@
       </c>
       <c r="R21" s="21"/>
       <c r="S21" s="22"/>
-      <c r="T21" s="21">
-        <v>1</v>
-      </c>
-      <c r="U21" s="21">
-        <v>1</v>
-      </c>
-      <c r="V21" s="21">
-        <v>1</v>
-      </c>
-      <c r="W21" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" ht="62.4">
+    </row>
+    <row r="22" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A22" s="79" t="s">
         <v>101</v>
       </c>
@@ -3482,12 +6833,8 @@
       </c>
       <c r="R22" s="19"/>
       <c r="S22" s="23"/>
-      <c r="T22" s="19"/>
-      <c r="U22" s="19"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="19"/>
-    </row>
-    <row r="23" spans="1:23" ht="60">
+    </row>
+    <row r="23" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A23" s="79" t="s">
         <v>101</v>
       </c>
@@ -3537,20 +6884,8 @@
       </c>
       <c r="R23" s="86"/>
       <c r="S23" s="87"/>
-      <c r="T23" s="86">
-        <v>0.45</v>
-      </c>
-      <c r="U23" s="86">
-        <v>0.5</v>
-      </c>
-      <c r="V23" s="86">
-        <v>0.53</v>
-      </c>
-      <c r="W23" s="86">
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" ht="62.4">
+    </row>
+    <row r="24" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A24" s="79" t="s">
         <v>101</v>
       </c>
@@ -3596,12 +6931,8 @@
       <c r="Q24" s="19"/>
       <c r="R24" s="19"/>
       <c r="S24" s="23"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="19"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="19"/>
-    </row>
-    <row r="25" spans="1:23" ht="46.8">
+    </row>
+    <row r="25" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A25" s="79" t="s">
         <v>101</v>
       </c>
@@ -3652,12 +6983,8 @@
       </c>
       <c r="R25" s="19"/>
       <c r="S25" s="23"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="19"/>
-      <c r="V25" s="19"/>
-      <c r="W25" s="19"/>
-    </row>
-    <row r="26" spans="1:23" ht="46.8">
+    </row>
+    <row r="26" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A26" s="79" t="s">
         <v>101</v>
       </c>
@@ -3715,12 +7042,8 @@
         <f>R26/Q26</f>
         <v>0.99356223175965663</v>
       </c>
-      <c r="T26" s="19"/>
-      <c r="U26" s="19"/>
-      <c r="V26" s="19"/>
-      <c r="W26" s="19"/>
-    </row>
-    <row r="27" spans="1:23" ht="93.6">
+    </row>
+    <row r="27" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A27" s="57" t="s">
         <v>135</v>
       </c>
@@ -3758,12 +7081,8 @@
       <c r="Q27" s="29"/>
       <c r="R27" s="29"/>
       <c r="S27" s="31"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="29"/>
-      <c r="W27" s="29"/>
-    </row>
-    <row r="28" spans="1:23" ht="93.6">
+    </row>
+    <row r="28" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A28" s="79" t="s">
         <v>135</v>
       </c>
@@ -3807,12 +7126,8 @@
       <c r="Q28" s="19"/>
       <c r="R28" s="19"/>
       <c r="S28" s="23"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="19"/>
-      <c r="V28" s="19"/>
-      <c r="W28" s="19"/>
-    </row>
-    <row r="29" spans="1:23" ht="62.4">
+    </row>
+    <row r="29" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A29" s="79" t="s">
         <v>135</v>
       </c>
@@ -3856,16 +7171,8 @@
       </c>
       <c r="R29" s="19"/>
       <c r="S29" s="23"/>
-      <c r="T29" s="19">
-        <v>28</v>
-      </c>
-      <c r="U29" s="19">
-        <v>22</v>
-      </c>
-      <c r="V29" s="97"/>
-      <c r="W29" s="97"/>
-    </row>
-    <row r="30" spans="1:23" ht="62.4">
+    </row>
+    <row r="30" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A30" s="79" t="s">
         <v>135</v>
       </c>
@@ -3919,20 +7226,8 @@
         <f>R30/Q30</f>
         <v>0</v>
       </c>
-      <c r="T30" s="19">
-        <v>11</v>
-      </c>
-      <c r="U30" s="19">
-        <v>7</v>
-      </c>
-      <c r="V30" s="19">
-        <v>7</v>
-      </c>
-      <c r="W30" s="19">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" ht="62.4">
+    </row>
+    <row r="31" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A31" s="79" t="s">
         <v>135</v>
       </c>
@@ -3988,20 +7283,8 @@
         <f>R31/Q31</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="T31" s="99">
-        <v>5</v>
-      </c>
-      <c r="U31" s="99">
-        <v>29</v>
-      </c>
-      <c r="V31" s="99">
-        <v>20</v>
-      </c>
-      <c r="W31" s="99">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" ht="75">
+    </row>
+    <row r="32" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A32" s="33" t="s">
         <v>156</v>
       </c>
@@ -4047,7 +7330,7 @@
       <c r="O32" s="110">
         <v>6.7799999999999999E-2</v>
       </c>
-      <c r="P32" s="144">
+      <c r="P32" s="139">
         <f>O32/N32</f>
         <v>1.3559999999999999</v>
       </c>
@@ -4057,24 +7340,12 @@
       <c r="R32" s="55">
         <v>8.1699999999999995E-2</v>
       </c>
-      <c r="S32" s="144">
+      <c r="S32" s="139">
         <f>R32/Q32</f>
         <v>1.02125</v>
       </c>
-      <c r="T32" s="55">
-        <v>0.1</v>
-      </c>
-      <c r="U32" s="55">
-        <v>0.12</v>
-      </c>
-      <c r="V32" s="55">
-        <v>0.13</v>
-      </c>
-      <c r="W32" s="55">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" ht="46.8">
+    </row>
+    <row r="33" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A33" s="33" t="s">
         <v>156</v>
       </c>
@@ -4120,20 +7391,8 @@
       </c>
       <c r="R33" s="40"/>
       <c r="S33" s="44"/>
-      <c r="T33" s="55">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="U33" s="55">
-        <v>0.76</v>
-      </c>
-      <c r="V33" s="55">
-        <v>0.76</v>
-      </c>
-      <c r="W33" s="55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" ht="105">
+    </row>
+    <row r="34" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A34" s="33" t="s">
         <v>156</v>
       </c>
@@ -4181,20 +7440,8 @@
       </c>
       <c r="R34" s="40"/>
       <c r="S34" s="44"/>
-      <c r="T34" s="40">
-        <v>110</v>
-      </c>
-      <c r="U34" s="40">
-        <v>110</v>
-      </c>
-      <c r="V34" s="40">
-        <v>115</v>
-      </c>
-      <c r="W34" s="40">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23" ht="120">
+    </row>
+    <row r="35" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A35" s="33" t="s">
         <v>156</v>
       </c>
@@ -4240,20 +7487,8 @@
       </c>
       <c r="R35" s="108"/>
       <c r="S35" s="109"/>
-      <c r="T35" s="108">
-        <v>68</v>
-      </c>
-      <c r="U35" s="108">
-        <v>102</v>
-      </c>
-      <c r="V35" s="108">
-        <v>136</v>
-      </c>
-      <c r="W35" s="108">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" ht="46.8">
+    </row>
+    <row r="36" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A36" s="33" t="s">
         <v>156</v>
       </c>
@@ -4301,20 +7536,8 @@
       </c>
       <c r="R36" s="40"/>
       <c r="S36" s="44"/>
-      <c r="T36" s="55">
-        <v>0.44</v>
-      </c>
-      <c r="U36" s="55">
-        <v>0.65</v>
-      </c>
-      <c r="V36" s="55">
-        <v>0.65</v>
-      </c>
-      <c r="W36" s="55">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" ht="124.8">
+    </row>
+    <row r="37" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A37" s="80" t="s">
         <v>170</v>
       </c>
@@ -4352,12 +7575,8 @@
       <c r="Q37" s="19"/>
       <c r="R37" s="19"/>
       <c r="S37" s="23"/>
-      <c r="T37" s="19"/>
-      <c r="U37" s="19"/>
-      <c r="V37" s="19"/>
-      <c r="W37" s="19"/>
-    </row>
-    <row r="38" spans="1:23" ht="60">
+    </row>
+    <row r="38" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A38" s="80" t="s">
         <v>170</v>
       </c>
@@ -4395,12 +7614,8 @@
       <c r="Q38" s="19"/>
       <c r="R38" s="19"/>
       <c r="S38" s="23"/>
-      <c r="T38" s="19"/>
-      <c r="U38" s="19"/>
-      <c r="V38" s="19"/>
-      <c r="W38" s="19"/>
-    </row>
-    <row r="39" spans="1:23" ht="93.6">
+    </row>
+    <row r="39" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A39" s="80" t="s">
         <v>170</v>
       </c>
@@ -4438,12 +7653,8 @@
       <c r="Q39" s="19"/>
       <c r="R39" s="19"/>
       <c r="S39" s="23"/>
-      <c r="T39" s="19"/>
-      <c r="U39" s="19"/>
-      <c r="V39" s="19"/>
-      <c r="W39" s="19"/>
-    </row>
-    <row r="40" spans="1:23" ht="46.95" customHeight="1">
+    </row>
+    <row r="40" spans="1:19" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="93" t="s">
         <v>182</v>
       </c>
@@ -4486,10 +7697,10 @@
       <c r="N40" s="120">
         <v>0.85</v>
       </c>
-      <c r="O40" s="146">
+      <c r="O40" s="141">
         <v>0.86160000000000003</v>
       </c>
-      <c r="P40" s="145">
+      <c r="P40" s="140">
         <f>O40/N40</f>
         <v>1.0136470588235296</v>
       </c>
@@ -4497,24 +7708,12 @@
         <v>0.85</v>
       </c>
       <c r="R40" s="29"/>
-      <c r="S40" s="145">
+      <c r="S40" s="140">
         <f>R40/Q40</f>
         <v>0</v>
       </c>
-      <c r="T40" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="U40" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="V40" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="W40" s="120">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" ht="62.4">
+    </row>
+    <row r="41" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A41" s="93" t="s">
         <v>182</v>
       </c>
@@ -4558,7 +7757,7 @@
       <c r="O41" s="65">
         <v>1.3392999999999999</v>
       </c>
-      <c r="P41" s="145">
+      <c r="P41" s="140">
         <f>O41/N41</f>
         <v>1.3392999999999999</v>
       </c>
@@ -4568,24 +7767,12 @@
       <c r="R41" s="65">
         <v>1.099</v>
       </c>
-      <c r="S41" s="145">
+      <c r="S41" s="140">
         <f>R41/Q41</f>
         <v>1.099</v>
       </c>
-      <c r="T41" s="64">
-        <v>1</v>
-      </c>
-      <c r="U41" s="64">
-        <v>1</v>
-      </c>
-      <c r="V41" s="64">
-        <v>1</v>
-      </c>
-      <c r="W41" s="64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23" ht="105">
+    </row>
+    <row r="42" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A42" s="93" t="s">
         <v>182</v>
       </c>
@@ -4629,7 +7816,7 @@
       <c r="O42" s="65">
         <v>1.5142</v>
       </c>
-      <c r="P42" s="145">
+      <c r="P42" s="140">
         <f t="shared" ref="P42:P45" si="0">O42/N42</f>
         <v>1.5142</v>
       </c>
@@ -4639,24 +7826,12 @@
       <c r="R42" s="65">
         <v>0.82269999999999999</v>
       </c>
-      <c r="S42" s="145">
+      <c r="S42" s="140">
         <f t="shared" ref="S42:S45" si="1">R42/Q42</f>
         <v>0.82269999999999999</v>
       </c>
-      <c r="T42" s="64">
-        <v>1</v>
-      </c>
-      <c r="U42" s="64">
-        <v>1</v>
-      </c>
-      <c r="V42" s="64">
-        <v>1</v>
-      </c>
-      <c r="W42" s="64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23" ht="75">
+    </row>
+    <row r="43" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A43" s="93" t="s">
         <v>182</v>
       </c>
@@ -4700,7 +7875,7 @@
       <c r="O43" s="65">
         <v>1.3431999999999999</v>
       </c>
-      <c r="P43" s="145">
+      <c r="P43" s="140">
         <f t="shared" si="0"/>
         <v>1.3431999999999999</v>
       </c>
@@ -4710,24 +7885,12 @@
       <c r="R43" s="65">
         <v>1.3244</v>
       </c>
-      <c r="S43" s="145">
+      <c r="S43" s="140">
         <f t="shared" si="1"/>
         <v>1.3244</v>
       </c>
-      <c r="T43" s="64">
-        <v>1</v>
-      </c>
-      <c r="U43" s="64">
-        <v>1</v>
-      </c>
-      <c r="V43" s="64">
-        <v>1</v>
-      </c>
-      <c r="W43" s="64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23" ht="75">
+    </row>
+    <row r="44" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A44" s="93" t="s">
         <v>182</v>
       </c>
@@ -4771,7 +7934,7 @@
       <c r="O44" s="65">
         <v>1.6912</v>
       </c>
-      <c r="P44" s="145">
+      <c r="P44" s="140">
         <f t="shared" si="0"/>
         <v>1.6912</v>
       </c>
@@ -4781,24 +7944,12 @@
       <c r="R44" s="65">
         <v>1.1175999999999999</v>
       </c>
-      <c r="S44" s="145">
+      <c r="S44" s="140">
         <f t="shared" si="1"/>
         <v>1.1175999999999999</v>
       </c>
-      <c r="T44" s="64">
-        <v>1</v>
-      </c>
-      <c r="U44" s="64">
-        <v>1</v>
-      </c>
-      <c r="V44" s="64">
-        <v>1</v>
-      </c>
-      <c r="W44" s="64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23" ht="90">
+    </row>
+    <row r="45" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A45" s="93" t="s">
         <v>182</v>
       </c>
@@ -4842,7 +7993,7 @@
       <c r="O45" s="120">
         <v>1.7237</v>
       </c>
-      <c r="P45" s="145">
+      <c r="P45" s="140">
         <f t="shared" si="0"/>
         <v>1.7237</v>
       </c>
@@ -4852,24 +8003,12 @@
       <c r="R45" s="65">
         <v>0.72</v>
       </c>
-      <c r="S45" s="145">
+      <c r="S45" s="140">
         <f t="shared" si="1"/>
         <v>0.72</v>
       </c>
-      <c r="T45" s="64">
-        <v>1</v>
-      </c>
-      <c r="U45" s="64">
-        <v>1</v>
-      </c>
-      <c r="V45" s="64">
-        <v>1</v>
-      </c>
-      <c r="W45" s="64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23" ht="88.8" customHeight="1">
+    </row>
+    <row r="46" spans="1:19" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="93" t="s">
         <v>199</v>
       </c>
@@ -4911,12 +8050,8 @@
       <c r="Q46" s="29"/>
       <c r="R46" s="29"/>
       <c r="S46" s="31"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
-    </row>
-    <row r="47" spans="1:23" ht="130.80000000000001" customHeight="1">
+    </row>
+    <row r="47" spans="1:19" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="80" t="s">
         <v>199</v>
       </c>
@@ -4962,12 +8097,8 @@
       </c>
       <c r="R47" s="19"/>
       <c r="S47" s="23"/>
-      <c r="T47" s="19"/>
-      <c r="U47" s="19"/>
-      <c r="V47" s="19"/>
-      <c r="W47" s="19"/>
-    </row>
-    <row r="48" spans="1:23" ht="132.6" customHeight="1">
+    </row>
+    <row r="48" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="93" t="s">
         <v>199</v>
       </c>
@@ -5025,12 +8156,8 @@
         <f>R48/Q48</f>
         <v>1.1764705882352942</v>
       </c>
-      <c r="T48" s="29"/>
-      <c r="U48" s="29"/>
-      <c r="V48" s="29"/>
-      <c r="W48" s="29"/>
-    </row>
-    <row r="49" spans="1:23" ht="132.6" customHeight="1">
+    </row>
+    <row r="49" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="93" t="s">
         <v>199</v>
       </c>
@@ -5086,12 +8213,8 @@
         <f>R49/Q49</f>
         <v>1.151764705882353</v>
       </c>
-      <c r="T49" s="29"/>
-      <c r="U49" s="29"/>
-      <c r="V49" s="29"/>
-      <c r="W49" s="29"/>
-    </row>
-    <row r="50" spans="1:23" ht="93.6">
+    </row>
+    <row r="50" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A50" s="80" t="s">
         <v>199</v>
       </c>
@@ -5133,12 +8256,8 @@
       <c r="Q50" s="19"/>
       <c r="R50" s="19"/>
       <c r="S50" s="23"/>
-      <c r="T50" s="19"/>
-      <c r="U50" s="19"/>
-      <c r="V50" s="19"/>
-      <c r="W50" s="19"/>
-    </row>
-    <row r="51" spans="1:23" ht="90">
+    </row>
+    <row r="51" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A51" s="80" t="s">
         <v>217</v>
       </c>
@@ -5186,20 +8305,8 @@
       </c>
       <c r="R51" s="21"/>
       <c r="S51" s="22"/>
-      <c r="T51" s="21">
-        <v>1</v>
-      </c>
-      <c r="U51" s="21">
-        <v>1</v>
-      </c>
-      <c r="V51" s="21">
-        <v>1</v>
-      </c>
-      <c r="W51" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:23" ht="78" customHeight="1">
+    </row>
+    <row r="52" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="93" t="s">
         <v>217</v>
       </c>
@@ -5245,20 +8352,8 @@
       </c>
       <c r="R52" s="29"/>
       <c r="S52" s="31"/>
-      <c r="T52" s="29">
-        <v>99</v>
-      </c>
-      <c r="U52" s="29">
-        <v>88</v>
-      </c>
-      <c r="V52" s="29">
-        <v>75</v>
-      </c>
-      <c r="W52" s="29">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="53" spans="1:23" ht="90">
+    </row>
+    <row r="53" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A53" s="80" t="s">
         <v>217</v>
       </c>
@@ -5302,12 +8397,8 @@
       <c r="Q53" s="131"/>
       <c r="R53" s="131"/>
       <c r="S53" s="23"/>
-      <c r="T53" s="131"/>
-      <c r="U53" s="131"/>
-      <c r="V53" s="131"/>
-      <c r="W53" s="131"/>
-    </row>
-    <row r="54" spans="1:23" ht="60">
+    </row>
+    <row r="54" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A54" s="80" t="s">
         <v>217</v>
       </c>
@@ -5353,20 +8444,8 @@
       </c>
       <c r="R54" s="64"/>
       <c r="S54" s="132"/>
-      <c r="T54" s="64">
-        <v>0.8</v>
-      </c>
-      <c r="U54" s="64">
-        <v>0.8</v>
-      </c>
-      <c r="V54" s="64">
-        <v>0.8</v>
-      </c>
-      <c r="W54" s="64">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:23" ht="75">
+    </row>
+    <row r="55" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A55" s="80" t="s">
         <v>217</v>
       </c>
@@ -5410,20 +8489,8 @@
       </c>
       <c r="R55" s="64"/>
       <c r="S55" s="132"/>
-      <c r="T55" s="64">
-        <v>1</v>
-      </c>
-      <c r="U55" s="64">
-        <v>1</v>
-      </c>
-      <c r="V55" s="64">
-        <v>1</v>
-      </c>
-      <c r="W55" s="64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:23" ht="105">
+    </row>
+    <row r="56" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A56" s="80" t="s">
         <v>217</v>
       </c>
@@ -5476,20 +8543,8 @@
       </c>
       <c r="R56" s="19"/>
       <c r="S56" s="23"/>
-      <c r="T56" s="21">
-        <v>0.83</v>
-      </c>
-      <c r="U56" s="21">
-        <v>0.83</v>
-      </c>
-      <c r="V56" s="21">
-        <v>0.84</v>
-      </c>
-      <c r="W56" s="21">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="57" spans="1:23" ht="105">
+    </row>
+    <row r="57" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A57" s="80" t="s">
         <v>217</v>
       </c>
@@ -5529,12 +8584,8 @@
       <c r="Q57" s="19"/>
       <c r="R57" s="19"/>
       <c r="S57" s="23"/>
-      <c r="T57" s="19"/>
-      <c r="U57" s="19"/>
-      <c r="V57" s="19"/>
-      <c r="W57" s="19"/>
-    </row>
-    <row r="58" spans="1:23" ht="75">
+    </row>
+    <row r="58" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A58" s="80" t="s">
         <v>246</v>
       </c>
@@ -5572,12 +8623,8 @@
       <c r="Q58" s="19"/>
       <c r="R58" s="19"/>
       <c r="S58" s="23"/>
-      <c r="T58" s="19"/>
-      <c r="U58" s="19"/>
-      <c r="V58" s="19"/>
-      <c r="W58" s="19"/>
-    </row>
-    <row r="59" spans="1:23" ht="45">
+    </row>
+    <row r="59" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A59" s="80" t="s">
         <v>246</v>
       </c>
@@ -5623,12 +8670,8 @@
       </c>
       <c r="R59" s="19"/>
       <c r="S59" s="23"/>
-      <c r="T59" s="19"/>
-      <c r="U59" s="19"/>
-      <c r="V59" s="19"/>
-      <c r="W59" s="19"/>
-    </row>
-    <row r="60" spans="1:23" ht="109.2">
+    </row>
+    <row r="60" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A60" s="80" t="s">
         <v>246</v>
       </c>
@@ -5684,12 +8727,8 @@
         <f>R60/Q60</f>
         <v>0</v>
       </c>
-      <c r="T60" s="19"/>
-      <c r="U60" s="19"/>
-      <c r="V60" s="19"/>
-      <c r="W60" s="19"/>
-    </row>
-    <row r="61" spans="1:23" ht="109.2">
+    </row>
+    <row r="61" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A61" s="80" t="s">
         <v>246</v>
       </c>
@@ -5733,12 +8772,8 @@
       <c r="Q61" s="19"/>
       <c r="R61" s="19"/>
       <c r="S61" s="23"/>
-      <c r="T61" s="19"/>
-      <c r="U61" s="19"/>
-      <c r="V61" s="19"/>
-      <c r="W61" s="19"/>
-    </row>
-    <row r="62" spans="1:23" ht="124.95" customHeight="1">
+    </row>
+    <row r="62" spans="1:19" ht="124.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="93" t="s">
         <v>246</v>
       </c>
@@ -5780,12 +8815,8 @@
       <c r="Q62" s="29"/>
       <c r="R62" s="29"/>
       <c r="S62" s="31"/>
-      <c r="T62" s="29"/>
-      <c r="U62" s="29"/>
-      <c r="V62" s="29"/>
-      <c r="W62" s="29"/>
-    </row>
-    <row r="63" spans="1:23" ht="109.2">
+    </row>
+    <row r="63" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A63" s="80" t="s">
         <v>246</v>
       </c>
@@ -5827,12 +8858,8 @@
       <c r="Q63" s="19"/>
       <c r="R63" s="19"/>
       <c r="S63" s="23"/>
-      <c r="T63" s="19"/>
-      <c r="U63" s="19"/>
-      <c r="V63" s="19"/>
-      <c r="W63" s="19"/>
-    </row>
-    <row r="64" spans="1:23" ht="75">
+    </row>
+    <row r="64" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A64" s="80" t="s">
         <v>246</v>
       </c>
@@ -5874,12 +8901,8 @@
       <c r="Q64" s="19"/>
       <c r="R64" s="19"/>
       <c r="S64" s="23"/>
-      <c r="T64" s="19"/>
-      <c r="U64" s="19"/>
-      <c r="V64" s="19"/>
-      <c r="W64" s="19"/>
-    </row>
-    <row r="65" spans="1:23" ht="120.6">
+    </row>
+    <row r="65" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A65" s="93" t="s">
         <v>271</v>
       </c>
@@ -5925,12 +8948,8 @@
       <c r="Q65" s="29"/>
       <c r="R65" s="29"/>
       <c r="S65" s="31"/>
-      <c r="T65" s="29"/>
-      <c r="U65" s="29"/>
-      <c r="V65" s="29"/>
-      <c r="W65" s="29"/>
-    </row>
-    <row r="66" spans="1:23" ht="70.95" customHeight="1">
+    </row>
+    <row r="66" spans="1:19" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="93" t="s">
         <v>271</v>
       </c>
@@ -5970,12 +8989,8 @@
       <c r="Q66" s="29"/>
       <c r="R66" s="29"/>
       <c r="S66" s="31"/>
-      <c r="T66" s="29"/>
-      <c r="U66" s="29"/>
-      <c r="V66" s="29"/>
-      <c r="W66" s="29"/>
-    </row>
-    <row r="67" spans="1:23" ht="150">
+    </row>
+    <row r="67" spans="1:19" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A67" s="93" t="s">
         <v>271</v>
       </c>
@@ -6019,12 +9034,8 @@
       <c r="Q67" s="29"/>
       <c r="R67" s="29"/>
       <c r="S67" s="31"/>
-      <c r="T67" s="29"/>
-      <c r="U67" s="29"/>
-      <c r="V67" s="29"/>
-      <c r="W67" s="29"/>
-    </row>
-    <row r="68" spans="1:23" ht="46.8">
+    </row>
+    <row r="68" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A68" s="80" t="s">
         <v>271</v>
       </c>
@@ -6068,17 +9079,11 @@
       <c r="Q68" s="19"/>
       <c r="R68" s="19"/>
       <c r="S68" s="23"/>
-      <c r="T68" s="19"/>
-      <c r="U68" s="19"/>
-      <c r="V68" s="19"/>
-      <c r="W68" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="N1:W1"/>
+  <mergeCells count="2">
+    <mergeCell ref="N1:S1"/>
     <mergeCell ref="L13:L14"/>
-    <mergeCell ref="V13:V14"/>
-    <mergeCell ref="W13:W14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Plan de mejoramiento/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Plan de mejoramiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5377319B-A2AF-4812-861F-3809BA79B2CB}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FF0C608-5A8C-49F2-BFD5-10381659363A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD3A294A-1D13-4C18-8C58-F237245A6723}"/>
   </bookViews>
@@ -162,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="302">
   <si>
     <t>Metas Preliminares</t>
   </si>
@@ -1292,7 +1292,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1452,12 +1452,6 @@
       <sz val="10"/>
       <color rgb="FF002060"/>
       <name val="Inter"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
@@ -2115,6 +2109,9 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2126,9 +2123,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2544,7 +2538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{625CFDA2-DB7B-4B41-9A64-5658BBBE0A38}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:S66"/>
@@ -2553,11 +2547,13 @@
     <col min="1" max="1" width="39.5546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="30.88671875" style="2" customWidth="1"/>
     <col min="3" max="3" width="58.6640625" style="2" customWidth="1"/>
-    <col min="4" max="9" width="34.5546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="23.6640625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="26.44140625" style="2" customWidth="1"/>
+    <col min="4" max="7" width="34.5546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="34.5546875" style="2" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="34.5546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="23.6640625" style="2" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="26.44140625" style="2" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="22.33203125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="27.21875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="27.21875" style="2" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="13.77734375" style="2" customWidth="1"/>
     <col min="15" max="19" width="16.5546875" style="2" customWidth="1"/>
     <col min="20" max="16384" width="11.5546875" style="2"/>
@@ -2577,16 +2573,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="142" t="s">
+      <c r="N1" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="143"/>
-      <c r="P1" s="143"/>
-      <c r="Q1" s="143"/>
-      <c r="R1" s="143"/>
-      <c r="S1" s="143"/>
-    </row>
-    <row r="2" spans="1:19" ht="36" x14ac:dyDescent="0.3">
+      <c r="O1" s="144"/>
+      <c r="P1" s="144"/>
+      <c r="Q1" s="144"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="144"/>
+    </row>
+    <row r="2" spans="1:19" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2626,11 +2622,11 @@
       <c r="M2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>17</v>
+      <c r="N2" s="9">
+        <v>2025</v>
+      </c>
+      <c r="O2" s="11">
+        <v>2026</v>
       </c>
       <c r="P2" s="13">
         <v>2027</v>
@@ -2768,7 +2764,7 @@
       </c>
       <c r="E5" s="17"/>
       <c r="F5" s="17" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="G5" s="27" t="s">
         <v>40</v>
@@ -2811,7 +2807,7 @@
       </c>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="G6" s="27" t="s">
         <v>40</v>
@@ -2921,7 +2917,7 @@
       <c r="R8" s="40"/>
       <c r="S8" s="40"/>
     </row>
-    <row r="9" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A9" s="32" t="s">
         <v>47</v>
       </c>
@@ -3112,7 +3108,7 @@
       <c r="K12" s="63" t="s">
         <v>81</v>
       </c>
-      <c r="L12" s="144" t="s">
+      <c r="L12" s="145" t="s">
         <v>82</v>
       </c>
       <c r="M12" s="59" t="s">
@@ -3169,7 +3165,7 @@
       <c r="K13" s="63" t="s">
         <v>81</v>
       </c>
-      <c r="L13" s="145"/>
+      <c r="L13" s="146"/>
       <c r="M13" s="59" t="s">
         <v>43</v>
       </c>
@@ -3731,7 +3727,7 @@
       <c r="R24" s="19"/>
       <c r="S24" s="19"/>
     </row>
-    <row r="25" spans="1:19" ht="218.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="218.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="79" t="s">
         <v>135</v>
       </c>
@@ -3741,7 +3737,7 @@
       <c r="C25" s="113" t="s">
         <v>137</v>
       </c>
-      <c r="D25" s="146" t="s">
+      <c r="D25" s="142" t="s">
         <v>296</v>
       </c>
       <c r="E25" s="17"/>
@@ -3770,7 +3766,7 @@
       <c r="R25" s="29"/>
       <c r="S25" s="29"/>
     </row>
-    <row r="26" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="79" t="s">
         <v>135</v>
       </c>
@@ -3780,7 +3776,7 @@
       <c r="C26" s="80" t="s">
         <v>137</v>
       </c>
-      <c r="D26" s="146" t="s">
+      <c r="D26" s="142" t="s">
         <v>297</v>
       </c>
       <c r="E26" s="17"/>
@@ -3809,7 +3805,7 @@
       <c r="R26" s="29"/>
       <c r="S26" s="29"/>
     </row>
-    <row r="27" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="79" t="s">
         <v>135</v>
       </c>
@@ -3854,7 +3850,7 @@
       <c r="R27" s="19"/>
       <c r="S27" s="19"/>
     </row>
-    <row r="28" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="79" t="s">
         <v>135</v>
       </c>
@@ -4292,7 +4288,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="80" t="s">
         <v>170</v>
       </c>
@@ -4976,7 +4972,7 @@
       <c r="R49" s="19"/>
       <c r="S49" s="19"/>
     </row>
-    <row r="50" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A50" s="80" t="s">
         <v>217</v>
       </c>
@@ -5088,7 +5084,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="80" t="s">
         <v>217</v>
       </c>
@@ -5143,7 +5139,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="80" t="s">
         <v>217</v>
       </c>
@@ -5253,7 +5249,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="80" t="s">
         <v>217</v>
       </c>
@@ -5429,7 +5425,7 @@
       <c r="R58" s="19"/>
       <c r="S58" s="19"/>
     </row>
-    <row r="59" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="80" t="s">
         <v>246</v>
       </c>
@@ -5474,7 +5470,7 @@
       <c r="R59" s="19"/>
       <c r="S59" s="19"/>
     </row>
-    <row r="60" spans="1:19" ht="124.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" ht="124.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="93" t="s">
         <v>246</v>
       </c>
@@ -5517,7 +5513,7 @@
       <c r="R60" s="29"/>
       <c r="S60" s="29"/>
     </row>
-    <row r="61" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A61" s="80" t="s">
         <v>246</v>
       </c>
@@ -5560,7 +5556,7 @@
       <c r="R61" s="19"/>
       <c r="S61" s="19"/>
     </row>
-    <row r="62" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="80" t="s">
         <v>246</v>
       </c>
@@ -5794,6 +5790,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:S66" xr:uid="{625CFDA2-DB7B-4B41-9A64-5658BBBE0A38}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="Indicador"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="N1:S1"/>
     <mergeCell ref="L12:L13"/>
@@ -5840,14 +5843,14 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="142" t="s">
+      <c r="N1" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="143"/>
-      <c r="P1" s="143"/>
-      <c r="Q1" s="143"/>
-      <c r="R1" s="143"/>
-      <c r="S1" s="143"/>
+      <c r="O1" s="144"/>
+      <c r="P1" s="144"/>
+      <c r="Q1" s="144"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="144"/>
     </row>
     <row r="2" spans="1:19" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -6233,7 +6236,7 @@
       <c r="R9" s="40"/>
       <c r="S9" s="44"/>
     </row>
-    <row r="10" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
         <v>47</v>
       </c>
@@ -6423,7 +6426,7 @@
       <c r="K13" s="63" t="s">
         <v>81</v>
       </c>
-      <c r="L13" s="144" t="s">
+      <c r="L13" s="145" t="s">
         <v>82</v>
       </c>
       <c r="M13" s="59" t="s">
@@ -6479,7 +6482,7 @@
       <c r="K14" s="63" t="s">
         <v>81</v>
       </c>
-      <c r="L14" s="145"/>
+      <c r="L14" s="146"/>
       <c r="M14" s="59" t="s">
         <v>43</v>
       </c>
@@ -8257,7 +8260,7 @@
       <c r="R50" s="19"/>
       <c r="S50" s="23"/>
     </row>
-    <row r="51" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A51" s="80" t="s">
         <v>217</v>
       </c>
@@ -8816,7 +8819,7 @@
       <c r="R62" s="29"/>
       <c r="S62" s="31"/>
     </row>
-    <row r="63" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A63" s="80" t="s">
         <v>246</v>
       </c>

--- a/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Plan de mejoramiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B8F77F7-47C8-4A72-AF5D-C5434F6E0836}"/>
+  <xr:revisionPtr revIDLastSave="190" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2ABD203-B3E0-41B4-9D3C-1E943D1EF392}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{DD3A294A-1D13-4C18-8C58-F237245A6723}"/>
   </bookViews>

--- a/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Plan de mejoramiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="190" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2ABD203-B3E0-41B4-9D3C-1E943D1EF392}"/>
+  <xr:revisionPtr revIDLastSave="192" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00766FF2-CCBF-4417-B367-2373FD6B0CC8}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{DD3A294A-1D13-4C18-8C58-F237245A6723}"/>
   </bookViews>
@@ -2467,7 +2467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{625CFDA2-DB7B-4B41-9A64-5658BBBE0A38}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:S65"/>
@@ -2570,7 +2570,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>20</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>20</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>20</v>
       </c>
@@ -2721,7 +2721,7 @@
       <c r="R5" s="29"/>
       <c r="S5" s="29"/>
     </row>
-    <row r="6" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="69" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>20</v>
       </c>
@@ -2764,7 +2764,7 @@
       <c r="R6" s="29"/>
       <c r="S6" s="29"/>
     </row>
-    <row r="7" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="32" t="s">
         <v>47</v>
       </c>
@@ -2801,7 +2801,7 @@
       <c r="R7" s="40"/>
       <c r="S7" s="40"/>
     </row>
-    <row r="8" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
         <v>47</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="32" t="s">
         <v>47</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
         <v>47</v>
       </c>
@@ -3303,7 +3303,7 @@
       <c r="R17" s="29"/>
       <c r="S17" s="29"/>
     </row>
-    <row r="18" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="79" t="s">
         <v>96</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="79" t="s">
         <v>96</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="79" t="s">
         <v>96</v>
       </c>
@@ -3456,7 +3456,7 @@
       <c r="R20" s="19"/>
       <c r="S20" s="19"/>
     </row>
-    <row r="21" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="79" t="s">
         <v>96</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="79" t="s">
         <v>96</v>
       </c>
@@ -3562,7 +3562,7 @@
       <c r="R22" s="19"/>
       <c r="S22" s="19"/>
     </row>
-    <row r="23" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="79" t="s">
         <v>96</v>
       </c>
@@ -3611,7 +3611,7 @@
       <c r="R23" s="19"/>
       <c r="S23" s="19"/>
     </row>
-    <row r="24" spans="1:19" ht="218.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="218.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="79" t="s">
         <v>130</v>
       </c>
@@ -3650,7 +3650,7 @@
       <c r="R24" s="29"/>
       <c r="S24" s="29"/>
     </row>
-    <row r="25" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="79" t="s">
         <v>130</v>
       </c>
@@ -3689,7 +3689,7 @@
       <c r="R25" s="29"/>
       <c r="S25" s="29"/>
     </row>
-    <row r="26" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="79" t="s">
         <v>130</v>
       </c>
@@ -3734,7 +3734,7 @@
       <c r="R26" s="19"/>
       <c r="S26" s="19"/>
     </row>
-    <row r="27" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="79" t="s">
         <v>130</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="79" t="s">
         <v>130</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="79" t="s">
         <v>130</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33" t="s">
         <v>151</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33" t="s">
         <v>151</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33" t="s">
         <v>151</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33" t="s">
         <v>151</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33" t="s">
         <v>151</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="80" t="s">
         <v>165</v>
       </c>
@@ -4211,7 +4211,7 @@
       <c r="R35" s="19"/>
       <c r="S35" s="19"/>
     </row>
-    <row r="36" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="80" t="s">
         <v>165</v>
       </c>
@@ -4250,7 +4250,7 @@
       <c r="R36" s="19"/>
       <c r="S36" s="19"/>
     </row>
-    <row r="37" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="80" t="s">
         <v>165</v>
       </c>
@@ -4289,7 +4289,7 @@
       <c r="R37" s="19"/>
       <c r="S37" s="19"/>
     </row>
-    <row r="38" spans="1:19" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="46.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="93" t="s">
         <v>177</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="93" t="s">
         <v>177</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="93" t="s">
         <v>177</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="93" t="s">
         <v>177</v>
       </c>
@@ -4519,7 +4519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="93" t="s">
         <v>177</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="93" t="s">
         <v>177</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="88.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="93" t="s">
         <v>194</v>
       </c>
@@ -4674,7 +4674,7 @@
       <c r="R44" s="29"/>
       <c r="S44" s="29"/>
     </row>
-    <row r="45" spans="1:19" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="130.80000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="80" t="s">
         <v>194</v>
       </c>
@@ -4719,7 +4719,7 @@
       <c r="R45" s="19"/>
       <c r="S45" s="19"/>
     </row>
-    <row r="46" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="132.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="93" t="s">
         <v>194</v>
       </c>
@@ -4768,7 +4768,7 @@
       <c r="R46" s="29"/>
       <c r="S46" s="29"/>
     </row>
-    <row r="47" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="132.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="93" t="s">
         <v>194</v>
       </c>
@@ -4815,7 +4815,7 @@
       <c r="R47" s="29"/>
       <c r="S47" s="29"/>
     </row>
-    <row r="48" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="80" t="s">
         <v>194</v>
       </c>
@@ -4856,7 +4856,7 @@
       <c r="R48" s="19"/>
       <c r="S48" s="19"/>
     </row>
-    <row r="49" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="80" t="s">
         <v>212</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="93" t="s">
         <v>212</v>
       </c>
@@ -4968,7 +4968,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="80" t="s">
         <v>212</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="80" t="s">
         <v>212</v>
       </c>
@@ -5076,7 +5076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="80" t="s">
         <v>212</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="80" t="s">
         <v>212</v>
       </c>
@@ -5174,7 +5174,7 @@
       <c r="R54" s="19"/>
       <c r="S54" s="19"/>
     </row>
-    <row r="55" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="80" t="s">
         <v>241</v>
       </c>
@@ -5213,7 +5213,7 @@
       <c r="R55" s="19"/>
       <c r="S55" s="19"/>
     </row>
-    <row r="56" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="80" t="s">
         <v>241</v>
       </c>
@@ -5260,7 +5260,7 @@
       <c r="R56" s="19"/>
       <c r="S56" s="19"/>
     </row>
-    <row r="57" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="80" t="s">
         <v>241</v>
       </c>
@@ -5309,7 +5309,7 @@
       <c r="R57" s="19"/>
       <c r="S57" s="19"/>
     </row>
-    <row r="58" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="80" t="s">
         <v>241</v>
       </c>
@@ -5354,7 +5354,7 @@
       <c r="R58" s="19"/>
       <c r="S58" s="19"/>
     </row>
-    <row r="59" spans="1:19" ht="124.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" ht="124.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="93" t="s">
         <v>241</v>
       </c>
@@ -5397,7 +5397,7 @@
       <c r="R59" s="29"/>
       <c r="S59" s="29"/>
     </row>
-    <row r="60" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="80" t="s">
         <v>241</v>
       </c>
@@ -5440,7 +5440,7 @@
       <c r="R60" s="19"/>
       <c r="S60" s="19"/>
     </row>
-    <row r="61" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="80" t="s">
         <v>241</v>
       </c>
@@ -5483,7 +5483,7 @@
       <c r="R61" s="19"/>
       <c r="S61" s="19"/>
     </row>
-    <row r="62" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="93" t="s">
         <v>266</v>
       </c>
@@ -5530,7 +5530,7 @@
       <c r="R62" s="29"/>
       <c r="S62" s="29"/>
     </row>
-    <row r="63" spans="1:19" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" ht="70.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="93" t="s">
         <v>266</v>
       </c>
@@ -5571,7 +5571,7 @@
       <c r="R63" s="29"/>
       <c r="S63" s="29"/>
     </row>
-    <row r="64" spans="1:19" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" ht="171.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="93" t="s">
         <v>266</v>
       </c>
@@ -5616,7 +5616,7 @@
       <c r="R64" s="29"/>
       <c r="S64" s="29"/>
     </row>
-    <row r="65" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="80" t="s">
         <v>266</v>
       </c>
@@ -5674,6 +5674,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:S65" xr:uid="{625CFDA2-DB7B-4B41-9A64-5658BBBE0A38}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Factor 3. Desarrollo, gestión y sostenibilidad institucional"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="N1:S1"/>
     <mergeCell ref="L11:L12"/>

--- a/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Plan de mejoramiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="192" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00766FF2-CCBF-4417-B367-2373FD6B0CC8}"/>
+  <xr:revisionPtr revIDLastSave="195" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12E2FFCC-8BAC-41FD-8C38-3782273B452B}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{DD3A294A-1D13-4C18-8C58-F237245A6723}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD3A294A-1D13-4C18-8C58-F237245A6723}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores Plan de Mejor" sheetId="1" r:id="rId1"/>
@@ -2467,7 +2467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{625CFDA2-DB7B-4B41-9A64-5658BBBE0A38}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:S65"/>
@@ -2570,7 +2570,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>20</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>20</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>20</v>
       </c>
@@ -2721,7 +2721,7 @@
       <c r="R5" s="29"/>
       <c r="S5" s="29"/>
     </row>
-    <row r="6" spans="1:19" ht="69" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>20</v>
       </c>
@@ -2764,7 +2764,7 @@
       <c r="R6" s="29"/>
       <c r="S6" s="29"/>
     </row>
-    <row r="7" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A7" s="32" t="s">
         <v>47</v>
       </c>
@@ -2801,7 +2801,7 @@
       <c r="R7" s="40"/>
       <c r="S7" s="40"/>
     </row>
-    <row r="8" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
         <v>47</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A9" s="32" t="s">
         <v>47</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
         <v>47</v>
       </c>
@@ -3303,7 +3303,7 @@
       <c r="R17" s="29"/>
       <c r="S17" s="29"/>
     </row>
-    <row r="18" spans="1:19" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A18" s="79" t="s">
         <v>96</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A19" s="79" t="s">
         <v>96</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A20" s="79" t="s">
         <v>96</v>
       </c>
@@ -3456,7 +3456,7 @@
       <c r="R20" s="19"/>
       <c r="S20" s="19"/>
     </row>
-    <row r="21" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A21" s="79" t="s">
         <v>96</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A22" s="79" t="s">
         <v>96</v>
       </c>
@@ -3562,7 +3562,7 @@
       <c r="R22" s="19"/>
       <c r="S22" s="19"/>
     </row>
-    <row r="23" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A23" s="79" t="s">
         <v>96</v>
       </c>
@@ -3611,7 +3611,7 @@
       <c r="R23" s="19"/>
       <c r="S23" s="19"/>
     </row>
-    <row r="24" spans="1:19" ht="218.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="218.4" x14ac:dyDescent="0.3">
       <c r="A24" s="79" t="s">
         <v>130</v>
       </c>
@@ -3650,7 +3650,7 @@
       <c r="R24" s="29"/>
       <c r="S24" s="29"/>
     </row>
-    <row r="25" spans="1:19" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A25" s="79" t="s">
         <v>130</v>
       </c>
@@ -3689,7 +3689,7 @@
       <c r="R25" s="29"/>
       <c r="S25" s="29"/>
     </row>
-    <row r="26" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A26" s="79" t="s">
         <v>130</v>
       </c>
@@ -3734,7 +3734,7 @@
       <c r="R26" s="19"/>
       <c r="S26" s="19"/>
     </row>
-    <row r="27" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A27" s="79" t="s">
         <v>130</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A28" s="79" t="s">
         <v>130</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A29" s="79" t="s">
         <v>130</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A30" s="33" t="s">
         <v>151</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A31" s="33" t="s">
         <v>151</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A32" s="33" t="s">
         <v>151</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A33" s="33" t="s">
         <v>151</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A34" s="33" t="s">
         <v>151</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A35" s="80" t="s">
         <v>165</v>
       </c>
@@ -4211,7 +4211,7 @@
       <c r="R35" s="19"/>
       <c r="S35" s="19"/>
     </row>
-    <row r="36" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A36" s="80" t="s">
         <v>165</v>
       </c>
@@ -4250,7 +4250,7 @@
       <c r="R36" s="19"/>
       <c r="S36" s="19"/>
     </row>
-    <row r="37" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A37" s="80" t="s">
         <v>165</v>
       </c>
@@ -4289,7 +4289,7 @@
       <c r="R37" s="19"/>
       <c r="S37" s="19"/>
     </row>
-    <row r="38" spans="1:19" ht="46.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="93" t="s">
         <v>177</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A39" s="93" t="s">
         <v>177</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A40" s="93" t="s">
         <v>177</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A41" s="93" t="s">
         <v>177</v>
       </c>
@@ -4519,7 +4519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A42" s="93" t="s">
         <v>177</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A43" s="93" t="s">
         <v>177</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="88.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="93" t="s">
         <v>194</v>
       </c>
@@ -4674,7 +4674,7 @@
       <c r="R44" s="29"/>
       <c r="S44" s="29"/>
     </row>
-    <row r="45" spans="1:19" ht="130.80000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="80" t="s">
         <v>194</v>
       </c>
@@ -4719,7 +4719,7 @@
       <c r="R45" s="19"/>
       <c r="S45" s="19"/>
     </row>
-    <row r="46" spans="1:19" ht="132.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="93" t="s">
         <v>194</v>
       </c>
@@ -4768,7 +4768,7 @@
       <c r="R46" s="29"/>
       <c r="S46" s="29"/>
     </row>
-    <row r="47" spans="1:19" ht="132.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="93" t="s">
         <v>194</v>
       </c>
@@ -4815,7 +4815,7 @@
       <c r="R47" s="29"/>
       <c r="S47" s="29"/>
     </row>
-    <row r="48" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A48" s="80" t="s">
         <v>194</v>
       </c>
@@ -4856,7 +4856,7 @@
       <c r="R48" s="19"/>
       <c r="S48" s="19"/>
     </row>
-    <row r="49" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A49" s="80" t="s">
         <v>212</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="93" t="s">
         <v>212</v>
       </c>
@@ -4968,7 +4968,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A51" s="80" t="s">
         <v>212</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A52" s="80" t="s">
         <v>212</v>
       </c>
@@ -5076,7 +5076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A53" s="80" t="s">
         <v>212</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A54" s="80" t="s">
         <v>212</v>
       </c>
@@ -5174,7 +5174,7 @@
       <c r="R54" s="19"/>
       <c r="S54" s="19"/>
     </row>
-    <row r="55" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A55" s="80" t="s">
         <v>241</v>
       </c>
@@ -5213,7 +5213,7 @@
       <c r="R55" s="19"/>
       <c r="S55" s="19"/>
     </row>
-    <row r="56" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A56" s="80" t="s">
         <v>241</v>
       </c>
@@ -5260,7 +5260,7 @@
       <c r="R56" s="19"/>
       <c r="S56" s="19"/>
     </row>
-    <row r="57" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A57" s="80" t="s">
         <v>241</v>
       </c>
@@ -5309,7 +5309,7 @@
       <c r="R57" s="19"/>
       <c r="S57" s="19"/>
     </row>
-    <row r="58" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A58" s="80" t="s">
         <v>241</v>
       </c>
@@ -5354,7 +5354,7 @@
       <c r="R58" s="19"/>
       <c r="S58" s="19"/>
     </row>
-    <row r="59" spans="1:19" ht="124.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" ht="124.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="93" t="s">
         <v>241</v>
       </c>
@@ -5397,7 +5397,7 @@
       <c r="R59" s="29"/>
       <c r="S59" s="29"/>
     </row>
-    <row r="60" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A60" s="80" t="s">
         <v>241</v>
       </c>
@@ -5440,7 +5440,7 @@
       <c r="R60" s="19"/>
       <c r="S60" s="19"/>
     </row>
-    <row r="61" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A61" s="80" t="s">
         <v>241</v>
       </c>
@@ -5483,7 +5483,7 @@
       <c r="R61" s="19"/>
       <c r="S61" s="19"/>
     </row>
-    <row r="62" spans="1:19" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A62" s="93" t="s">
         <v>266</v>
       </c>
@@ -5530,7 +5530,7 @@
       <c r="R62" s="29"/>
       <c r="S62" s="29"/>
     </row>
-    <row r="63" spans="1:19" ht="70.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="93" t="s">
         <v>266</v>
       </c>
@@ -5571,7 +5571,7 @@
       <c r="R63" s="29"/>
       <c r="S63" s="29"/>
     </row>
-    <row r="64" spans="1:19" ht="171.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A64" s="93" t="s">
         <v>266</v>
       </c>
@@ -5616,7 +5616,7 @@
       <c r="R64" s="29"/>
       <c r="S64" s="29"/>
     </row>
-    <row r="65" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A65" s="80" t="s">
         <v>266</v>
       </c>
@@ -5674,13 +5674,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S65" xr:uid="{625CFDA2-DB7B-4B41-9A64-5658BBBE0A38}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Factor 3. Desarrollo, gestión y sostenibilidad institucional"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="N1:S1"/>
     <mergeCell ref="L11:L12"/>

--- a/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Plan de mejoramiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="195" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12E2FFCC-8BAC-41FD-8C38-3782273B452B}"/>
+  <xr:revisionPtr revIDLastSave="234" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{101BC4DD-D44C-4670-9E45-911E0D24584E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD3A294A-1D13-4C18-8C58-F237245A6723}"/>
   </bookViews>
@@ -81,6 +81,7 @@
     <author>tc={3F85CAB4-6021-44EC-B795-E932C183C912}</author>
     <author>tc={242351BE-3094-4A32-A1BB-45F00F8A6CDF}</author>
     <author>tc={89AA3457-36D7-4CDB-AC41-C208171F6214}</author>
+    <author>tc={E581DAFC-44AD-42D5-8849-003A27C98076}</author>
   </authors>
   <commentList>
     <comment ref="N7" authorId="0" shapeId="0" xr:uid="{FA05611A-1D16-4452-B93C-2E4DFFD86645}">
@@ -137,12 +138,22 @@
 Resultado General: 97.9% </t>
       </text>
     </comment>
+    <comment ref="N64" authorId="4" shapeId="0" xr:uid="{E581DAFC-44AD-42D5-8849-003A27C98076}">
+      <text>
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    M0:  90% tasa de respuesta
+M1: 9% tasa de respuesta
+M5: 3,5% tasa de respuesta</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="297">
   <si>
     <t>Metas Preliminares</t>
   </si>
@@ -1235,7 +1246,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1402,6 +1413,12 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Inter"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1629,7 +1646,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2066,6 +2083,12 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2462,6 +2485,11 @@
 Nivel de satisfacción Graduado: 100%
 Resultado General: 97.9% </text>
   </threadedComment>
+  <threadedComment ref="N64" dT="2026-09-21T08:25:44.93" personId="{4069C3FC-DE77-490E-9BCA-D060BF504FA7}" id="{E581DAFC-44AD-42D5-8849-003A27C98076}">
+    <text>M0:  90% tasa de respuesta
+M1: 9% tasa de respuesta
+M5: 3,5% tasa de respuesta</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -5433,7 +5461,9 @@
         <v>254</v>
       </c>
       <c r="M60" s="136"/>
-      <c r="N60" s="66"/>
+      <c r="N60" s="19">
+        <v>74.8</v>
+      </c>
       <c r="O60" s="19"/>
       <c r="P60" s="19"/>
       <c r="Q60" s="19"/>
@@ -5524,11 +5554,21 @@
       <c r="N62" s="138" t="s">
         <v>272</v>
       </c>
-      <c r="O62" s="29"/>
-      <c r="P62" s="29"/>
-      <c r="Q62" s="29"/>
-      <c r="R62" s="29"/>
-      <c r="S62" s="29"/>
+      <c r="O62" s="122">
+        <v>1</v>
+      </c>
+      <c r="P62" s="122">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="122">
+        <v>1</v>
+      </c>
+      <c r="R62" s="122">
+        <v>1</v>
+      </c>
+      <c r="S62" s="122">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:19" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="93" t="s">
@@ -5610,7 +5650,9 @@
       </c>
       <c r="M64" s="94"/>
       <c r="N64" s="63"/>
-      <c r="O64" s="29"/>
+      <c r="O64" s="122">
+        <v>0.09</v>
+      </c>
       <c r="P64" s="29"/>
       <c r="Q64" s="29"/>
       <c r="R64" s="29"/>
@@ -5664,10 +5706,10 @@
         <v>0.85</v>
       </c>
       <c r="Q65" s="64">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="R65" s="64">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="S65" s="64">
         <v>0.87</v>
@@ -5686,7 +5728,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C65FC67-03C0-423A-92BB-67DDC6589F1C}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:S67"/>
@@ -5788,7 +5830,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>20</v>
       </c>
@@ -5844,7 +5886,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>20</v>
       </c>
@@ -5893,7 +5935,7 @@
       <c r="R4" s="21"/>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>20</v>
       </c>
@@ -5936,7 +5978,7 @@
       <c r="R5" s="29"/>
       <c r="S5" s="31"/>
     </row>
-    <row r="6" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="69" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>20</v>
       </c>
@@ -5979,7 +6021,7 @@
       <c r="R6" s="29"/>
       <c r="S6" s="31"/>
     </row>
-    <row r="7" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="32" t="s">
         <v>47</v>
       </c>
@@ -6029,7 +6071,7 @@
       <c r="R7" s="40"/>
       <c r="S7" s="44"/>
     </row>
-    <row r="8" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
         <v>47</v>
       </c>
@@ -6066,7 +6108,7 @@
       <c r="R8" s="40"/>
       <c r="S8" s="44"/>
     </row>
-    <row r="9" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="32" t="s">
         <v>47</v>
       </c>
@@ -6125,7 +6167,7 @@
         <v>1.0608333333333333</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
         <v>47</v>
       </c>
@@ -6177,7 +6219,7 @@
       <c r="R10" s="40"/>
       <c r="S10" s="44"/>
     </row>
-    <row r="11" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="32" t="s">
         <v>47</v>
       </c>
@@ -6224,7 +6266,7 @@
       <c r="R11" s="40"/>
       <c r="S11" s="44"/>
     </row>
-    <row r="12" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="56" t="s">
         <v>71</v>
       </c>
@@ -6280,7 +6322,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="56" t="s">
         <v>71</v>
       </c>
@@ -6325,7 +6367,7 @@
       <c r="R13" s="19"/>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="56" t="s">
         <v>71</v>
       </c>
@@ -6370,7 +6412,7 @@
       <c r="R14" s="68"/>
       <c r="S14" s="69"/>
     </row>
-    <row r="15" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="56" t="s">
         <v>71</v>
       </c>
@@ -6413,7 +6455,7 @@
       <c r="R15" s="19"/>
       <c r="S15" s="23"/>
     </row>
-    <row r="16" spans="1:19" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="56" t="s">
         <v>71</v>
       </c>
@@ -6454,7 +6496,7 @@
       <c r="R16" s="19"/>
       <c r="S16" s="23"/>
     </row>
-    <row r="17" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="56" t="s">
         <v>71</v>
       </c>
@@ -6491,7 +6533,7 @@
       <c r="R17" s="19"/>
       <c r="S17" s="23"/>
     </row>
-    <row r="18" spans="1:19" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="56" t="s">
         <v>71</v>
       </c>
@@ -6532,7 +6574,7 @@
       <c r="R18" s="29"/>
       <c r="S18" s="31"/>
     </row>
-    <row r="19" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="79" t="s">
         <v>96</v>
       </c>
@@ -6575,7 +6617,7 @@
       <c r="R19" s="19"/>
       <c r="S19" s="23"/>
     </row>
-    <row r="20" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="79" t="s">
         <v>96</v>
       </c>
@@ -6622,7 +6664,7 @@
       <c r="R20" s="21"/>
       <c r="S20" s="22"/>
     </row>
-    <row r="21" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="79" t="s">
         <v>96</v>
       </c>
@@ -6667,7 +6709,7 @@
       <c r="R21" s="19"/>
       <c r="S21" s="23"/>
     </row>
-    <row r="22" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="79" t="s">
         <v>96</v>
       </c>
@@ -6765,7 +6807,7 @@
       <c r="R23" s="19"/>
       <c r="S23" s="23"/>
     </row>
-    <row r="24" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="79" t="s">
         <v>96</v>
       </c>
@@ -6817,7 +6859,7 @@
       <c r="R24" s="19"/>
       <c r="S24" s="23"/>
     </row>
-    <row r="25" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="79" t="s">
         <v>96</v>
       </c>
@@ -6876,7 +6918,7 @@
         <v>0.99356223175965663</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="57" t="s">
         <v>130</v>
       </c>
@@ -6915,7 +6957,7 @@
       <c r="R26" s="29"/>
       <c r="S26" s="31"/>
     </row>
-    <row r="27" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="79" t="s">
         <v>130</v>
       </c>
@@ -6960,7 +7002,7 @@
       <c r="R27" s="19"/>
       <c r="S27" s="23"/>
     </row>
-    <row r="28" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="79" t="s">
         <v>130</v>
       </c>
@@ -7005,7 +7047,7 @@
       <c r="R28" s="19"/>
       <c r="S28" s="23"/>
     </row>
-    <row r="29" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="79" t="s">
         <v>130</v>
       </c>
@@ -7060,7 +7102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="79" t="s">
         <v>130</v>
       </c>
@@ -7117,7 +7159,7 @@
         <v>0.14285714285714285</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33" t="s">
         <v>151</v>
       </c>
@@ -7178,7 +7220,7 @@
         <v>1.02125</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33" t="s">
         <v>151</v>
       </c>
@@ -7225,7 +7267,7 @@
       <c r="R32" s="40"/>
       <c r="S32" s="44"/>
     </row>
-    <row r="33" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33" t="s">
         <v>151</v>
       </c>
@@ -7274,7 +7316,7 @@
       <c r="R33" s="40"/>
       <c r="S33" s="44"/>
     </row>
-    <row r="34" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33" t="s">
         <v>151</v>
       </c>
@@ -7321,7 +7363,7 @@
       <c r="R34" s="108"/>
       <c r="S34" s="109"/>
     </row>
-    <row r="35" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33" t="s">
         <v>151</v>
       </c>
@@ -7370,7 +7412,7 @@
       <c r="R35" s="40"/>
       <c r="S35" s="44"/>
     </row>
-    <row r="36" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="80" t="s">
         <v>165</v>
       </c>
@@ -7409,7 +7451,7 @@
       <c r="R36" s="19"/>
       <c r="S36" s="23"/>
     </row>
-    <row r="37" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="80" t="s">
         <v>165</v>
       </c>
@@ -7448,7 +7490,7 @@
       <c r="R37" s="19"/>
       <c r="S37" s="23"/>
     </row>
-    <row r="38" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="80" t="s">
         <v>165</v>
       </c>
@@ -7487,7 +7529,7 @@
       <c r="R38" s="19"/>
       <c r="S38" s="23"/>
     </row>
-    <row r="39" spans="1:19" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="46.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="93" t="s">
         <v>177</v>
       </c>
@@ -7546,7 +7588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="93" t="s">
         <v>177</v>
       </c>
@@ -7605,7 +7647,7 @@
         <v>1.099</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="93" t="s">
         <v>177</v>
       </c>
@@ -7664,7 +7706,7 @@
         <v>0.82269999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="93" t="s">
         <v>177</v>
       </c>
@@ -7723,7 +7765,7 @@
         <v>1.3244</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="93" t="s">
         <v>177</v>
       </c>
@@ -7782,7 +7824,7 @@
         <v>1.1175999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="93" t="s">
         <v>177</v>
       </c>
@@ -7841,7 +7883,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="88.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="93" t="s">
         <v>194</v>
       </c>
@@ -7884,7 +7926,7 @@
       <c r="R45" s="29"/>
       <c r="S45" s="31"/>
     </row>
-    <row r="46" spans="1:19" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="130.80000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="80" t="s">
         <v>194</v>
       </c>
@@ -7931,7 +7973,7 @@
       <c r="R46" s="19"/>
       <c r="S46" s="23"/>
     </row>
-    <row r="47" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="132.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="93" t="s">
         <v>194</v>
       </c>
@@ -7990,7 +8032,7 @@
         <v>1.1764705882352942</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="132.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="93" t="s">
         <v>194</v>
       </c>
@@ -8047,7 +8089,7 @@
         <v>1.151764705882353</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="80" t="s">
         <v>194</v>
       </c>
@@ -8090,7 +8132,7 @@
       <c r="R49" s="19"/>
       <c r="S49" s="23"/>
     </row>
-    <row r="50" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="80" t="s">
         <v>212</v>
       </c>
@@ -8139,7 +8181,7 @@
       <c r="R50" s="21"/>
       <c r="S50" s="22"/>
     </row>
-    <row r="51" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="93" t="s">
         <v>212</v>
       </c>
@@ -8186,7 +8228,7 @@
       <c r="R51" s="29"/>
       <c r="S51" s="31"/>
     </row>
-    <row r="52" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="80" t="s">
         <v>212</v>
       </c>
@@ -8231,7 +8273,7 @@
       <c r="R52" s="131"/>
       <c r="S52" s="23"/>
     </row>
-    <row r="53" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="80" t="s">
         <v>212</v>
       </c>
@@ -8278,7 +8320,7 @@
       <c r="R53" s="64"/>
       <c r="S53" s="132"/>
     </row>
-    <row r="54" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="80" t="s">
         <v>212</v>
       </c>
@@ -8323,7 +8365,7 @@
       <c r="R54" s="64"/>
       <c r="S54" s="132"/>
     </row>
-    <row r="55" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="80" t="s">
         <v>212</v>
       </c>
@@ -8377,7 +8419,7 @@
       <c r="R55" s="19"/>
       <c r="S55" s="23"/>
     </row>
-    <row r="56" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="80" t="s">
         <v>212</v>
       </c>
@@ -8418,7 +8460,7 @@
       <c r="R56" s="19"/>
       <c r="S56" s="23"/>
     </row>
-    <row r="57" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="80" t="s">
         <v>241</v>
       </c>
@@ -8457,7 +8499,7 @@
       <c r="R57" s="19"/>
       <c r="S57" s="23"/>
     </row>
-    <row r="58" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="80" t="s">
         <v>241</v>
       </c>
@@ -8561,7 +8603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="80" t="s">
         <v>241</v>
       </c>
@@ -8606,7 +8648,7 @@
       <c r="R60" s="19"/>
       <c r="S60" s="23"/>
     </row>
-    <row r="61" spans="1:19" ht="124.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" ht="124.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="93" t="s">
         <v>241</v>
       </c>
@@ -8685,14 +8727,23 @@
         <v>254</v>
       </c>
       <c r="M62" s="136"/>
-      <c r="N62" s="66"/>
-      <c r="O62" s="66"/>
-      <c r="P62" s="76"/>
-      <c r="Q62" s="19"/>
+      <c r="N62" s="66">
+        <v>74.2</v>
+      </c>
+      <c r="O62" s="66">
+        <v>77.400000000000006</v>
+      </c>
+      <c r="P62" s="133">
+        <f>O62/N62</f>
+        <v>1.0431266846361187</v>
+      </c>
+      <c r="Q62" s="19">
+        <v>74.8</v>
+      </c>
       <c r="R62" s="19"/>
       <c r="S62" s="23"/>
     </row>
-    <row r="63" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="80" t="s">
         <v>241</v>
       </c>
@@ -8735,7 +8786,7 @@
       <c r="R63" s="19"/>
       <c r="S63" s="23"/>
     </row>
-    <row r="64" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="93" t="s">
         <v>266</v>
       </c>
@@ -8773,16 +8824,23 @@
         <v>271</v>
       </c>
       <c r="M64" s="94"/>
-      <c r="N64" s="138" t="s">
-        <v>272</v>
-      </c>
-      <c r="O64" s="63"/>
-      <c r="P64" s="96"/>
-      <c r="Q64" s="29"/>
+      <c r="N64" s="147">
+        <v>1</v>
+      </c>
+      <c r="O64" s="141">
+        <v>1.1357999999999999</v>
+      </c>
+      <c r="P64" s="148">
+        <f>O64/N64</f>
+        <v>1.1357999999999999</v>
+      </c>
+      <c r="Q64" s="122">
+        <v>1</v>
+      </c>
       <c r="R64" s="29"/>
       <c r="S64" s="31"/>
     </row>
-    <row r="65" spans="1:19" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" ht="70.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="93" t="s">
         <v>266</v>
       </c>
@@ -8817,13 +8875,15 @@
         <v>50</v>
       </c>
       <c r="N65" s="63"/>
-      <c r="O65" s="63"/>
+      <c r="O65" s="63">
+        <v>81.239999999999995</v>
+      </c>
       <c r="P65" s="96"/>
       <c r="Q65" s="29"/>
       <c r="R65" s="29"/>
       <c r="S65" s="31"/>
     </row>
-    <row r="66" spans="1:19" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" ht="171.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="93" t="s">
         <v>266</v>
       </c>
@@ -8861,14 +8921,23 @@
         <v>271</v>
       </c>
       <c r="M66" s="94"/>
-      <c r="N66" s="63"/>
-      <c r="O66" s="63"/>
-      <c r="P66" s="96"/>
-      <c r="Q66" s="29"/>
+      <c r="N66" s="120">
+        <v>0.04</v>
+      </c>
+      <c r="O66" s="141">
+        <v>6.9900000000000004E-2</v>
+      </c>
+      <c r="P66" s="148">
+        <f>O66/N66</f>
+        <v>1.7475000000000001</v>
+      </c>
+      <c r="Q66" s="122">
+        <v>0.09</v>
+      </c>
       <c r="R66" s="29"/>
       <c r="S66" s="31"/>
     </row>
-    <row r="67" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="80" t="s">
         <v>266</v>
       </c>
@@ -8914,7 +8983,15 @@
       <c r="S67" s="23"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S67" xr:uid="{2C65FC67-03C0-423A-92BB-67DDC6589F1C}"/>
+  <autoFilter ref="A2:S67" xr:uid="{2C65FC67-03C0-423A-92BB-67DDC6589F1C}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="% Permanencia intersemestral"/>
+        <filter val="% Permanencia intersemestral Ingresantes"/>
+        <filter val="Nùmero participantes en  Procesos formación permanente desarrollados desde el SIAC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="N1:S1"/>
     <mergeCell ref="L12:L13"/>

--- a/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Plan de mejoramiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="234" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{101BC4DD-D44C-4670-9E45-911E0D24584E}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{597DF08B-EB46-4890-8BF0-4E22C3D79E09}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD3A294A-1D13-4C18-8C58-F237245A6723}"/>
   </bookViews>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="323">
   <si>
     <t>Metas Preliminares</t>
   </si>
@@ -1126,9 +1126,6 @@
     <t>N de convenios con actividades en los ultimos 5 años / Total convenios</t>
   </si>
   <si>
-    <t>% inversion misionales de la institución</t>
-  </si>
-  <si>
     <t>Efectividad de las acciones derivadas de las oportunidades de mejora</t>
   </si>
   <si>
@@ -1154,11 +1151,142 @@
     </r>
   </si>
   <si>
-    <t>Número de programas con reforma curricular</t>
+    <t>Valor agregado en la pruebas Saber Pro Institucional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nivel de Satisfacción del graduado con la institución </t>
+  </si>
+  <si>
+    <t>Apropiación del modelo de gestión, evaluación e innovación curricular</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Sesion para identificar medición con Maria Isabel y Maria del Socorro
+      <t xml:space="preserve">Sesión con Diana
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Inter"/>
+        <family val="2"/>
+      </rPr>
+      <t>se propone indicador asociado con la apropiación del modelo de gestión, evaluación e innovación curricular</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF002060"/>
+        <rFont val="Inter"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Inter"/>
+        <family val="2"/>
+      </rPr>
+      <t>28 septiembre</t>
+    </r>
+  </si>
+  <si>
+    <t>Dirección de currículo</t>
+  </si>
+  <si>
+    <t>Propuesta de reemplazar con métrica, pero esta no mide resultado o impacto 
+Se propone utilizar fuentes oficiales del Icfes</t>
+  </si>
+  <si>
+    <t>Se valida con investigación y esta información se reporta completa en ADA y Boletín</t>
+  </si>
+  <si>
+    <t>Validar con vicerrectoría académica y del estudiante</t>
+  </si>
+  <si>
+    <t>Validar  Indicadores porque se debe medir el impacto a otros grupos de interés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participación ingresos por extensión (Consultorías, alquiler de espacios, prestación de servicios, centros de investigación entre otros) / total ingresos </t>
+  </si>
+  <si>
+    <t>N de convenios con actividades en los últimos 5 años / Total convenios</t>
+  </si>
+  <si>
+    <t>N° Estudiantes  externos invitados a actividades de cooperación Nacional e internacional de Bogotá y virtual</t>
+  </si>
+  <si>
+    <t>Índice de impacto Psicosocial de las actividades de bienestar</t>
+  </si>
+  <si>
+    <t>Proporción de profesores con nivel de formación (Maestría y Doctorado)</t>
+  </si>
+  <si>
+    <t>Métrica</t>
+  </si>
+  <si>
+    <t>Gestión docente informa que son métricas no indicadores</t>
+  </si>
+  <si>
+    <t>(N° de profesores con maestría y doctorado / N° total de profesores)*100</t>
+  </si>
+  <si>
+    <t>N° de cupos aprobados para el escalafón docente</t>
+  </si>
+  <si>
+    <t>(N° de profesores con escalafón docente/N° de cupos aprobados para el escalafón docente)*100</t>
+  </si>
+  <si>
+    <t>Tasa de empleabilidad de recién graduados de pregrado</t>
+  </si>
+  <si>
+    <t>Propuesta de limitar la línea base de los últimos 5 años</t>
+  </si>
+  <si>
+    <t>Resultado de satisfacción de graduados</t>
+  </si>
+  <si>
+    <t>Indicador o Métrica</t>
+  </si>
+  <si>
+    <t>Validar con Vicerrectoría académica y del estudiante</t>
+  </si>
+  <si>
+    <t>Centro de Psicología</t>
+  </si>
+  <si>
+    <t>Nivel de conocimiento de los grupos de interés  del informe de sostenibilidad</t>
+  </si>
+  <si>
+    <t>% inversión misionales de la institución</t>
+  </si>
+  <si>
+    <t>Inversión al plan de mejoramiento</t>
+  </si>
+  <si>
+    <t>Infraestructura Física
+Infra estructura Tecnológica
+Contenidos Virtuales
+Biblioteca CMA
+Fortalecimiento Docencia
+Inversiones Misionales
+Inversiones en bienestar</t>
+  </si>
+  <si>
+    <t>(N° de oportunidades de mejora cerradas derivadas de los ejercicios de autoevaluación/ N° de oportunidades de mejora definidas en el periodo)</t>
+  </si>
+  <si>
+    <t>(N.º de programas acreditados / Total de programas ofertados) * 100</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sesión para identificar medición con Maria Isabel y Maria del Socorro
 </t>
     </r>
     <r>
@@ -1193,49 +1321,6 @@
       <t>28 septiembre</t>
     </r>
   </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sesion con Diana
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Inter"/>
-        <family val="2"/>
-      </rPr>
-      <t>se propone indicador asociado con la apropiación del modelo de gestión, evaluación e innovación curricular</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF002060"/>
-        <rFont val="Inter"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Inter"/>
-        <family val="2"/>
-      </rPr>
-      <t>28 septiembre</t>
-    </r>
-  </si>
-  <si>
-    <t>Dirección de curriculo</t>
-  </si>
-  <si>
-    <t>Valor agregado en la pruebas Saber Pro Institucional</t>
-  </si>
 </sst>
 </file>
 
@@ -1246,7 +1331,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1413,12 +1498,6 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Inter"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -2072,6 +2151,12 @@
     <xf numFmtId="0" fontId="10" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2083,12 +2168,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2530,14 +2609,14 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="143" t="s">
+      <c r="N1" s="145" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
-      <c r="R1" s="144"/>
-      <c r="S1" s="144"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="146"/>
+      <c r="R1" s="146"/>
+      <c r="S1" s="146"/>
     </row>
     <row r="2" spans="1:19" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -2556,7 +2635,7 @@
         <v>5</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>6</v>
+        <v>313</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>7</v>
@@ -2724,7 +2803,7 @@
         <v>41</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>40</v>
+        <v>314</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>41</v>
@@ -2767,7 +2846,7 @@
         <v>41</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>40</v>
+        <v>314</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>41</v>
@@ -2777,7 +2856,7 @@
       </c>
       <c r="J6" s="28"/>
       <c r="K6" s="28" t="s">
-        <v>45</v>
+        <v>315</v>
       </c>
       <c r="L6" s="29" t="s">
         <v>46</v>
@@ -2968,7 +3047,7 @@
         <v>27</v>
       </c>
       <c r="J10" s="39" t="s">
-        <v>68</v>
+        <v>316</v>
       </c>
       <c r="K10" s="39" t="s">
         <v>69</v>
@@ -2980,7 +3059,7 @@
         <v>50</v>
       </c>
       <c r="N10" s="40" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="O10" s="40"/>
       <c r="P10" s="40"/>
@@ -3020,7 +3099,7 @@
       <c r="K11" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="L11" s="145" t="s">
+      <c r="L11" s="147" t="s">
         <v>77</v>
       </c>
       <c r="M11" s="59" t="s">
@@ -3077,7 +3156,7 @@
       <c r="K12" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="L12" s="146"/>
+      <c r="L12" s="148"/>
       <c r="M12" s="59" t="s">
         <v>43</v>
       </c>
@@ -3264,7 +3343,7 @@
         <v>91</v>
       </c>
       <c r="D16" s="77" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="E16" s="61"/>
       <c r="F16" s="37" t="s">
@@ -3301,7 +3380,7 @@
         <v>91</v>
       </c>
       <c r="D17" s="78" t="s">
-        <v>93</v>
+        <v>318</v>
       </c>
       <c r="E17" s="61"/>
       <c r="F17" s="37" t="s">
@@ -3317,7 +3396,7 @@
         <v>41</v>
       </c>
       <c r="J17" s="28" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="K17" s="28"/>
       <c r="L17" s="29"/>
@@ -3358,7 +3437,7 @@
         <v>27</v>
       </c>
       <c r="J18" s="66" t="s">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="K18" s="19" t="s">
         <v>101</v>
@@ -3397,7 +3476,7 @@
         <v>104</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E19" s="17"/>
       <c r="F19" s="37" t="s">
@@ -3413,10 +3492,10 @@
         <v>27</v>
       </c>
       <c r="J19" s="66" t="s">
+        <v>288</v>
+      </c>
+      <c r="K19" s="19" t="s">
         <v>289</v>
-      </c>
-      <c r="K19" s="19" t="s">
-        <v>290</v>
       </c>
       <c r="L19" s="19" t="s">
         <v>101</v>
@@ -3477,7 +3556,7 @@
       <c r="M20" s="34"/>
       <c r="N20" s="19"/>
       <c r="O20" s="84" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="P20" s="19"/>
       <c r="Q20" s="19"/>
@@ -3513,7 +3592,7 @@
         <v>27</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>116</v>
+        <v>321</v>
       </c>
       <c r="K21" s="18" t="s">
         <v>117</v>
@@ -3650,14 +3729,14 @@
         <v>132</v>
       </c>
       <c r="D24" s="142" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E24" s="17"/>
       <c r="F24" s="62" t="s">
         <v>41</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="H24" s="73" t="s">
         <v>41</v>
@@ -3689,7 +3768,7 @@
         <v>132</v>
       </c>
       <c r="D25" s="142" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E25" s="17"/>
       <c r="F25" s="62" t="s">
@@ -3728,14 +3807,14 @@
         <v>136</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="E26" s="17"/>
       <c r="F26" s="62" t="s">
         <v>41</v>
       </c>
       <c r="G26" s="82" t="s">
-        <v>138</v>
+        <v>296</v>
       </c>
       <c r="H26" s="73" t="s">
         <v>41</v>
@@ -3945,7 +4024,7 @@
         <v>24</v>
       </c>
       <c r="G30" s="35" t="s">
-        <v>155</v>
+        <v>297</v>
       </c>
       <c r="H30" s="36" t="s">
         <v>55</v>
@@ -4019,7 +4098,7 @@
       </c>
       <c r="M31" s="101"/>
       <c r="N31" s="55" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="O31" s="55">
         <v>0.57999999999999996</v>
@@ -4074,7 +4153,7 @@
         <v>161</v>
       </c>
       <c r="N32" s="42" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="O32" s="40">
         <v>116</v>
@@ -4127,7 +4206,7 @@
       </c>
       <c r="M33" s="101"/>
       <c r="N33" s="42" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="O33" s="108">
         <v>34</v>
@@ -4182,7 +4261,7 @@
         <v>161</v>
       </c>
       <c r="N34" s="42" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="O34" s="55">
         <v>0.44</v>
@@ -4218,7 +4297,7 @@
         <v>41</v>
       </c>
       <c r="G35" s="82" t="s">
-        <v>169</v>
+        <v>298</v>
       </c>
       <c r="H35" s="73" t="s">
         <v>41</v>
@@ -4257,7 +4336,7 @@
         <v>24</v>
       </c>
       <c r="G36" s="82" t="s">
-        <v>173</v>
+        <v>299</v>
       </c>
       <c r="H36" s="73" t="s">
         <v>41</v>
@@ -4289,7 +4368,7 @@
         <v>171</v>
       </c>
       <c r="D37" s="115" t="s">
-        <v>175</v>
+        <v>300</v>
       </c>
       <c r="E37" s="116"/>
       <c r="F37" s="73" t="s">
@@ -4346,7 +4425,7 @@
         <v>27</v>
       </c>
       <c r="J38" s="63" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="K38" s="19" t="s">
         <v>184</v>
@@ -4460,7 +4539,7 @@
         <v>27</v>
       </c>
       <c r="J40" s="66" t="s">
-        <v>187</v>
+        <v>302</v>
       </c>
       <c r="K40" s="19" t="s">
         <v>184</v>
@@ -4713,7 +4792,7 @@
         <v>196</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>200</v>
+        <v>303</v>
       </c>
       <c r="E45" s="17">
         <v>597</v>
@@ -4740,7 +4819,7 @@
       <c r="M45" s="34"/>
       <c r="N45" s="66"/>
       <c r="O45" s="19" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="P45" s="19"/>
       <c r="Q45" s="19"/>
@@ -5007,23 +5086,23 @@
         <v>218</v>
       </c>
       <c r="D51" s="88" t="s">
-        <v>225</v>
+        <v>304</v>
       </c>
       <c r="E51" s="88"/>
       <c r="F51" s="89" t="s">
-        <v>48</v>
+        <v>305</v>
       </c>
       <c r="G51" s="89" t="s">
         <v>63</v>
       </c>
       <c r="H51" s="73" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="I51" s="73" t="s">
         <v>27</v>
       </c>
       <c r="J51" s="130" t="s">
-        <v>226</v>
+        <v>307</v>
       </c>
       <c r="K51" s="131" t="s">
         <v>129</v>
@@ -5062,7 +5141,7 @@
         <v>228</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>229</v>
+        <v>308</v>
       </c>
       <c r="E52" s="17"/>
       <c r="F52" s="73" t="s">
@@ -5078,7 +5157,7 @@
         <v>27</v>
       </c>
       <c r="J52" s="66" t="s">
-        <v>231</v>
+        <v>309</v>
       </c>
       <c r="K52" s="19"/>
       <c r="L52" s="19" t="s">
@@ -5397,7 +5476,7 @@
       </c>
       <c r="E59" s="17"/>
       <c r="F59" s="134" t="s">
-        <v>48</v>
+        <v>305</v>
       </c>
       <c r="G59" s="27" t="s">
         <v>63</v>
@@ -5581,7 +5660,7 @@
         <v>274</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="E63" s="17">
         <v>542</v>
@@ -5631,7 +5710,7 @@
         <v>24</v>
       </c>
       <c r="G64" s="62" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="H64" s="73" t="s">
         <v>55</v>
@@ -5669,7 +5748,7 @@
         <v>282</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="E65" s="17">
         <v>547</v>
@@ -5685,7 +5764,7 @@
         <v>27</v>
       </c>
       <c r="J65" s="66" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="K65" s="19" t="s">
         <v>271</v>
@@ -5702,18 +5781,10 @@
       <c r="O65" s="64">
         <v>0.85</v>
       </c>
-      <c r="P65" s="64">
-        <v>0.85</v>
-      </c>
-      <c r="Q65" s="64">
-        <v>0.86</v>
-      </c>
-      <c r="R65" s="64">
-        <v>0.86</v>
-      </c>
-      <c r="S65" s="64">
-        <v>0.87</v>
-      </c>
+      <c r="P65" s="64"/>
+      <c r="Q65" s="64"/>
+      <c r="R65" s="64"/>
+      <c r="S65" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5762,14 +5833,14 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="143" t="s">
+      <c r="N1" s="145" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
-      <c r="R1" s="144"/>
-      <c r="S1" s="144"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="146"/>
+      <c r="R1" s="146"/>
+      <c r="S1" s="146"/>
     </row>
     <row r="2" spans="1:19" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -6298,7 +6369,7 @@
       <c r="K12" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="L12" s="145" t="s">
+      <c r="L12" s="147" t="s">
         <v>77</v>
       </c>
       <c r="M12" s="59" t="s">
@@ -6354,7 +6425,7 @@
       <c r="K13" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="L13" s="146"/>
+      <c r="L13" s="148"/>
       <c r="M13" s="59" t="s">
         <v>43</v>
       </c>
@@ -8824,13 +8895,13 @@
         <v>271</v>
       </c>
       <c r="M64" s="94"/>
-      <c r="N64" s="147">
+      <c r="N64" s="143">
         <v>1</v>
       </c>
       <c r="O64" s="141">
         <v>1.1357999999999999</v>
       </c>
-      <c r="P64" s="148">
+      <c r="P64" s="144">
         <f>O64/N64</f>
         <v>1.1357999999999999</v>
       </c>
@@ -8927,7 +8998,7 @@
       <c r="O66" s="141">
         <v>6.9900000000000004E-2</v>
       </c>
-      <c r="P66" s="148">
+      <c r="P66" s="144">
         <f>O66/N66</f>
         <v>1.7475000000000001</v>
       </c>

--- a/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Plan de mejoramiento/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/SGIND/data/raw/Plan de mejoramiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="239" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{597DF08B-EB46-4890-8BF0-4E22C3D79E09}"/>
+  <xr:revisionPtr revIDLastSave="254" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FB084A3-837D-4CB8-BB6C-CA87792D0567}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD3A294A-1D13-4C18-8C58-F237245A6723}"/>
   </bookViews>
@@ -53,7 +53,7 @@
     <comment ref="O11" authorId="0" shapeId="0" xr:uid="{029006E9-4008-49E2-BAEE-4CC12F0054C4}">
       <text>
         <t>[Comentario encadenado]
-Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Colaboradores: 63%
 Estudiantes: 18%
@@ -63,7 +63,7 @@
     <comment ref="O12" authorId="1" shapeId="0" xr:uid="{76CD3EFC-5330-4BD0-A48D-F1E64F16B9AC}">
       <text>
         <t>[Comentario encadenado]
-Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Colaboradores: 2% 
 Estudiantes: 3% 
@@ -87,7 +87,7 @@
     <comment ref="N7" authorId="0" shapeId="0" xr:uid="{FA05611A-1D16-4452-B93C-2E4DFFD86645}">
       <text>
         <t>[Comentario encadenado]
-Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Focus Group
 Estudiantes: 15
@@ -106,7 +106,7 @@
     <comment ref="Q12" authorId="1" shapeId="0" xr:uid="{3F85CAB4-6021-44EC-B795-E932C183C912}">
       <text>
         <t>[Comentario encadenado]
-Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Colaboradores: 63%
 Estudiantes: 18%
@@ -116,7 +116,7 @@
     <comment ref="R47" authorId="2" shapeId="0" xr:uid="{242351BE-3094-4A32-A1BB-45F00F8A6CDF}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Nivel de satisfacción Estudiante Presencial: 100%
 Nivel de satisfacción Estudiante Virtual: 100%
@@ -128,7 +128,7 @@
     <comment ref="R48" authorId="3" shapeId="0" xr:uid="{89AA3457-36D7-4CDB-AC41-C208171F6214}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Nivel de satisfacción Estudiante presencial: 98,1%
 Nivel de satisfacción Estudiante Virtual: 95,4%
@@ -141,7 +141,7 @@
     <comment ref="N64" authorId="4" shapeId="0" xr:uid="{E581DAFC-44AD-42D5-8849-003A27C98076}">
       <text>
         <t>[Comentario encadenado]
-Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     M0:  90% tasa de respuesta
 M1: 9% tasa de respuesta
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="323">
   <si>
     <t>Metas Preliminares</t>
   </si>
@@ -1331,7 +1331,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1725,7 +1725,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2167,6 +2167,9 @@
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2578,14 +2581,13 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:S65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="39.5546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="30.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="58.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="82" style="2" customWidth="1"/>
     <col min="4" max="7" width="34.5546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="34.5546875" style="2" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="34.5546875" style="2" customWidth="1"/>
+    <col min="8" max="9" width="34.5546875" style="2" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="23.6640625" style="2" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="26.44140625" style="2" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="22.33203125" style="2" customWidth="1"/>
@@ -2595,7 +2597,7 @@
     <col min="20" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="46.2" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2618,7 +2620,7 @@
       <c r="R1" s="146"/>
       <c r="S1" s="146"/>
     </row>
-    <row r="2" spans="1:19" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="31.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2658,10 +2660,10 @@
       <c r="M2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="13">
         <v>2025</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="13">
         <v>2026</v>
       </c>
       <c r="P2" s="13">
@@ -2677,7 +2679,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="75">
       <c r="A3" s="14" t="s">
         <v>20</v>
       </c>
@@ -2732,7 +2734,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="62.4">
       <c r="A4" s="14" t="s">
         <v>20</v>
       </c>
@@ -2785,7 +2787,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="46.8">
       <c r="A5" s="14" t="s">
         <v>20</v>
       </c>
@@ -2828,7 +2830,7 @@
       <c r="R5" s="29"/>
       <c r="S5" s="29"/>
     </row>
-    <row r="6" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="69" customHeight="1">
       <c r="A6" s="14" t="s">
         <v>20</v>
       </c>
@@ -2871,7 +2873,7 @@
       <c r="R6" s="29"/>
       <c r="S6" s="29"/>
     </row>
-    <row r="7" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="93.6">
       <c r="A7" s="32" t="s">
         <v>47</v>
       </c>
@@ -2899,16 +2901,14 @@
       <c r="K7" s="39"/>
       <c r="L7" s="40"/>
       <c r="M7" s="34"/>
-      <c r="N7" s="47" t="s">
-        <v>59</v>
-      </c>
+      <c r="N7" s="47"/>
       <c r="O7" s="40"/>
       <c r="P7" s="40"/>
       <c r="Q7" s="40"/>
       <c r="R7" s="40"/>
       <c r="S7" s="40"/>
     </row>
-    <row r="8" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="75">
       <c r="A8" s="32" t="s">
         <v>47</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="46.8">
       <c r="A9" s="32" t="s">
         <v>47</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="60">
       <c r="A10" s="32" t="s">
         <v>47</v>
       </c>
@@ -3067,7 +3067,7 @@
       <c r="R10" s="40"/>
       <c r="S10" s="40"/>
     </row>
-    <row r="11" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="46.8">
       <c r="A11" s="56" t="s">
         <v>71</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="60">
       <c r="A12" s="56" t="s">
         <v>71</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="46.8">
       <c r="A13" s="56" t="s">
         <v>71</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="46.8">
       <c r="A14" s="56" t="s">
         <v>71</v>
       </c>
@@ -3279,7 +3279,7 @@
       <c r="R14" s="19"/>
       <c r="S14" s="19"/>
     </row>
-    <row r="15" spans="1:19" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="31.2">
       <c r="A15" s="56" t="s">
         <v>71</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" ht="62.4">
       <c r="A16" s="56" t="s">
         <v>71</v>
       </c>
@@ -3369,7 +3369,7 @@
       <c r="R16" s="19"/>
       <c r="S16" s="19"/>
     </row>
-    <row r="17" spans="1:19" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="150">
       <c r="A17" s="56" t="s">
         <v>71</v>
       </c>
@@ -3410,7 +3410,7 @@
       <c r="R17" s="29"/>
       <c r="S17" s="29"/>
     </row>
-    <row r="18" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="120">
       <c r="A18" s="79" t="s">
         <v>96</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="75">
       <c r="A19" s="79" t="s">
         <v>96</v>
       </c>
@@ -3518,7 +3518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="62.4">
       <c r="A20" s="79" t="s">
         <v>96</v>
       </c>
@@ -3563,7 +3563,7 @@
       <c r="R20" s="19"/>
       <c r="S20" s="19"/>
     </row>
-    <row r="21" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="60">
       <c r="A21" s="79" t="s">
         <v>96</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="46.8">
       <c r="A22" s="79" t="s">
         <v>96</v>
       </c>
@@ -3669,7 +3669,7 @@
       <c r="R22" s="19"/>
       <c r="S22" s="19"/>
     </row>
-    <row r="23" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="46.8">
       <c r="A23" s="79" t="s">
         <v>96</v>
       </c>
@@ -3718,7 +3718,7 @@
       <c r="R23" s="19"/>
       <c r="S23" s="19"/>
     </row>
-    <row r="24" spans="1:19" ht="218.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="218.4">
       <c r="A24" s="79" t="s">
         <v>130</v>
       </c>
@@ -3757,7 +3757,7 @@
       <c r="R24" s="29"/>
       <c r="S24" s="29"/>
     </row>
-    <row r="25" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="124.8">
       <c r="A25" s="79" t="s">
         <v>130</v>
       </c>
@@ -3796,7 +3796,7 @@
       <c r="R25" s="29"/>
       <c r="S25" s="29"/>
     </row>
-    <row r="26" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="93.6">
       <c r="A26" s="79" t="s">
         <v>130</v>
       </c>
@@ -3841,7 +3841,7 @@
       <c r="R26" s="19"/>
       <c r="S26" s="19"/>
     </row>
-    <row r="27" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="62.4">
       <c r="A27" s="79" t="s">
         <v>130</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="62.4">
       <c r="A28" s="79" t="s">
         <v>130</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="62.4">
       <c r="A29" s="79" t="s">
         <v>130</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="75">
       <c r="A30" s="33" t="s">
         <v>151</v>
       </c>
@@ -4063,7 +4063,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="46.8">
       <c r="A31" s="33" t="s">
         <v>151</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="105">
       <c r="A32" s="33" t="s">
         <v>151</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="120">
       <c r="A33" s="33" t="s">
         <v>151</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="46.8">
       <c r="A34" s="33" t="s">
         <v>151</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="124.8">
       <c r="A35" s="80" t="s">
         <v>165</v>
       </c>
@@ -4318,7 +4318,7 @@
       <c r="R35" s="19"/>
       <c r="S35" s="19"/>
     </row>
-    <row r="36" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="60">
       <c r="A36" s="80" t="s">
         <v>165</v>
       </c>
@@ -4357,7 +4357,7 @@
       <c r="R36" s="19"/>
       <c r="S36" s="19"/>
     </row>
-    <row r="37" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="93.6">
       <c r="A37" s="80" t="s">
         <v>165</v>
       </c>
@@ -4396,7 +4396,7 @@
       <c r="R37" s="19"/>
       <c r="S37" s="19"/>
     </row>
-    <row r="38" spans="1:19" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="46.95" customHeight="1">
       <c r="A38" s="93" t="s">
         <v>177</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="62.4">
       <c r="A39" s="93" t="s">
         <v>177</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="90">
       <c r="A40" s="93" t="s">
         <v>177</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="75">
       <c r="A41" s="93" t="s">
         <v>177</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="75">
       <c r="A42" s="93" t="s">
         <v>177</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" ht="90">
       <c r="A43" s="93" t="s">
         <v>177</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="88.8" customHeight="1">
       <c r="A44" s="93" t="s">
         <v>194</v>
       </c>
@@ -4781,7 +4781,7 @@
       <c r="R44" s="29"/>
       <c r="S44" s="29"/>
     </row>
-    <row r="45" spans="1:19" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="130.80000000000001" customHeight="1">
       <c r="A45" s="80" t="s">
         <v>194</v>
       </c>
@@ -4826,7 +4826,7 @@
       <c r="R45" s="19"/>
       <c r="S45" s="19"/>
     </row>
-    <row r="46" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="132.6" customHeight="1">
       <c r="A46" s="93" t="s">
         <v>194</v>
       </c>
@@ -4875,7 +4875,7 @@
       <c r="R46" s="29"/>
       <c r="S46" s="29"/>
     </row>
-    <row r="47" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="132.6" customHeight="1">
       <c r="A47" s="93" t="s">
         <v>194</v>
       </c>
@@ -4922,7 +4922,7 @@
       <c r="R47" s="29"/>
       <c r="S47" s="29"/>
     </row>
-    <row r="48" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="93.6">
       <c r="A48" s="80" t="s">
         <v>194</v>
       </c>
@@ -4963,7 +4963,7 @@
       <c r="R48" s="19"/>
       <c r="S48" s="19"/>
     </row>
-    <row r="49" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" ht="90">
       <c r="A49" s="80" t="s">
         <v>212</v>
       </c>
@@ -5020,7 +5020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="78" customHeight="1">
       <c r="A50" s="93" t="s">
         <v>212</v>
       </c>
@@ -5075,7 +5075,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" ht="60">
       <c r="A51" s="80" t="s">
         <v>212</v>
       </c>
@@ -5130,7 +5130,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="75">
       <c r="A52" s="80" t="s">
         <v>212</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="105">
       <c r="A53" s="80" t="s">
         <v>212</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" ht="105">
       <c r="A54" s="80" t="s">
         <v>212</v>
       </c>
@@ -5281,7 +5281,7 @@
       <c r="R54" s="19"/>
       <c r="S54" s="19"/>
     </row>
-    <row r="55" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="75">
       <c r="A55" s="80" t="s">
         <v>241</v>
       </c>
@@ -5320,7 +5320,7 @@
       <c r="R55" s="19"/>
       <c r="S55" s="19"/>
     </row>
-    <row r="56" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" ht="45">
       <c r="A56" s="80" t="s">
         <v>241</v>
       </c>
@@ -5367,7 +5367,7 @@
       <c r="R56" s="19"/>
       <c r="S56" s="19"/>
     </row>
-    <row r="57" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" ht="105">
       <c r="A57" s="80" t="s">
         <v>241</v>
       </c>
@@ -5405,18 +5405,18 @@
       <c r="M57" s="136" t="s">
         <v>255</v>
       </c>
-      <c r="N57" s="66">
-        <v>86.1</v>
-      </c>
-      <c r="O57" s="19">
-        <v>86.6</v>
+      <c r="N57" s="65">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="O57" s="149">
+        <v>0.86599999999999999</v>
       </c>
       <c r="P57" s="19"/>
       <c r="Q57" s="19"/>
       <c r="R57" s="19"/>
       <c r="S57" s="19"/>
     </row>
-    <row r="58" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" ht="109.2">
       <c r="A58" s="80" t="s">
         <v>241</v>
       </c>
@@ -5461,7 +5461,7 @@
       <c r="R58" s="19"/>
       <c r="S58" s="19"/>
     </row>
-    <row r="59" spans="1:19" ht="124.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" ht="124.95" customHeight="1">
       <c r="A59" s="93" t="s">
         <v>241</v>
       </c>
@@ -5504,7 +5504,7 @@
       <c r="R59" s="29"/>
       <c r="S59" s="29"/>
     </row>
-    <row r="60" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" ht="105">
       <c r="A60" s="80" t="s">
         <v>241</v>
       </c>
@@ -5540,16 +5540,18 @@
         <v>254</v>
       </c>
       <c r="M60" s="136"/>
-      <c r="N60" s="19">
-        <v>74.8</v>
-      </c>
-      <c r="O60" s="19"/>
+      <c r="N60" s="149">
+        <v>0.74199999999999999</v>
+      </c>
+      <c r="O60" s="149">
+        <v>0.748</v>
+      </c>
       <c r="P60" s="19"/>
       <c r="Q60" s="19"/>
       <c r="R60" s="19"/>
       <c r="S60" s="19"/>
     </row>
-    <row r="61" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" ht="75">
       <c r="A61" s="80" t="s">
         <v>241</v>
       </c>
@@ -5592,7 +5594,7 @@
       <c r="R61" s="19"/>
       <c r="S61" s="19"/>
     </row>
-    <row r="62" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" ht="120.6">
       <c r="A62" s="93" t="s">
         <v>266</v>
       </c>
@@ -5649,7 +5651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" ht="70.95" customHeight="1">
       <c r="A63" s="93" t="s">
         <v>266</v>
       </c>
@@ -5690,7 +5692,7 @@
       <c r="R63" s="29"/>
       <c r="S63" s="29"/>
     </row>
-    <row r="64" spans="1:19" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" ht="150">
       <c r="A64" s="93" t="s">
         <v>266</v>
       </c>
@@ -5737,7 +5739,7 @@
       <c r="R64" s="29"/>
       <c r="S64" s="29"/>
     </row>
-    <row r="65" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" ht="46.8">
       <c r="A65" s="80" t="s">
         <v>266</v>
       </c>
@@ -5803,7 +5805,7 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:S67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="39.5546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="30.88671875" style="2" customWidth="1"/>
@@ -5819,7 +5821,7 @@
     <col min="20" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="46.2" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5842,7 +5844,7 @@
       <c r="R1" s="146"/>
       <c r="S1" s="146"/>
     </row>
-    <row r="2" spans="1:19" ht="36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="36">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -5901,7 +5903,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="78" hidden="1">
       <c r="A3" s="14" t="s">
         <v>20</v>
       </c>
@@ -5957,7 +5959,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="62.4" hidden="1">
       <c r="A4" s="14" t="s">
         <v>20</v>
       </c>
@@ -6006,7 +6008,7 @@
       <c r="R4" s="21"/>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="46.8" hidden="1">
       <c r="A5" s="14" t="s">
         <v>20</v>
       </c>
@@ -6049,7 +6051,7 @@
       <c r="R5" s="29"/>
       <c r="S5" s="31"/>
     </row>
-    <row r="6" spans="1:19" ht="69" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="69" hidden="1" customHeight="1">
       <c r="A6" s="14" t="s">
         <v>20</v>
       </c>
@@ -6092,7 +6094,7 @@
       <c r="R6" s="29"/>
       <c r="S6" s="31"/>
     </row>
-    <row r="7" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="62.4" hidden="1">
       <c r="A7" s="32" t="s">
         <v>47</v>
       </c>
@@ -6142,7 +6144,7 @@
       <c r="R7" s="40"/>
       <c r="S7" s="44"/>
     </row>
-    <row r="8" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="93.6" hidden="1">
       <c r="A8" s="32" t="s">
         <v>47</v>
       </c>
@@ -6179,7 +6181,7 @@
       <c r="R8" s="40"/>
       <c r="S8" s="44"/>
     </row>
-    <row r="9" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="78" hidden="1">
       <c r="A9" s="32" t="s">
         <v>47</v>
       </c>
@@ -6238,7 +6240,7 @@
         <v>1.0608333333333333</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="46.8" hidden="1">
       <c r="A10" s="32" t="s">
         <v>47</v>
       </c>
@@ -6290,7 +6292,7 @@
       <c r="R10" s="40"/>
       <c r="S10" s="44"/>
     </row>
-    <row r="11" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="78" hidden="1">
       <c r="A11" s="32" t="s">
         <v>47</v>
       </c>
@@ -6337,7 +6339,7 @@
       <c r="R11" s="40"/>
       <c r="S11" s="44"/>
     </row>
-    <row r="12" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="62.4" hidden="1">
       <c r="A12" s="56" t="s">
         <v>71</v>
       </c>
@@ -6393,7 +6395,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="93.6" hidden="1">
       <c r="A13" s="56" t="s">
         <v>71</v>
       </c>
@@ -6438,7 +6440,7 @@
       <c r="R13" s="19"/>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="46.8" hidden="1">
       <c r="A14" s="56" t="s">
         <v>71</v>
       </c>
@@ -6483,7 +6485,7 @@
       <c r="R14" s="68"/>
       <c r="S14" s="69"/>
     </row>
-    <row r="15" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="46.8" hidden="1">
       <c r="A15" s="56" t="s">
         <v>71</v>
       </c>
@@ -6526,7 +6528,7 @@
       <c r="R15" s="19"/>
       <c r="S15" s="23"/>
     </row>
-    <row r="16" spans="1:19" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" ht="31.2" hidden="1">
       <c r="A16" s="56" t="s">
         <v>71</v>
       </c>
@@ -6567,7 +6569,7 @@
       <c r="R16" s="19"/>
       <c r="S16" s="23"/>
     </row>
-    <row r="17" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="62.4" hidden="1">
       <c r="A17" s="56" t="s">
         <v>71</v>
       </c>
@@ -6604,7 +6606,7 @@
       <c r="R17" s="19"/>
       <c r="S17" s="23"/>
     </row>
-    <row r="18" spans="1:19" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="187.2" hidden="1">
       <c r="A18" s="56" t="s">
         <v>71</v>
       </c>
@@ -6645,7 +6647,7 @@
       <c r="R18" s="29"/>
       <c r="S18" s="31"/>
     </row>
-    <row r="19" spans="1:19" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="140.4" hidden="1">
       <c r="A19" s="79" t="s">
         <v>96</v>
       </c>
@@ -6688,7 +6690,7 @@
       <c r="R19" s="19"/>
       <c r="S19" s="23"/>
     </row>
-    <row r="20" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="109.2" hidden="1">
       <c r="A20" s="79" t="s">
         <v>96</v>
       </c>
@@ -6735,7 +6737,7 @@
       <c r="R20" s="21"/>
       <c r="S20" s="22"/>
     </row>
-    <row r="21" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="78" hidden="1">
       <c r="A21" s="79" t="s">
         <v>96</v>
       </c>
@@ -6780,7 +6782,7 @@
       <c r="R21" s="19"/>
       <c r="S21" s="23"/>
     </row>
-    <row r="22" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="62.4" hidden="1">
       <c r="A22" s="79" t="s">
         <v>96</v>
       </c>
@@ -6831,7 +6833,7 @@
       <c r="R22" s="86"/>
       <c r="S22" s="87"/>
     </row>
-    <row r="23" spans="1:19" ht="78" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="62.4">
       <c r="A23" s="79" t="s">
         <v>96</v>
       </c>
@@ -6878,7 +6880,7 @@
       <c r="R23" s="19"/>
       <c r="S23" s="23"/>
     </row>
-    <row r="24" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="46.8" hidden="1">
       <c r="A24" s="79" t="s">
         <v>96</v>
       </c>
@@ -6930,7 +6932,7 @@
       <c r="R24" s="19"/>
       <c r="S24" s="23"/>
     </row>
-    <row r="25" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="62.4" hidden="1">
       <c r="A25" s="79" t="s">
         <v>96</v>
       </c>
@@ -6989,7 +6991,7 @@
         <v>0.99356223175965663</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="109.2" hidden="1">
       <c r="A26" s="57" t="s">
         <v>130</v>
       </c>
@@ -7028,7 +7030,7 @@
       <c r="R26" s="29"/>
       <c r="S26" s="31"/>
     </row>
-    <row r="27" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="93.6" hidden="1">
       <c r="A27" s="79" t="s">
         <v>130</v>
       </c>
@@ -7073,7 +7075,7 @@
       <c r="R27" s="19"/>
       <c r="S27" s="23"/>
     </row>
-    <row r="28" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="78" hidden="1">
       <c r="A28" s="79" t="s">
         <v>130</v>
       </c>
@@ -7118,7 +7120,7 @@
       <c r="R28" s="19"/>
       <c r="S28" s="23"/>
     </row>
-    <row r="29" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="62.4" hidden="1">
       <c r="A29" s="79" t="s">
         <v>130</v>
       </c>
@@ -7173,7 +7175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="62.4" hidden="1">
       <c r="A30" s="79" t="s">
         <v>130</v>
       </c>
@@ -7230,7 +7232,7 @@
         <v>0.14285714285714285</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="78" hidden="1">
       <c r="A31" s="33" t="s">
         <v>151</v>
       </c>
@@ -7291,7 +7293,7 @@
         <v>1.02125</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="62.4" hidden="1">
       <c r="A32" s="33" t="s">
         <v>151</v>
       </c>
@@ -7338,7 +7340,7 @@
       <c r="R32" s="40"/>
       <c r="S32" s="44"/>
     </row>
-    <row r="33" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="124.8" hidden="1">
       <c r="A33" s="33" t="s">
         <v>151</v>
       </c>
@@ -7387,7 +7389,7 @@
       <c r="R33" s="40"/>
       <c r="S33" s="44"/>
     </row>
-    <row r="34" spans="1:19" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="140.4" hidden="1">
       <c r="A34" s="33" t="s">
         <v>151</v>
       </c>
@@ -7434,7 +7436,7 @@
       <c r="R34" s="108"/>
       <c r="S34" s="109"/>
     </row>
-    <row r="35" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="62.4" hidden="1">
       <c r="A35" s="33" t="s">
         <v>151</v>
       </c>
@@ -7483,7 +7485,7 @@
       <c r="R35" s="40"/>
       <c r="S35" s="44"/>
     </row>
-    <row r="36" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="124.8" hidden="1">
       <c r="A36" s="80" t="s">
         <v>165</v>
       </c>
@@ -7522,7 +7524,7 @@
       <c r="R36" s="19"/>
       <c r="S36" s="23"/>
     </row>
-    <row r="37" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="62.4" hidden="1">
       <c r="A37" s="80" t="s">
         <v>165</v>
       </c>
@@ -7561,7 +7563,7 @@
       <c r="R37" s="19"/>
       <c r="S37" s="23"/>
     </row>
-    <row r="38" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="93.6" hidden="1">
       <c r="A38" s="80" t="s">
         <v>165</v>
       </c>
@@ -7600,7 +7602,7 @@
       <c r="R38" s="19"/>
       <c r="S38" s="23"/>
     </row>
-    <row r="39" spans="1:19" ht="46.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="46.95" hidden="1" customHeight="1">
       <c r="A39" s="93" t="s">
         <v>177</v>
       </c>
@@ -7659,7 +7661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="62.4" hidden="1">
       <c r="A40" s="93" t="s">
         <v>177</v>
       </c>
@@ -7718,7 +7720,7 @@
         <v>1.099</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="124.8" hidden="1">
       <c r="A41" s="93" t="s">
         <v>177</v>
       </c>
@@ -7777,7 +7779,7 @@
         <v>0.82269999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="93.6" hidden="1">
       <c r="A42" s="93" t="s">
         <v>177</v>
       </c>
@@ -7836,7 +7838,7 @@
         <v>1.3244</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" ht="93.6" hidden="1">
       <c r="A43" s="93" t="s">
         <v>177</v>
       </c>
@@ -7895,7 +7897,7 @@
         <v>1.1175999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="93.6" hidden="1">
       <c r="A44" s="93" t="s">
         <v>177</v>
       </c>
@@ -7954,7 +7956,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="88.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="88.8" hidden="1" customHeight="1">
       <c r="A45" s="93" t="s">
         <v>194</v>
       </c>
@@ -7997,7 +7999,7 @@
       <c r="R45" s="29"/>
       <c r="S45" s="31"/>
     </row>
-    <row r="46" spans="1:19" ht="130.80000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="130.80000000000001" hidden="1" customHeight="1">
       <c r="A46" s="80" t="s">
         <v>194</v>
       </c>
@@ -8044,7 +8046,7 @@
       <c r="R46" s="19"/>
       <c r="S46" s="23"/>
     </row>
-    <row r="47" spans="1:19" ht="132.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="132.6" hidden="1" customHeight="1">
       <c r="A47" s="93" t="s">
         <v>194</v>
       </c>
@@ -8103,7 +8105,7 @@
         <v>1.1764705882352942</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="132.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="132.6" hidden="1" customHeight="1">
       <c r="A48" s="93" t="s">
         <v>194</v>
       </c>
@@ -8160,7 +8162,7 @@
         <v>1.151764705882353</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" ht="93.6" hidden="1">
       <c r="A49" s="80" t="s">
         <v>194</v>
       </c>
@@ -8203,7 +8205,7 @@
       <c r="R49" s="19"/>
       <c r="S49" s="23"/>
     </row>
-    <row r="50" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="109.2" hidden="1">
       <c r="A50" s="80" t="s">
         <v>212</v>
       </c>
@@ -8252,7 +8254,7 @@
       <c r="R50" s="21"/>
       <c r="S50" s="22"/>
     </row>
-    <row r="51" spans="1:19" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" ht="78" hidden="1" customHeight="1">
       <c r="A51" s="93" t="s">
         <v>212</v>
       </c>
@@ -8299,7 +8301,7 @@
       <c r="R51" s="29"/>
       <c r="S51" s="31"/>
     </row>
-    <row r="52" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="93.6" hidden="1">
       <c r="A52" s="80" t="s">
         <v>212</v>
       </c>
@@ -8344,7 +8346,7 @@
       <c r="R52" s="131"/>
       <c r="S52" s="23"/>
     </row>
-    <row r="53" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="62.4" hidden="1">
       <c r="A53" s="80" t="s">
         <v>212</v>
       </c>
@@ -8391,7 +8393,7 @@
       <c r="R53" s="64"/>
       <c r="S53" s="132"/>
     </row>
-    <row r="54" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" ht="93.6" hidden="1">
       <c r="A54" s="80" t="s">
         <v>212</v>
       </c>
@@ -8436,7 +8438,7 @@
       <c r="R54" s="64"/>
       <c r="S54" s="132"/>
     </row>
-    <row r="55" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="109.2" hidden="1">
       <c r="A55" s="80" t="s">
         <v>212</v>
       </c>
@@ -8490,7 +8492,7 @@
       <c r="R55" s="19"/>
       <c r="S55" s="23"/>
     </row>
-    <row r="56" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" ht="124.8" hidden="1">
       <c r="A56" s="80" t="s">
         <v>212</v>
       </c>
@@ -8531,7 +8533,7 @@
       <c r="R56" s="19"/>
       <c r="S56" s="23"/>
     </row>
-    <row r="57" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" ht="93.6" hidden="1">
       <c r="A57" s="80" t="s">
         <v>241</v>
       </c>
@@ -8570,7 +8572,7 @@
       <c r="R57" s="19"/>
       <c r="S57" s="23"/>
     </row>
-    <row r="58" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" ht="46.8" hidden="1">
       <c r="A58" s="80" t="s">
         <v>241</v>
       </c>
@@ -8617,7 +8619,7 @@
       <c r="R58" s="19"/>
       <c r="S58" s="23"/>
     </row>
-    <row r="59" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" ht="109.2">
       <c r="A59" s="80" t="s">
         <v>241</v>
       </c>
@@ -8674,7 +8676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" ht="124.8" hidden="1">
       <c r="A60" s="80" t="s">
         <v>241</v>
       </c>
@@ -8719,7 +8721,7 @@
       <c r="R60" s="19"/>
       <c r="S60" s="23"/>
     </row>
-    <row r="61" spans="1:19" ht="124.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" ht="124.95" hidden="1" customHeight="1">
       <c r="A61" s="93" t="s">
         <v>241</v>
       </c>
@@ -8762,7 +8764,7 @@
       <c r="R61" s="29"/>
       <c r="S61" s="31"/>
     </row>
-    <row r="62" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" ht="109.2">
       <c r="A62" s="80" t="s">
         <v>241</v>
       </c>
@@ -8814,7 +8816,7 @@
       <c r="R62" s="19"/>
       <c r="S62" s="23"/>
     </row>
-    <row r="63" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" ht="93.6" hidden="1">
       <c r="A63" s="80" t="s">
         <v>241</v>
       </c>
@@ -8857,7 +8859,7 @@
       <c r="R63" s="19"/>
       <c r="S63" s="23"/>
     </row>
-    <row r="64" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" ht="109.2" hidden="1">
       <c r="A64" s="93" t="s">
         <v>266</v>
       </c>
@@ -8911,7 +8913,7 @@
       <c r="R64" s="29"/>
       <c r="S64" s="31"/>
     </row>
-    <row r="65" spans="1:19" ht="70.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" ht="70.95" hidden="1" customHeight="1">
       <c r="A65" s="93" t="s">
         <v>266</v>
       </c>
@@ -8954,7 +8956,7 @@
       <c r="R65" s="29"/>
       <c r="S65" s="31"/>
     </row>
-    <row r="66" spans="1:19" ht="171.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" ht="171.6" hidden="1">
       <c r="A66" s="93" t="s">
         <v>266</v>
       </c>
@@ -9008,7 +9010,7 @@
       <c r="R66" s="29"/>
       <c r="S66" s="31"/>
     </row>
-    <row r="67" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" ht="46.8" hidden="1">
       <c r="A67" s="80" t="s">
         <v>266</v>
       </c>

--- a/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/SGIND/data/raw/Plan de mejoramiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="254" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FB084A3-837D-4CB8-BB6C-CA87792D0567}"/>
+  <xr:revisionPtr revIDLastSave="264" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D4FEF24-A07B-4E3F-80B4-33065419E645}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD3A294A-1D13-4C18-8C58-F237245A6723}"/>
   </bookViews>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="324">
   <si>
     <t>Metas Preliminares</t>
   </si>
@@ -1320,6 +1320,9 @@
       </rPr>
       <t>28 septiembre</t>
     </r>
+  </si>
+  <si>
+    <t>Disponibilidad de servicios tecnologicos</t>
   </si>
 </sst>
 </file>
@@ -2157,6 +2160,9 @@
     <xf numFmtId="10" fontId="11" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2167,9 +2173,6 @@
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2580,7 +2583,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="39.5546875" style="2" customWidth="1"/>
@@ -2611,14 +2614,14 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="145" t="s">
+      <c r="N1" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="146"/>
-      <c r="P1" s="146"/>
-      <c r="Q1" s="146"/>
-      <c r="R1" s="146"/>
-      <c r="S1" s="146"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="147"/>
     </row>
     <row r="2" spans="1:19" ht="31.2">
       <c r="A2" s="3" t="s">
@@ -3067,7 +3070,7 @@
       <c r="R10" s="40"/>
       <c r="S10" s="40"/>
     </row>
-    <row r="11" spans="1:19" ht="46.8">
+    <row r="11" spans="1:19" ht="45">
       <c r="A11" s="56" t="s">
         <v>71</v>
       </c>
@@ -3099,7 +3102,7 @@
       <c r="K11" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="L11" s="147" t="s">
+      <c r="L11" s="148" t="s">
         <v>77</v>
       </c>
       <c r="M11" s="59" t="s">
@@ -3156,7 +3159,7 @@
       <c r="K12" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="L12" s="148"/>
+      <c r="L12" s="149"/>
       <c r="M12" s="59" t="s">
         <v>43</v>
       </c>
@@ -3179,7 +3182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="46.8">
+    <row r="13" spans="1:19" ht="31.2">
       <c r="A13" s="56" t="s">
         <v>71</v>
       </c>
@@ -3236,7 +3239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="46.8">
+    <row r="14" spans="1:19" ht="31.2">
       <c r="A14" s="56" t="s">
         <v>71</v>
       </c>
@@ -3332,7 +3335,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="62.4">
+    <row r="16" spans="1:19" ht="46.8">
       <c r="A16" s="56" t="s">
         <v>71</v>
       </c>
@@ -3841,7 +3844,7 @@
       <c r="R26" s="19"/>
       <c r="S26" s="19"/>
     </row>
-    <row r="27" spans="1:19" ht="62.4">
+    <row r="27" spans="1:19" ht="60">
       <c r="A27" s="79" t="s">
         <v>130</v>
       </c>
@@ -5408,7 +5411,7 @@
       <c r="N57" s="65">
         <v>0.86099999999999999</v>
       </c>
-      <c r="O57" s="149">
+      <c r="O57" s="145">
         <v>0.86599999999999999</v>
       </c>
       <c r="P57" s="19"/>
@@ -5416,7 +5419,7 @@
       <c r="R57" s="19"/>
       <c r="S57" s="19"/>
     </row>
-    <row r="58" spans="1:19" ht="109.2">
+    <row r="58" spans="1:19" ht="105">
       <c r="A58" s="80" t="s">
         <v>241</v>
       </c>
@@ -5540,10 +5543,10 @@
         <v>254</v>
       </c>
       <c r="M60" s="136"/>
-      <c r="N60" s="149">
+      <c r="N60" s="145">
         <v>0.74199999999999999</v>
       </c>
-      <c r="O60" s="149">
+      <c r="O60" s="145">
         <v>0.748</v>
       </c>
       <c r="P60" s="19"/>
@@ -5787,6 +5790,40 @@
       <c r="Q65" s="64"/>
       <c r="R65" s="64"/>
       <c r="S65" s="64"/>
+    </row>
+    <row r="66" spans="1:19" ht="46.8">
+      <c r="A66" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="C66" s="70" t="s">
+        <v>91</v>
+      </c>
+      <c r="D66" s="77" t="s">
+        <v>323</v>
+      </c>
+      <c r="E66" s="61"/>
+      <c r="F66" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G66" s="72"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="19"/>
+      <c r="K66" s="19"/>
+      <c r="L66" s="21"/>
+      <c r="M66" s="19"/>
+      <c r="N66" s="21">
+        <v>0.97</v>
+      </c>
+      <c r="O66" s="21">
+        <v>0.97</v>
+      </c>
+      <c r="P66" s="21">
+        <v>0.97</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5835,14 +5872,14 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="145" t="s">
+      <c r="N1" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="146"/>
-      <c r="P1" s="146"/>
-      <c r="Q1" s="146"/>
-      <c r="R1" s="146"/>
-      <c r="S1" s="146"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="147"/>
     </row>
     <row r="2" spans="1:19" ht="36">
       <c r="A2" s="3" t="s">
@@ -5903,7 +5940,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="78" hidden="1">
+    <row r="3" spans="1:19" ht="75" hidden="1">
       <c r="A3" s="14" t="s">
         <v>20</v>
       </c>
@@ -6181,7 +6218,7 @@
       <c r="R8" s="40"/>
       <c r="S8" s="44"/>
     </row>
-    <row r="9" spans="1:19" ht="78" hidden="1">
+    <row r="9" spans="1:19" ht="75" hidden="1">
       <c r="A9" s="32" t="s">
         <v>47</v>
       </c>
@@ -6292,7 +6329,7 @@
       <c r="R10" s="40"/>
       <c r="S10" s="44"/>
     </row>
-    <row r="11" spans="1:19" ht="78" hidden="1">
+    <row r="11" spans="1:19" ht="60" hidden="1">
       <c r="A11" s="32" t="s">
         <v>47</v>
       </c>
@@ -6339,7 +6376,7 @@
       <c r="R11" s="40"/>
       <c r="S11" s="44"/>
     </row>
-    <row r="12" spans="1:19" ht="62.4" hidden="1">
+    <row r="12" spans="1:19" ht="46.8" hidden="1">
       <c r="A12" s="56" t="s">
         <v>71</v>
       </c>
@@ -6371,7 +6408,7 @@
       <c r="K12" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="L12" s="147" t="s">
+      <c r="L12" s="148" t="s">
         <v>77</v>
       </c>
       <c r="M12" s="59" t="s">
@@ -6395,7 +6432,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="93.6" hidden="1">
+    <row r="13" spans="1:19" ht="75" hidden="1">
       <c r="A13" s="56" t="s">
         <v>71</v>
       </c>
@@ -6427,7 +6464,7 @@
       <c r="K13" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="L13" s="148"/>
+      <c r="L13" s="149"/>
       <c r="M13" s="59" t="s">
         <v>43</v>
       </c>
@@ -6606,7 +6643,7 @@
       <c r="R17" s="19"/>
       <c r="S17" s="23"/>
     </row>
-    <row r="18" spans="1:19" ht="187.2" hidden="1">
+    <row r="18" spans="1:19" ht="150" hidden="1">
       <c r="A18" s="56" t="s">
         <v>71</v>
       </c>
@@ -6647,7 +6684,7 @@
       <c r="R18" s="29"/>
       <c r="S18" s="31"/>
     </row>
-    <row r="19" spans="1:19" ht="140.4" hidden="1">
+    <row r="19" spans="1:19" ht="120" hidden="1">
       <c r="A19" s="79" t="s">
         <v>96</v>
       </c>
@@ -6690,7 +6727,7 @@
       <c r="R19" s="19"/>
       <c r="S19" s="23"/>
     </row>
-    <row r="20" spans="1:19" ht="109.2" hidden="1">
+    <row r="20" spans="1:19" ht="105" hidden="1">
       <c r="A20" s="79" t="s">
         <v>96</v>
       </c>
@@ -6737,7 +6774,7 @@
       <c r="R20" s="21"/>
       <c r="S20" s="22"/>
     </row>
-    <row r="21" spans="1:19" ht="78" hidden="1">
+    <row r="21" spans="1:19" ht="62.4" hidden="1">
       <c r="A21" s="79" t="s">
         <v>96</v>
       </c>
@@ -6782,7 +6819,7 @@
       <c r="R21" s="19"/>
       <c r="S21" s="23"/>
     </row>
-    <row r="22" spans="1:19" ht="62.4" hidden="1">
+    <row r="22" spans="1:19" ht="60" hidden="1">
       <c r="A22" s="79" t="s">
         <v>96</v>
       </c>
@@ -6932,7 +6969,7 @@
       <c r="R24" s="19"/>
       <c r="S24" s="23"/>
     </row>
-    <row r="25" spans="1:19" ht="62.4" hidden="1">
+    <row r="25" spans="1:19" ht="46.8" hidden="1">
       <c r="A25" s="79" t="s">
         <v>96</v>
       </c>
@@ -6991,7 +7028,7 @@
         <v>0.99356223175965663</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="109.2" hidden="1">
+    <row r="26" spans="1:19" ht="93.6" hidden="1">
       <c r="A26" s="57" t="s">
         <v>130</v>
       </c>
@@ -7075,7 +7112,7 @@
       <c r="R27" s="19"/>
       <c r="S27" s="23"/>
     </row>
-    <row r="28" spans="1:19" ht="78" hidden="1">
+    <row r="28" spans="1:19" ht="62.4" hidden="1">
       <c r="A28" s="79" t="s">
         <v>130</v>
       </c>
@@ -7232,7 +7269,7 @@
         <v>0.14285714285714285</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="78" hidden="1">
+    <row r="31" spans="1:19" ht="75" hidden="1">
       <c r="A31" s="33" t="s">
         <v>151</v>
       </c>
@@ -7293,7 +7330,7 @@
         <v>1.02125</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="62.4" hidden="1">
+    <row r="32" spans="1:19" ht="46.8" hidden="1">
       <c r="A32" s="33" t="s">
         <v>151</v>
       </c>
@@ -7340,7 +7377,7 @@
       <c r="R32" s="40"/>
       <c r="S32" s="44"/>
     </row>
-    <row r="33" spans="1:19" ht="124.8" hidden="1">
+    <row r="33" spans="1:19" ht="105" hidden="1">
       <c r="A33" s="33" t="s">
         <v>151</v>
       </c>
@@ -7389,7 +7426,7 @@
       <c r="R33" s="40"/>
       <c r="S33" s="44"/>
     </row>
-    <row r="34" spans="1:19" ht="140.4" hidden="1">
+    <row r="34" spans="1:19" ht="120" hidden="1">
       <c r="A34" s="33" t="s">
         <v>151</v>
       </c>
@@ -7436,7 +7473,7 @@
       <c r="R34" s="108"/>
       <c r="S34" s="109"/>
     </row>
-    <row r="35" spans="1:19" ht="62.4" hidden="1">
+    <row r="35" spans="1:19" ht="46.8" hidden="1">
       <c r="A35" s="33" t="s">
         <v>151</v>
       </c>
@@ -7524,7 +7561,7 @@
       <c r="R36" s="19"/>
       <c r="S36" s="23"/>
     </row>
-    <row r="37" spans="1:19" ht="62.4" hidden="1">
+    <row r="37" spans="1:19" ht="60" hidden="1">
       <c r="A37" s="80" t="s">
         <v>165</v>
       </c>
@@ -7720,7 +7757,7 @@
         <v>1.099</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="124.8" hidden="1">
+    <row r="41" spans="1:19" ht="105" hidden="1">
       <c r="A41" s="93" t="s">
         <v>177</v>
       </c>
@@ -7779,7 +7816,7 @@
         <v>0.82269999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="93.6" hidden="1">
+    <row r="42" spans="1:19" ht="75" hidden="1">
       <c r="A42" s="93" t="s">
         <v>177</v>
       </c>
@@ -7838,7 +7875,7 @@
         <v>1.3244</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="93.6" hidden="1">
+    <row r="43" spans="1:19" ht="75" hidden="1">
       <c r="A43" s="93" t="s">
         <v>177</v>
       </c>
@@ -7897,7 +7934,7 @@
         <v>1.1175999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="93.6" hidden="1">
+    <row r="44" spans="1:19" ht="90" hidden="1">
       <c r="A44" s="93" t="s">
         <v>177</v>
       </c>
@@ -8205,7 +8242,7 @@
       <c r="R49" s="19"/>
       <c r="S49" s="23"/>
     </row>
-    <row r="50" spans="1:19" ht="109.2" hidden="1">
+    <row r="50" spans="1:19" ht="90" hidden="1">
       <c r="A50" s="80" t="s">
         <v>212</v>
       </c>
@@ -8301,7 +8338,7 @@
       <c r="R51" s="29"/>
       <c r="S51" s="31"/>
     </row>
-    <row r="52" spans="1:19" ht="93.6" hidden="1">
+    <row r="52" spans="1:19" ht="90" hidden="1">
       <c r="A52" s="80" t="s">
         <v>212</v>
       </c>
@@ -8346,7 +8383,7 @@
       <c r="R52" s="131"/>
       <c r="S52" s="23"/>
     </row>
-    <row r="53" spans="1:19" ht="62.4" hidden="1">
+    <row r="53" spans="1:19" ht="60" hidden="1">
       <c r="A53" s="80" t="s">
         <v>212</v>
       </c>
@@ -8393,7 +8430,7 @@
       <c r="R53" s="64"/>
       <c r="S53" s="132"/>
     </row>
-    <row r="54" spans="1:19" ht="93.6" hidden="1">
+    <row r="54" spans="1:19" ht="75" hidden="1">
       <c r="A54" s="80" t="s">
         <v>212</v>
       </c>
@@ -8438,7 +8475,7 @@
       <c r="R54" s="64"/>
       <c r="S54" s="132"/>
     </row>
-    <row r="55" spans="1:19" ht="109.2" hidden="1">
+    <row r="55" spans="1:19" ht="105" hidden="1">
       <c r="A55" s="80" t="s">
         <v>212</v>
       </c>
@@ -8492,7 +8529,7 @@
       <c r="R55" s="19"/>
       <c r="S55" s="23"/>
     </row>
-    <row r="56" spans="1:19" ht="124.8" hidden="1">
+    <row r="56" spans="1:19" ht="105" hidden="1">
       <c r="A56" s="80" t="s">
         <v>212</v>
       </c>
@@ -8533,7 +8570,7 @@
       <c r="R56" s="19"/>
       <c r="S56" s="23"/>
     </row>
-    <row r="57" spans="1:19" ht="93.6" hidden="1">
+    <row r="57" spans="1:19" ht="75" hidden="1">
       <c r="A57" s="80" t="s">
         <v>241</v>
       </c>
@@ -8572,7 +8609,7 @@
       <c r="R57" s="19"/>
       <c r="S57" s="23"/>
     </row>
-    <row r="58" spans="1:19" ht="46.8" hidden="1">
+    <row r="58" spans="1:19" ht="45" hidden="1">
       <c r="A58" s="80" t="s">
         <v>241</v>
       </c>
@@ -8676,7 +8713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="124.8" hidden="1">
+    <row r="60" spans="1:19" ht="109.2" hidden="1">
       <c r="A60" s="80" t="s">
         <v>241</v>
       </c>
@@ -8816,7 +8853,7 @@
       <c r="R62" s="19"/>
       <c r="S62" s="23"/>
     </row>
-    <row r="63" spans="1:19" ht="93.6" hidden="1">
+    <row r="63" spans="1:19" ht="75" hidden="1">
       <c r="A63" s="80" t="s">
         <v>241</v>
       </c>
@@ -8956,7 +8993,7 @@
       <c r="R65" s="29"/>
       <c r="S65" s="31"/>
     </row>
-    <row r="66" spans="1:19" ht="171.6" hidden="1">
+    <row r="66" spans="1:19" ht="150" hidden="1">
       <c r="A66" s="93" t="s">
         <v>266</v>
       </c>

--- a/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/SGIND/data/raw/Plan de mejoramiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="264" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D4FEF24-A07B-4E3F-80B4-33065419E645}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EC4940B-522A-4EE8-95FC-EF5C6EDAAEB3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD3A294A-1D13-4C18-8C58-F237245A6723}"/>
   </bookViews>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="325">
   <si>
     <t>Metas Preliminares</t>
   </si>
@@ -1267,9 +1267,6 @@
     <t>% inversión misionales de la institución</t>
   </si>
   <si>
-    <t>Inversión al plan de mejoramiento</t>
-  </si>
-  <si>
     <t>Infraestructura Física
 Infra estructura Tecnológica
 Contenidos Virtuales
@@ -1322,7 +1319,13 @@
     </r>
   </si>
   <si>
-    <t>Disponibilidad de servicios tecnologicos</t>
+    <t>Gerencia de tecnología</t>
+  </si>
+  <si>
+    <t>Disponibilidad de servicios tecnológicos</t>
+  </si>
+  <si>
+    <t>% Inversión al plan de mejoramiento</t>
   </si>
 </sst>
 </file>
@@ -3383,7 +3386,7 @@
         <v>91</v>
       </c>
       <c r="D17" s="78" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="E17" s="61"/>
       <c r="F17" s="37" t="s">
@@ -3399,7 +3402,7 @@
         <v>41</v>
       </c>
       <c r="J17" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="K17" s="28"/>
       <c r="L17" s="29"/>
@@ -3440,7 +3443,7 @@
         <v>27</v>
       </c>
       <c r="J18" s="66" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K18" s="19" t="s">
         <v>101</v>
@@ -3595,7 +3598,7 @@
         <v>27</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K21" s="18" t="s">
         <v>117</v>
@@ -3739,7 +3742,7 @@
         <v>41</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H24" s="73" t="s">
         <v>41</v>
@@ -5813,7 +5816,9 @@
       <c r="I66" s="19"/>
       <c r="J66" s="19"/>
       <c r="K66" s="19"/>
-      <c r="L66" s="21"/>
+      <c r="L66" s="21" t="s">
+        <v>322</v>
+      </c>
       <c r="M66" s="19"/>
       <c r="N66" s="21">
         <v>0.97</v>

--- a/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/SGIND/data/raw/Plan de mejoramiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="267" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EC4940B-522A-4EE8-95FC-EF5C6EDAAEB3}"/>
+  <xr:revisionPtr revIDLastSave="269" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{710377C6-5A63-446A-8D54-E2DD9448A13A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD3A294A-1D13-4C18-8C58-F237245A6723}"/>
   </bookViews>

--- a/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/SGIND/data/raw/Plan de mejoramiento/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Plan de mejoramiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="269" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{710377C6-5A63-446A-8D54-E2DD9448A13A}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="8_{EDBE0DD7-5DF9-4C9A-8F8F-6CDFE6F49D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A667824F-A795-4523-9BDA-32A3F071BDFB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD3A294A-1D13-4C18-8C58-F237245A6723}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Indicadores Real" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Indicadores Plan de Mejor'!$A$2:$S$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Indicadores Plan de Mejor'!$A$2:$S$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Indicadores Real'!$A$2:$S$67</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -53,7 +53,7 @@
     <comment ref="O11" authorId="0" shapeId="0" xr:uid="{029006E9-4008-49E2-BAEE-4CC12F0054C4}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Colaboradores: 63%
 Estudiantes: 18%
@@ -63,7 +63,7 @@
     <comment ref="O12" authorId="1" shapeId="0" xr:uid="{76CD3EFC-5330-4BD0-A48D-F1E64F16B9AC}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Colaboradores: 2% 
 Estudiantes: 3% 
@@ -87,7 +87,7 @@
     <comment ref="N7" authorId="0" shapeId="0" xr:uid="{FA05611A-1D16-4452-B93C-2E4DFFD86645}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Focus Group
 Estudiantes: 15
@@ -106,7 +106,7 @@
     <comment ref="Q12" authorId="1" shapeId="0" xr:uid="{3F85CAB4-6021-44EC-B795-E932C183C912}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Colaboradores: 63%
 Estudiantes: 18%
@@ -116,7 +116,7 @@
     <comment ref="R47" authorId="2" shapeId="0" xr:uid="{242351BE-3094-4A32-A1BB-45F00F8A6CDF}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Nivel de satisfacción Estudiante Presencial: 100%
 Nivel de satisfacción Estudiante Virtual: 100%
@@ -128,7 +128,7 @@
     <comment ref="R48" authorId="3" shapeId="0" xr:uid="{89AA3457-36D7-4CDB-AC41-C208171F6214}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Nivel de satisfacción Estudiante presencial: 98,1%
 Nivel de satisfacción Estudiante Virtual: 95,4%
@@ -141,7 +141,7 @@
     <comment ref="N64" authorId="4" shapeId="0" xr:uid="{E581DAFC-44AD-42D5-8849-003A27C98076}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     M0:  90% tasa de respuesta
 M1: 9% tasa de respuesta
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="320">
   <si>
     <t>Metas Preliminares</t>
   </si>
@@ -1133,25 +1133,6 @@
   </si>
   <si>
     <t>Director de control interno</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Por definir- Pendiente Implementación de instrumentos
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Inter"/>
-        <family val="2"/>
-      </rPr>
-      <t>Modelo de gestión, evaluación e innovación curricular</t>
-    </r>
-  </si>
-  <si>
-    <t>Valor agregado en la pruebas Saber Pro Institucional</t>
   </si>
   <si>
     <t xml:space="preserve">Nivel de Satisfacción del graduado con la institución </t>
@@ -1207,12 +1188,6 @@
     <t>Se valida con investigación y esta información se reporta completa en ADA y Boletín</t>
   </si>
   <si>
-    <t>Validar con vicerrectoría académica y del estudiante</t>
-  </si>
-  <si>
-    <t>Validar  Indicadores porque se debe medir el impacto a otros grupos de interés</t>
-  </si>
-  <si>
     <t xml:space="preserve">Participación ingresos por extensión (Consultorías, alquiler de espacios, prestación de servicios, centros de investigación entre otros) / total ingresos </t>
   </si>
   <si>
@@ -1225,22 +1200,7 @@
     <t>Índice de impacto Psicosocial de las actividades de bienestar</t>
   </si>
   <si>
-    <t>Proporción de profesores con nivel de formación (Maestría y Doctorado)</t>
-  </si>
-  <si>
     <t>Métrica</t>
-  </si>
-  <si>
-    <t>Gestión docente informa que son métricas no indicadores</t>
-  </si>
-  <si>
-    <t>(N° de profesores con maestría y doctorado / N° total de profesores)*100</t>
-  </si>
-  <si>
-    <t>N° de cupos aprobados para el escalafón docente</t>
-  </si>
-  <si>
-    <t>(N° de profesores con escalafón docente/N° de cupos aprobados para el escalafón docente)*100</t>
   </si>
   <si>
     <t>Tasa de empleabilidad de recién graduados de pregrado</t>
@@ -1327,6 +1287,69 @@
   <si>
     <t>% Inversión al plan de mejoramiento</t>
   </si>
+  <si>
+    <t>Definición de indicador asociado a la constitución del Modelo de evaluación del aprendizaje en la institución</t>
+  </si>
+  <si>
+    <t>Resultados Institucionales Prueba Saber Pro</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Validar con 
+Educacion continua, prácticas
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Inter"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Línea de educación e innovación
+Impacto Social y desarrollo comunitario
+Emprendimiento y Promoción de la empleabilidad
+Investigación y transferencia de conocimiento</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF002060"/>
+        <rFont val="Inter"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Se enviará formulario de caracterización de acciones de extensión, analisis de capitalización de recursos y  se establecerá comite extensión</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Inter"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">% de Participación de graduados en actividades de empleabilidad y relacionamiento de los ultimos 5 años
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF002060"/>
+        <rFont val="Inter"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Eje (Empleabilidad, relacionamiento, seguimiento al graduado.)
+Actividad (Emprendimiento, formación etc.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1337,7 +1360,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1506,8 +1529,15 @@
       <name val="Inter"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="Inter"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1628,6 +1658,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -1731,7 +1767,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2177,6 +2213,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2586,8 +2625,8 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:S66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S63"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.5546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="30.88671875" style="2" customWidth="1"/>
@@ -2603,7 +2642,7 @@
     <col min="20" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="46.2" customHeight="1">
+    <row r="1" spans="1:19" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2626,7 +2665,7 @@
       <c r="R1" s="147"/>
       <c r="S1" s="147"/>
     </row>
-    <row r="2" spans="1:19" ht="31.2">
+    <row r="2" spans="1:19" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2643,7 +2682,7 @@
         <v>5</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>7</v>
@@ -2685,7 +2724,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="75">
+    <row r="3" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>20</v>
       </c>
@@ -2740,7 +2779,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="62.4">
+    <row r="4" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>20</v>
       </c>
@@ -2793,7 +2832,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="46.8">
+    <row r="5" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>20</v>
       </c>
@@ -2811,7 +2850,7 @@
         <v>41</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>41</v>
@@ -2836,7 +2875,7 @@
       <c r="R5" s="29"/>
       <c r="S5" s="29"/>
     </row>
-    <row r="6" spans="1:19" ht="69" customHeight="1">
+    <row r="6" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>20</v>
       </c>
@@ -2854,7 +2893,7 @@
         <v>41</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>41</v>
@@ -2864,7 +2903,7 @@
       </c>
       <c r="J6" s="28"/>
       <c r="K6" s="28" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="L6" s="29" t="s">
         <v>46</v>
@@ -2879,7 +2918,7 @@
       <c r="R6" s="29"/>
       <c r="S6" s="29"/>
     </row>
-    <row r="7" spans="1:19" ht="93.6">
+    <row r="7" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A7" s="32" t="s">
         <v>47</v>
       </c>
@@ -2914,7 +2953,7 @@
       <c r="R7" s="40"/>
       <c r="S7" s="40"/>
     </row>
-    <row r="8" spans="1:19" ht="75">
+    <row r="8" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
         <v>47</v>
       </c>
@@ -2971,7 +3010,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="46.8">
+    <row r="9" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A9" s="32" t="s">
         <v>47</v>
       </c>
@@ -3026,7 +3065,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="60">
+    <row r="10" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
         <v>47</v>
       </c>
@@ -3053,7 +3092,7 @@
         <v>27</v>
       </c>
       <c r="J10" s="39" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="K10" s="39" t="s">
         <v>69</v>
@@ -3073,7 +3112,7 @@
       <c r="R10" s="40"/>
       <c r="S10" s="40"/>
     </row>
-    <row r="11" spans="1:19" ht="45">
+    <row r="11" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A11" s="56" t="s">
         <v>71</v>
       </c>
@@ -3130,7 +3169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="60">
+    <row r="12" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A12" s="56" t="s">
         <v>71</v>
       </c>
@@ -3185,7 +3224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="31.2">
+    <row r="13" spans="1:19" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A13" s="56" t="s">
         <v>71</v>
       </c>
@@ -3242,7 +3281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="31.2">
+    <row r="14" spans="1:19" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A14" s="56" t="s">
         <v>71</v>
       </c>
@@ -3285,7 +3324,7 @@
       <c r="R14" s="19"/>
       <c r="S14" s="19"/>
     </row>
-    <row r="15" spans="1:19" ht="31.2">
+    <row r="15" spans="1:19" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A15" s="56" t="s">
         <v>71</v>
       </c>
@@ -3338,7 +3377,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="46.8">
+    <row r="16" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A16" s="56" t="s">
         <v>71</v>
       </c>
@@ -3349,7 +3388,7 @@
         <v>91</v>
       </c>
       <c r="D16" s="77" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="E16" s="61"/>
       <c r="F16" s="37" t="s">
@@ -3375,7 +3414,7 @@
       <c r="R16" s="19"/>
       <c r="S16" s="19"/>
     </row>
-    <row r="17" spans="1:19" ht="150">
+    <row r="17" spans="1:19" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A17" s="56" t="s">
         <v>71</v>
       </c>
@@ -3386,7 +3425,7 @@
         <v>91</v>
       </c>
       <c r="D17" s="78" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="E17" s="61"/>
       <c r="F17" s="37" t="s">
@@ -3402,7 +3441,7 @@
         <v>41</v>
       </c>
       <c r="J17" s="28" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="K17" s="28"/>
       <c r="L17" s="29"/>
@@ -3416,7 +3455,7 @@
       <c r="R17" s="29"/>
       <c r="S17" s="29"/>
     </row>
-    <row r="18" spans="1:19" ht="120">
+    <row r="18" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A18" s="79" t="s">
         <v>96</v>
       </c>
@@ -3443,7 +3482,7 @@
         <v>27</v>
       </c>
       <c r="J18" s="66" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="K18" s="19" t="s">
         <v>101</v>
@@ -3471,7 +3510,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="75">
+    <row r="19" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A19" s="79" t="s">
         <v>96</v>
       </c>
@@ -3524,7 +3563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="62.4">
+    <row r="20" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A20" s="79" t="s">
         <v>96</v>
       </c>
@@ -3569,7 +3608,7 @@
       <c r="R20" s="19"/>
       <c r="S20" s="19"/>
     </row>
-    <row r="21" spans="1:19" ht="60">
+    <row r="21" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A21" s="79" t="s">
         <v>96</v>
       </c>
@@ -3598,7 +3637,7 @@
         <v>27</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="K21" s="18" t="s">
         <v>117</v>
@@ -3628,7 +3667,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="46.8">
+    <row r="22" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A22" s="79" t="s">
         <v>96</v>
       </c>
@@ -3675,7 +3714,7 @@
       <c r="R22" s="19"/>
       <c r="S22" s="19"/>
     </row>
-    <row r="23" spans="1:19" ht="46.8">
+    <row r="23" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A23" s="79" t="s">
         <v>96</v>
       </c>
@@ -3724,7 +3763,7 @@
       <c r="R23" s="19"/>
       <c r="S23" s="19"/>
     </row>
-    <row r="24" spans="1:19" ht="218.4">
+    <row r="24" spans="1:19" ht="218.4" x14ac:dyDescent="0.3">
       <c r="A24" s="79" t="s">
         <v>130</v>
       </c>
@@ -3735,14 +3774,14 @@
         <v>132</v>
       </c>
       <c r="D24" s="142" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="E24" s="17"/>
       <c r="F24" s="62" t="s">
         <v>41</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="H24" s="73" t="s">
         <v>41</v>
@@ -3753,7 +3792,7 @@
       <c r="J24" s="63"/>
       <c r="K24" s="29"/>
       <c r="L24" s="29" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M24" s="94"/>
       <c r="N24" s="63"/>
@@ -3763,7 +3802,7 @@
       <c r="R24" s="29"/>
       <c r="S24" s="29"/>
     </row>
-    <row r="25" spans="1:19" ht="124.8">
+    <row r="25" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A25" s="79" t="s">
         <v>130</v>
       </c>
@@ -3774,14 +3813,14 @@
         <v>132</v>
       </c>
       <c r="D25" s="142" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E25" s="17"/>
       <c r="F25" s="62" t="s">
         <v>41</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H25" s="73" t="s">
         <v>41</v>
@@ -3792,7 +3831,7 @@
       <c r="J25" s="63"/>
       <c r="K25" s="29"/>
       <c r="L25" s="29" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M25" s="94"/>
       <c r="N25" s="63"/>
@@ -3802,7 +3841,7 @@
       <c r="R25" s="29"/>
       <c r="S25" s="29"/>
     </row>
-    <row r="26" spans="1:19" ht="93.6">
+    <row r="26" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A26" s="79" t="s">
         <v>130</v>
       </c>
@@ -3813,14 +3852,14 @@
         <v>136</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="E26" s="17"/>
       <c r="F26" s="62" t="s">
         <v>41</v>
       </c>
       <c r="G26" s="82" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H26" s="73" t="s">
         <v>41</v>
@@ -3847,7 +3886,7 @@
       <c r="R26" s="19"/>
       <c r="S26" s="19"/>
     </row>
-    <row r="27" spans="1:19" ht="60">
+    <row r="27" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A27" s="79" t="s">
         <v>130</v>
       </c>
@@ -3900,7 +3939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="62.4">
+    <row r="28" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A28" s="79" t="s">
         <v>130</v>
       </c>
@@ -3955,7 +3994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="62.4">
+    <row r="29" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A29" s="79" t="s">
         <v>130</v>
       </c>
@@ -4010,7 +4049,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="75">
+    <row r="30" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A30" s="33" t="s">
         <v>151</v>
       </c>
@@ -4030,7 +4069,7 @@
         <v>24</v>
       </c>
       <c r="G30" s="35" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H30" s="36" t="s">
         <v>55</v>
@@ -4069,7 +4108,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="46.8">
+    <row r="31" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A31" s="33" t="s">
         <v>151</v>
       </c>
@@ -4122,7 +4161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="105">
+    <row r="32" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A32" s="33" t="s">
         <v>151</v>
       </c>
@@ -4177,7 +4216,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="120">
+    <row r="33" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A33" s="33" t="s">
         <v>151</v>
       </c>
@@ -4230,7 +4269,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="46.8">
+    <row r="34" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A34" s="33" t="s">
         <v>151</v>
       </c>
@@ -4285,7 +4324,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="124.8">
+    <row r="35" spans="1:19" ht="296.39999999999998" x14ac:dyDescent="0.3">
       <c r="A35" s="80" t="s">
         <v>165</v>
       </c>
@@ -4302,8 +4341,8 @@
       <c r="F35" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="G35" s="82" t="s">
-        <v>298</v>
+      <c r="G35" s="95" t="s">
+        <v>318</v>
       </c>
       <c r="H35" s="73" t="s">
         <v>41</v>
@@ -4324,7 +4363,7 @@
       <c r="R35" s="19"/>
       <c r="S35" s="19"/>
     </row>
-    <row r="36" spans="1:19" ht="60">
+    <row r="36" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A36" s="80" t="s">
         <v>165</v>
       </c>
@@ -4334,15 +4373,15 @@
       <c r="C36" s="80" t="s">
         <v>171</v>
       </c>
-      <c r="D36" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="E36" s="17"/>
+      <c r="D36" s="115" t="s">
+        <v>296</v>
+      </c>
+      <c r="E36" s="116"/>
       <c r="F36" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="G36" s="82" t="s">
-        <v>299</v>
+      <c r="G36" s="17" t="s">
+        <v>176</v>
       </c>
       <c r="H36" s="73" t="s">
         <v>41</v>
@@ -4350,88 +4389,106 @@
       <c r="I36" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J36" s="66" t="s">
-        <v>174</v>
-      </c>
-      <c r="K36" s="19"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
       <c r="L36" s="19"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="66"/>
+      <c r="M36" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="N36" s="19"/>
       <c r="O36" s="19"/>
       <c r="P36" s="19"/>
       <c r="Q36" s="19"/>
       <c r="R36" s="19"/>
       <c r="S36" s="19"/>
     </row>
-    <row r="37" spans="1:19" ht="93.6">
-      <c r="A37" s="80" t="s">
-        <v>165</v>
-      </c>
-      <c r="B37" s="98" t="s">
-        <v>166</v>
-      </c>
-      <c r="C37" s="80" t="s">
-        <v>171</v>
-      </c>
-      <c r="D37" s="115" t="s">
-        <v>300</v>
-      </c>
-      <c r="E37" s="116"/>
-      <c r="F37" s="73" t="s">
-        <v>24</v>
-      </c>
-      <c r="G37" s="73" t="s">
-        <v>176</v>
-      </c>
-      <c r="H37" s="73" t="s">
-        <v>41</v>
+    <row r="37" spans="1:19" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="93" t="s">
+        <v>177</v>
+      </c>
+      <c r="B37" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="C37" s="93" t="s">
+        <v>179</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="E37" s="17">
+        <v>318</v>
+      </c>
+      <c r="F37" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G37" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>55</v>
       </c>
       <c r="I37" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="34" t="s">
+      <c r="J37" s="63" t="s">
+        <v>297</v>
+      </c>
+      <c r="K37" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="L37" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="M37" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="N37" s="19"/>
-      <c r="O37" s="19"/>
-      <c r="P37" s="19"/>
-      <c r="Q37" s="19"/>
-      <c r="R37" s="19"/>
-      <c r="S37" s="19"/>
-    </row>
-    <row r="38" spans="1:19" ht="46.95" customHeight="1">
+      <c r="N37" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="O37" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="P37" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="Q37" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="R37" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="S37" s="120">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A38" s="93" t="s">
         <v>177</v>
       </c>
-      <c r="B38" s="117" t="s">
+      <c r="B38" s="119" t="s">
         <v>178</v>
       </c>
-      <c r="C38" s="93" t="s">
-        <v>179</v>
-      </c>
-      <c r="D38" s="27" t="s">
-        <v>180</v>
+      <c r="C38" s="113" t="s">
+        <v>181</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>182</v>
       </c>
       <c r="E38" s="17">
-        <v>318</v>
+        <v>532</v>
       </c>
       <c r="F38" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="G38" s="27" t="s">
-        <v>63</v>
-      </c>
+      <c r="G38" s="16"/>
       <c r="H38" s="16" t="s">
         <v>55</v>
       </c>
       <c r="I38" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J38" s="63" t="s">
-        <v>301</v>
+      <c r="J38" s="66" t="s">
+        <v>183</v>
       </c>
       <c r="K38" s="19" t="s">
         <v>184</v>
@@ -4442,40 +4499,40 @@
       <c r="M38" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="N38" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="O38" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="P38" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="Q38" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="R38" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="S38" s="120">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="62.4">
+      <c r="N38" s="64">
+        <v>1</v>
+      </c>
+      <c r="O38" s="64">
+        <v>1</v>
+      </c>
+      <c r="P38" s="64">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="64">
+        <v>1</v>
+      </c>
+      <c r="R38" s="64">
+        <v>1</v>
+      </c>
+      <c r="S38" s="64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A39" s="93" t="s">
         <v>177</v>
       </c>
-      <c r="B39" s="119" t="s">
-        <v>178</v>
-      </c>
-      <c r="C39" s="113" t="s">
+      <c r="B39" s="98" t="s">
+        <v>185</v>
+      </c>
+      <c r="C39" s="80" t="s">
         <v>181</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E39" s="17">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F39" s="27" t="s">
         <v>24</v>
@@ -4488,7 +4545,7 @@
         <v>27</v>
       </c>
       <c r="J39" s="66" t="s">
-        <v>183</v>
+        <v>298</v>
       </c>
       <c r="K39" s="19" t="s">
         <v>184</v>
@@ -4496,8 +4553,8 @@
       <c r="L39" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="M39" s="94" t="s">
-        <v>50</v>
+      <c r="M39" s="34" t="s">
+        <v>43</v>
       </c>
       <c r="N39" s="64">
         <v>1</v>
@@ -4518,7 +4575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="90">
+    <row r="40" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A40" s="93" t="s">
         <v>177</v>
       </c>
@@ -4529,10 +4586,10 @@
         <v>181</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E40" s="17">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F40" s="27" t="s">
         <v>24</v>
@@ -4544,8 +4601,8 @@
       <c r="I40" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J40" s="66" t="s">
-        <v>302</v>
+      <c r="J40" s="18" t="s">
+        <v>189</v>
       </c>
       <c r="K40" s="19" t="s">
         <v>184</v>
@@ -4575,7 +4632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="75">
+    <row r="41" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A41" s="93" t="s">
         <v>177</v>
       </c>
@@ -4586,10 +4643,10 @@
         <v>181</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E41" s="17">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F41" s="27" t="s">
         <v>24</v>
@@ -4602,7 +4659,7 @@
         <v>27</v>
       </c>
       <c r="J41" s="18" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K41" s="19" t="s">
         <v>184</v>
@@ -4632,7 +4689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="75">
+    <row r="42" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A42" s="93" t="s">
         <v>177</v>
       </c>
@@ -4643,10 +4700,10 @@
         <v>181</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E42" s="17">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F42" s="27" t="s">
         <v>24</v>
@@ -4659,7 +4716,7 @@
         <v>27</v>
       </c>
       <c r="J42" s="18" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K42" s="19" t="s">
         <v>184</v>
@@ -4689,81 +4746,67 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="90">
+    <row r="43" spans="1:19" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="93" t="s">
-        <v>177</v>
-      </c>
-      <c r="B43" s="98" t="s">
-        <v>185</v>
-      </c>
-      <c r="C43" s="80" t="s">
-        <v>181</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E43" s="17">
-        <v>536</v>
-      </c>
-      <c r="F43" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="I43" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="J43" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="K43" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="L43" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="M43" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="N43" s="64">
-        <v>1</v>
-      </c>
-      <c r="O43" s="64">
-        <v>1</v>
-      </c>
-      <c r="P43" s="64">
-        <v>1</v>
-      </c>
-      <c r="Q43" s="64">
-        <v>1</v>
-      </c>
-      <c r="R43" s="64">
-        <v>1</v>
-      </c>
-      <c r="S43" s="64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="88.8" customHeight="1">
-      <c r="A44" s="93" t="s">
         <v>194</v>
       </c>
-      <c r="B44" s="117" t="s">
+      <c r="B43" s="117" t="s">
         <v>195</v>
       </c>
-      <c r="C44" s="93" t="s">
+      <c r="C43" s="93" t="s">
         <v>196</v>
       </c>
-      <c r="D44" s="26" t="s">
+      <c r="D43" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="E44" s="17"/>
-      <c r="F44" s="62" t="s">
-        <v>24</v>
-      </c>
-      <c r="G44" s="95" t="s">
+      <c r="E43" s="17"/>
+      <c r="F43" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="95" t="s">
+        <v>63</v>
+      </c>
+      <c r="H43" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I43" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="J43" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="M43" s="94"/>
+      <c r="N43" s="63"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="29"/>
+      <c r="S43" s="29"/>
+    </row>
+    <row r="44" spans="1:19" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="80" t="s">
+        <v>194</v>
+      </c>
+      <c r="B44" s="98" t="s">
+        <v>195</v>
+      </c>
+      <c r="C44" s="80" t="s">
+        <v>196</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="E44" s="17">
+        <v>597</v>
+      </c>
+      <c r="F44" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="G44" s="82" t="s">
         <v>63</v>
       </c>
       <c r="H44" s="73" t="s">
@@ -4772,67 +4815,73 @@
       <c r="I44" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="J44" s="63" t="s">
-        <v>198</v>
-      </c>
-      <c r="K44" s="29"/>
-      <c r="L44" s="29" t="s">
+      <c r="J44" s="66" t="s">
+        <v>201</v>
+      </c>
+      <c r="K44" s="19"/>
+      <c r="L44" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="M44" s="94"/>
-      <c r="N44" s="63"/>
-      <c r="O44" s="29"/>
-      <c r="P44" s="29"/>
-      <c r="Q44" s="29"/>
-      <c r="R44" s="29"/>
-      <c r="S44" s="29"/>
-    </row>
-    <row r="45" spans="1:19" ht="130.80000000000001" customHeight="1">
-      <c r="A45" s="80" t="s">
+      <c r="M44" s="34"/>
+      <c r="N44" s="66"/>
+      <c r="O44" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="P44" s="19"/>
+      <c r="Q44" s="19"/>
+      <c r="R44" s="19"/>
+      <c r="S44" s="19"/>
+    </row>
+    <row r="45" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="93" t="s">
         <v>194</v>
       </c>
-      <c r="B45" s="98" t="s">
+      <c r="B45" s="117" t="s">
         <v>195</v>
       </c>
-      <c r="C45" s="80" t="s">
-        <v>196</v>
+      <c r="C45" s="93" t="s">
+        <v>202</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>303</v>
+        <v>203</v>
       </c>
       <c r="E45" s="17">
-        <v>597</v>
+        <v>500</v>
       </c>
       <c r="F45" s="73" t="s">
         <v>24</v>
       </c>
       <c r="G45" s="82" t="s">
-        <v>63</v>
-      </c>
-      <c r="H45" s="73" t="s">
-        <v>41</v>
+        <v>204</v>
+      </c>
+      <c r="H45" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="I45" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="J45" s="66" t="s">
-        <v>201</v>
-      </c>
-      <c r="K45" s="19"/>
-      <c r="L45" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="M45" s="34"/>
-      <c r="N45" s="66"/>
-      <c r="O45" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="P45" s="19"/>
-      <c r="Q45" s="19"/>
-      <c r="R45" s="19"/>
-      <c r="S45" s="19"/>
-    </row>
-    <row r="46" spans="1:19" ht="132.6" customHeight="1">
+      <c r="J45" s="63" t="s">
+        <v>205</v>
+      </c>
+      <c r="K45" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="L45" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="M45" s="94"/>
+      <c r="N45" s="120">
+        <v>0.8</v>
+      </c>
+      <c r="O45" s="122">
+        <v>0.85</v>
+      </c>
+      <c r="P45" s="29"/>
+      <c r="Q45" s="29"/>
+      <c r="R45" s="29"/>
+      <c r="S45" s="29"/>
+    </row>
+    <row r="46" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="93" t="s">
         <v>194</v>
       </c>
@@ -4843,11 +4892,9 @@
         <v>202</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="E46" s="17">
-        <v>500</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="E46" s="17"/>
       <c r="F46" s="73" t="s">
         <v>24</v>
       </c>
@@ -4867,7 +4914,7 @@
         <v>206</v>
       </c>
       <c r="L46" s="29" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M46" s="94"/>
       <c r="N46" s="120">
@@ -4881,114 +4928,124 @@
       <c r="R46" s="29"/>
       <c r="S46" s="29"/>
     </row>
-    <row r="47" spans="1:19" ht="132.6" customHeight="1">
-      <c r="A47" s="93" t="s">
+    <row r="47" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="80" t="s">
         <v>194</v>
       </c>
-      <c r="B47" s="117" t="s">
+      <c r="B47" s="98" t="s">
         <v>195</v>
       </c>
-      <c r="C47" s="93" t="s">
+      <c r="C47" s="80" t="s">
         <v>202</v>
       </c>
-      <c r="D47" s="17" t="s">
-        <v>208</v>
+      <c r="D47" s="16" t="s">
+        <v>210</v>
       </c>
       <c r="E47" s="17"/>
       <c r="F47" s="73" t="s">
         <v>24</v>
       </c>
       <c r="G47" s="82" t="s">
-        <v>204</v>
-      </c>
-      <c r="H47" s="17" t="s">
-        <v>26</v>
+        <v>63</v>
+      </c>
+      <c r="H47" s="73" t="s">
+        <v>41</v>
       </c>
       <c r="I47" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="J47" s="63" t="s">
-        <v>205</v>
-      </c>
-      <c r="K47" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="L47" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="M47" s="94"/>
-      <c r="N47" s="120">
-        <v>0.8</v>
-      </c>
-      <c r="O47" s="122">
-        <v>0.85</v>
-      </c>
-      <c r="P47" s="29"/>
-      <c r="Q47" s="29"/>
-      <c r="R47" s="29"/>
-      <c r="S47" s="29"/>
-    </row>
-    <row r="48" spans="1:19" ht="93.6">
+      <c r="J47" s="114" t="s">
+        <v>211</v>
+      </c>
+      <c r="K47" s="19"/>
+      <c r="L47" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="M47" s="34"/>
+      <c r="N47" s="66"/>
+      <c r="O47" s="19"/>
+      <c r="P47" s="19"/>
+      <c r="Q47" s="19"/>
+      <c r="R47" s="19"/>
+      <c r="S47" s="19"/>
+    </row>
+    <row r="48" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A48" s="80" t="s">
-        <v>194</v>
-      </c>
-      <c r="B48" s="98" t="s">
-        <v>195</v>
-      </c>
-      <c r="C48" s="80" t="s">
-        <v>202</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="E48" s="17"/>
-      <c r="F48" s="73" t="s">
-        <v>24</v>
-      </c>
-      <c r="G48" s="82" t="s">
+        <v>212</v>
+      </c>
+      <c r="B48" s="125" t="s">
+        <v>213</v>
+      </c>
+      <c r="C48" s="126" t="s">
+        <v>214</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="E48" s="17">
+        <v>576</v>
+      </c>
+      <c r="F48" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" s="73" t="s">
         <v>63</v>
       </c>
       <c r="H48" s="73" t="s">
-        <v>41</v>
-      </c>
-      <c r="I48" s="62" t="s">
-        <v>27</v>
-      </c>
-      <c r="J48" s="114" t="s">
-        <v>211</v>
-      </c>
-      <c r="K48" s="19"/>
+        <v>55</v>
+      </c>
+      <c r="I48" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J48" s="66" t="s">
+        <v>216</v>
+      </c>
+      <c r="K48" s="19" t="s">
+        <v>129</v>
+      </c>
       <c r="L48" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="M48" s="34"/>
-      <c r="N48" s="66"/>
-      <c r="O48" s="19"/>
-      <c r="P48" s="19"/>
-      <c r="Q48" s="19"/>
-      <c r="R48" s="19"/>
-      <c r="S48" s="19"/>
-    </row>
-    <row r="49" spans="1:19" ht="90">
-      <c r="A49" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="M48" s="127"/>
+      <c r="N48" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="O48" s="21">
+        <v>1</v>
+      </c>
+      <c r="P48" s="21">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="21">
+        <v>1</v>
+      </c>
+      <c r="R48" s="21">
+        <v>1</v>
+      </c>
+      <c r="S48" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="B49" s="125" t="s">
-        <v>213</v>
-      </c>
-      <c r="C49" s="126" t="s">
-        <v>214</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>215</v>
+      <c r="B49" s="93" t="s">
+        <v>217</v>
+      </c>
+      <c r="C49" s="128" t="s">
+        <v>218</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>219</v>
       </c>
       <c r="E49" s="17">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="F49" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="G49" s="73" t="s">
+      <c r="G49" s="95" t="s">
         <v>63</v>
       </c>
       <c r="H49" s="73" t="s">
@@ -4997,56 +5054,54 @@
       <c r="I49" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="J49" s="66" t="s">
-        <v>216</v>
-      </c>
-      <c r="K49" s="19" t="s">
+      <c r="J49" s="63" t="s">
+        <v>220</v>
+      </c>
+      <c r="K49" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="L49" s="19" t="s">
+      <c r="L49" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="M49" s="127"/>
-      <c r="N49" s="66" t="s">
-        <v>51</v>
-      </c>
-      <c r="O49" s="21">
-        <v>1</v>
-      </c>
-      <c r="P49" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q49" s="21">
-        <v>1</v>
-      </c>
-      <c r="R49" s="21">
-        <v>1</v>
-      </c>
-      <c r="S49" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" ht="78" customHeight="1">
-      <c r="A50" s="93" t="s">
+      <c r="M49" s="129"/>
+      <c r="N49" s="63"/>
+      <c r="O49" s="29">
+        <v>112</v>
+      </c>
+      <c r="P49" s="29">
+        <v>99</v>
+      </c>
+      <c r="Q49" s="29">
+        <v>88</v>
+      </c>
+      <c r="R49" s="29">
+        <v>75</v>
+      </c>
+      <c r="S49" s="29">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="80" t="s">
         <v>212</v>
       </c>
-      <c r="B50" s="93" t="s">
-        <v>217</v>
-      </c>
-      <c r="C50" s="128" t="s">
-        <v>218</v>
-      </c>
-      <c r="D50" s="26" t="s">
-        <v>219</v>
+      <c r="B50" s="98" t="s">
+        <v>232</v>
+      </c>
+      <c r="C50" s="80" t="s">
+        <v>233</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>234</v>
       </c>
       <c r="E50" s="17">
-        <v>573</v>
-      </c>
-      <c r="F50" s="62" t="s">
-        <v>24</v>
-      </c>
-      <c r="G50" s="95" t="s">
-        <v>63</v>
+        <v>460</v>
+      </c>
+      <c r="F50" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="G50" s="73" t="s">
+        <v>88</v>
       </c>
       <c r="H50" s="73" t="s">
         <v>55</v>
@@ -5054,107 +5109,95 @@
       <c r="I50" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="J50" s="63" t="s">
-        <v>220</v>
-      </c>
-      <c r="K50" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="L50" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="M50" s="129"/>
-      <c r="N50" s="63"/>
-      <c r="O50" s="29">
-        <v>112</v>
-      </c>
-      <c r="P50" s="29">
-        <v>99</v>
-      </c>
-      <c r="Q50" s="29">
-        <v>88</v>
-      </c>
-      <c r="R50" s="29">
-        <v>75</v>
-      </c>
-      <c r="S50" s="29">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="60">
+      <c r="J50" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="K50" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="L50" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="M50" s="34"/>
+      <c r="N50" s="64">
+        <v>0.8</v>
+      </c>
+      <c r="O50" s="21">
+        <v>0.82</v>
+      </c>
+      <c r="P50" s="21">
+        <v>0.83</v>
+      </c>
+      <c r="Q50" s="21">
+        <v>0.83</v>
+      </c>
+      <c r="R50" s="21">
+        <v>0.84</v>
+      </c>
+      <c r="S50" s="21">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A51" s="80" t="s">
         <v>212</v>
       </c>
-      <c r="B51" s="80" t="s">
-        <v>217</v>
-      </c>
-      <c r="C51" s="126" t="s">
-        <v>218</v>
-      </c>
-      <c r="D51" s="88" t="s">
-        <v>304</v>
-      </c>
-      <c r="E51" s="88"/>
-      <c r="F51" s="89" t="s">
-        <v>305</v>
-      </c>
-      <c r="G51" s="89" t="s">
+      <c r="B51" s="98" t="s">
+        <v>237</v>
+      </c>
+      <c r="C51" s="80" t="s">
+        <v>238</v>
+      </c>
+      <c r="D51" s="73" t="s">
+        <v>239</v>
+      </c>
+      <c r="E51" s="17"/>
+      <c r="F51" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="G51" s="73" t="s">
         <v>63</v>
       </c>
       <c r="H51" s="73" t="s">
-        <v>306</v>
+        <v>41</v>
       </c>
       <c r="I51" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="J51" s="130" t="s">
-        <v>307</v>
-      </c>
-      <c r="K51" s="131" t="s">
-        <v>129</v>
-      </c>
-      <c r="L51" s="131" t="s">
-        <v>129</v>
-      </c>
-      <c r="M51" s="127"/>
-      <c r="N51" s="64">
-        <v>0.8</v>
-      </c>
-      <c r="O51" s="64">
-        <v>0.8</v>
-      </c>
-      <c r="P51" s="64">
-        <v>0.8</v>
-      </c>
-      <c r="Q51" s="64">
-        <v>0.8</v>
-      </c>
-      <c r="R51" s="64">
-        <v>0.8</v>
-      </c>
-      <c r="S51" s="64">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" ht="75">
+      <c r="J51" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="K51" s="19"/>
+      <c r="L51" s="19"/>
+      <c r="M51" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="N51" s="66"/>
+      <c r="O51" s="19"/>
+      <c r="P51" s="19"/>
+      <c r="Q51" s="19"/>
+      <c r="R51" s="19"/>
+      <c r="S51" s="19"/>
+    </row>
+    <row r="52" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A52" s="80" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="B52" s="98" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="C52" s="80" t="s">
-        <v>228</v>
-      </c>
-      <c r="D52" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="E52" s="17"/>
-      <c r="F52" s="73" t="s">
-        <v>41</v>
-      </c>
-      <c r="G52" s="73" t="s">
-        <v>230</v>
+        <v>243</v>
+      </c>
+      <c r="D52" s="116" t="s">
+        <v>244</v>
+      </c>
+      <c r="E52" s="116"/>
+      <c r="F52" s="134" t="s">
+        <v>24</v>
+      </c>
+      <c r="G52" s="134" t="s">
+        <v>63</v>
       </c>
       <c r="H52" s="73" t="s">
         <v>41</v>
@@ -5163,162 +5206,152 @@
         <v>27</v>
       </c>
       <c r="J52" s="66" t="s">
-        <v>309</v>
+        <v>244</v>
       </c>
       <c r="K52" s="19"/>
-      <c r="L52" s="19" t="s">
-        <v>129</v>
-      </c>
+      <c r="L52" s="19"/>
       <c r="M52" s="34"/>
-      <c r="N52" s="64">
-        <v>1</v>
-      </c>
-      <c r="O52" s="64">
-        <v>1</v>
-      </c>
-      <c r="P52" s="64">
-        <v>1</v>
-      </c>
-      <c r="Q52" s="64">
-        <v>1</v>
-      </c>
-      <c r="R52" s="64">
-        <v>1</v>
-      </c>
-      <c r="S52" s="64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" ht="105">
+      <c r="N52" s="66"/>
+      <c r="O52" s="19"/>
+      <c r="P52" s="19"/>
+      <c r="Q52" s="19"/>
+      <c r="R52" s="19"/>
+      <c r="S52" s="19"/>
+    </row>
+    <row r="53" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A53" s="80" t="s">
-        <v>212</v>
-      </c>
-      <c r="B53" s="98" t="s">
-        <v>232</v>
+        <v>241</v>
+      </c>
+      <c r="B53" s="80" t="s">
+        <v>245</v>
       </c>
       <c r="C53" s="80" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="E53" s="17">
-        <v>460</v>
-      </c>
-      <c r="F53" s="73" t="s">
-        <v>24</v>
-      </c>
-      <c r="G53" s="73" t="s">
-        <v>88</v>
+        <v>553</v>
+      </c>
+      <c r="F53" s="134" t="s">
+        <v>24</v>
+      </c>
+      <c r="G53" s="82" t="s">
+        <v>63</v>
       </c>
       <c r="H53" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I53" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J53" s="66" t="s">
+        <v>248</v>
+      </c>
+      <c r="K53" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="L53" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="M53" s="34"/>
+      <c r="N53" s="66"/>
+      <c r="O53" s="21">
+        <v>0.85</v>
+      </c>
+      <c r="P53" s="19"/>
+      <c r="Q53" s="19"/>
+      <c r="R53" s="19"/>
+      <c r="S53" s="19"/>
+    </row>
+    <row r="54" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="80" t="s">
+        <v>241</v>
+      </c>
+      <c r="B54" s="80" t="s">
+        <v>245</v>
+      </c>
+      <c r="C54" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="E54" s="17"/>
+      <c r="F54" s="134" t="s">
+        <v>24</v>
+      </c>
+      <c r="G54" s="82" t="s">
+        <v>63</v>
+      </c>
+      <c r="H54" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="I53" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="J53" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="K53" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="L53" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="M53" s="34"/>
-      <c r="N53" s="64">
-        <v>0.8</v>
-      </c>
-      <c r="O53" s="21">
-        <v>0.82</v>
-      </c>
-      <c r="P53" s="21">
-        <v>0.83</v>
-      </c>
-      <c r="Q53" s="21">
-        <v>0.83</v>
-      </c>
-      <c r="R53" s="21">
-        <v>0.84</v>
-      </c>
-      <c r="S53" s="21">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" ht="105">
-      <c r="A54" s="80" t="s">
-        <v>212</v>
-      </c>
-      <c r="B54" s="98" t="s">
-        <v>237</v>
-      </c>
-      <c r="C54" s="80" t="s">
-        <v>238</v>
-      </c>
-      <c r="D54" s="73" t="s">
-        <v>239</v>
-      </c>
-      <c r="E54" s="17"/>
-      <c r="F54" s="73" t="s">
-        <v>41</v>
-      </c>
-      <c r="G54" s="73" t="s">
-        <v>63</v>
-      </c>
-      <c r="H54" s="73" t="s">
-        <v>41</v>
-      </c>
       <c r="I54" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="J54" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="K54" s="19"/>
-      <c r="L54" s="19"/>
-      <c r="M54" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="N54" s="66"/>
-      <c r="O54" s="19"/>
+      <c r="J54" s="66" t="s">
+        <v>253</v>
+      </c>
+      <c r="K54" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="L54" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="M54" s="136" t="s">
+        <v>255</v>
+      </c>
+      <c r="N54" s="65">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="O54" s="145">
+        <v>0.86599999999999999</v>
+      </c>
       <c r="P54" s="19"/>
       <c r="Q54" s="19"/>
       <c r="R54" s="19"/>
       <c r="S54" s="19"/>
     </row>
-    <row r="55" spans="1:19" ht="75">
+    <row r="55" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A55" s="80" t="s">
         <v>241</v>
       </c>
-      <c r="B55" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="C55" s="80" t="s">
-        <v>243</v>
-      </c>
-      <c r="D55" s="116" t="s">
-        <v>244</v>
-      </c>
-      <c r="E55" s="116"/>
-      <c r="F55" s="134" t="s">
-        <v>24</v>
-      </c>
-      <c r="G55" s="134" t="s">
+      <c r="B55" s="80" t="s">
+        <v>245</v>
+      </c>
+      <c r="C55" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="E55" s="17"/>
+      <c r="F55" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="G55" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="H55" s="73" t="s">
-        <v>41</v>
+      <c r="H55" s="17" t="s">
+        <v>55</v>
       </c>
       <c r="I55" s="73" t="s">
         <v>27</v>
       </c>
       <c r="J55" s="66" t="s">
-        <v>244</v>
-      </c>
-      <c r="K55" s="19"/>
-      <c r="L55" s="19"/>
-      <c r="M55" s="34"/>
+        <v>253</v>
+      </c>
+      <c r="K55" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="L55" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="M55" s="136" t="s">
+        <v>255</v>
+      </c>
       <c r="N55" s="66"/>
       <c r="O55" s="19"/>
       <c r="P55" s="19"/>
@@ -5326,54 +5359,50 @@
       <c r="R55" s="19"/>
       <c r="S55" s="19"/>
     </row>
-    <row r="56" spans="1:19" ht="45">
-      <c r="A56" s="80" t="s">
+    <row r="56" spans="1:19" ht="124.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="93" t="s">
         <v>241</v>
       </c>
-      <c r="B56" s="80" t="s">
+      <c r="B56" s="93" t="s">
         <v>245</v>
       </c>
-      <c r="C56" s="80" t="s">
-        <v>246</v>
-      </c>
-      <c r="D56" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="E56" s="17">
-        <v>553</v>
-      </c>
+      <c r="C56" s="137" t="s">
+        <v>251</v>
+      </c>
+      <c r="D56" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="E56" s="17"/>
       <c r="F56" s="134" t="s">
-        <v>24</v>
-      </c>
-      <c r="G56" s="82" t="s">
+        <v>300</v>
+      </c>
+      <c r="G56" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="H56" s="73" t="s">
+      <c r="H56" s="27" t="s">
         <v>41</v>
       </c>
       <c r="I56" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="J56" s="66" t="s">
-        <v>248</v>
-      </c>
-      <c r="K56" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="L56" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="M56" s="34"/>
-      <c r="N56" s="66"/>
-      <c r="O56" s="21">
-        <v>0.85</v>
-      </c>
-      <c r="P56" s="19"/>
-      <c r="Q56" s="19"/>
-      <c r="R56" s="19"/>
-      <c r="S56" s="19"/>
-    </row>
-    <row r="57" spans="1:19" ht="105">
+      <c r="J56" s="63"/>
+      <c r="K56" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="L56" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="M56" s="136" t="s">
+        <v>255</v>
+      </c>
+      <c r="N56" s="63"/>
+      <c r="O56" s="29"/>
+      <c r="P56" s="29"/>
+      <c r="Q56" s="29"/>
+      <c r="R56" s="29"/>
+      <c r="S56" s="29"/>
+    </row>
+    <row r="57" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A57" s="80" t="s">
         <v>241</v>
       </c>
@@ -5384,14 +5413,14 @@
         <v>251</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E57" s="17"/>
-      <c r="F57" s="134" t="s">
-        <v>24</v>
-      </c>
-      <c r="G57" s="82" t="s">
-        <v>63</v>
+      <c r="F57" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G57" s="17" t="s">
+        <v>88</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>55</v>
@@ -5400,7 +5429,7 @@
         <v>27</v>
       </c>
       <c r="J57" s="66" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="K57" s="19" t="s">
         <v>254</v>
@@ -5408,57 +5437,53 @@
       <c r="L57" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="M57" s="136" t="s">
-        <v>255</v>
-      </c>
-      <c r="N57" s="65">
-        <v>0.86099999999999999</v>
+      <c r="M57" s="136"/>
+      <c r="N57" s="145">
+        <v>0.74199999999999999</v>
       </c>
       <c r="O57" s="145">
-        <v>0.86599999999999999</v>
+        <v>0.748</v>
       </c>
       <c r="P57" s="19"/>
       <c r="Q57" s="19"/>
       <c r="R57" s="19"/>
       <c r="S57" s="19"/>
     </row>
-    <row r="58" spans="1:19" ht="105">
+    <row r="58" spans="1:19" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A58" s="80" t="s">
         <v>241</v>
       </c>
-      <c r="B58" s="80" t="s">
-        <v>245</v>
-      </c>
-      <c r="C58" s="135" t="s">
-        <v>251</v>
+      <c r="B58" s="98" t="s">
+        <v>260</v>
+      </c>
+      <c r="C58" s="126" t="s">
+        <v>261</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="E58" s="17"/>
-      <c r="F58" s="73" t="s">
+      <c r="F58" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="G58" s="82" t="s">
+      <c r="G58" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="H58" s="17" t="s">
-        <v>55</v>
+      <c r="H58" s="73" t="s">
+        <v>41</v>
       </c>
       <c r="I58" s="73" t="s">
         <v>27</v>
       </c>
       <c r="J58" s="66" t="s">
-        <v>253</v>
-      </c>
-      <c r="K58" s="19" t="s">
-        <v>254</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="K58" s="19"/>
       <c r="L58" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="M58" s="136" t="s">
-        <v>255</v>
+        <v>264</v>
+      </c>
+      <c r="M58" s="127" t="s">
+        <v>265</v>
       </c>
       <c r="N58" s="66"/>
       <c r="O58" s="19"/>
@@ -5467,366 +5492,233 @@
       <c r="R58" s="19"/>
       <c r="S58" s="19"/>
     </row>
-    <row r="59" spans="1:19" ht="124.95" customHeight="1">
+    <row r="59" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A59" s="93" t="s">
-        <v>241</v>
-      </c>
-      <c r="B59" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="C59" s="137" t="s">
-        <v>251</v>
+        <v>266</v>
+      </c>
+      <c r="B59" s="117" t="s">
+        <v>267</v>
+      </c>
+      <c r="C59" s="93" t="s">
+        <v>268</v>
       </c>
       <c r="D59" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="E59" s="17"/>
+        <v>269</v>
+      </c>
+      <c r="E59" s="17">
+        <v>546</v>
+      </c>
       <c r="F59" s="134" t="s">
-        <v>305</v>
+        <v>24</v>
       </c>
       <c r="G59" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H59" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I59" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J59" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="K59" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="L59" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="M59" s="94"/>
+      <c r="N59" s="138" t="s">
+        <v>272</v>
+      </c>
+      <c r="O59" s="122">
+        <v>1</v>
+      </c>
+      <c r="P59" s="122">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="122">
+        <v>1</v>
+      </c>
+      <c r="R59" s="122">
+        <v>1</v>
+      </c>
+      <c r="S59" s="122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="93" t="s">
+        <v>266</v>
+      </c>
+      <c r="B60" s="117" t="s">
+        <v>273</v>
+      </c>
+      <c r="C60" s="93" t="s">
+        <v>274</v>
+      </c>
+      <c r="D60" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="E60" s="17">
+        <v>542</v>
+      </c>
+      <c r="F60" s="134" t="s">
+        <v>24</v>
+      </c>
+      <c r="G60" s="27"/>
+      <c r="H60" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="H59" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="I59" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="J59" s="63"/>
-      <c r="K59" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="L59" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="M59" s="136" t="s">
-        <v>255</v>
-      </c>
-      <c r="N59" s="63"/>
-      <c r="O59" s="29"/>
-      <c r="P59" s="29"/>
-      <c r="Q59" s="29"/>
-      <c r="R59" s="29"/>
-      <c r="S59" s="29"/>
-    </row>
-    <row r="60" spans="1:19" ht="105">
-      <c r="A60" s="80" t="s">
-        <v>241</v>
-      </c>
-      <c r="B60" s="80" t="s">
-        <v>245</v>
-      </c>
-      <c r="C60" s="135" t="s">
-        <v>251</v>
-      </c>
-      <c r="D60" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="E60" s="17"/>
-      <c r="F60" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="G60" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H60" s="17" t="s">
+      <c r="I60" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J60" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="K60" s="29"/>
+      <c r="L60" s="29"/>
+      <c r="M60" s="118" t="s">
+        <v>50</v>
+      </c>
+      <c r="N60" s="63"/>
+      <c r="O60" s="29"/>
+      <c r="P60" s="29"/>
+      <c r="Q60" s="29"/>
+      <c r="R60" s="29"/>
+      <c r="S60" s="29"/>
+    </row>
+    <row r="61" spans="1:19" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A61" s="93" t="s">
+        <v>266</v>
+      </c>
+      <c r="B61" s="117" t="s">
+        <v>273</v>
+      </c>
+      <c r="C61" s="93" t="s">
+        <v>277</v>
+      </c>
+      <c r="D61" s="150" t="s">
+        <v>319</v>
+      </c>
+      <c r="E61" s="17">
+        <v>541</v>
+      </c>
+      <c r="F61" s="134" t="s">
+        <v>24</v>
+      </c>
+      <c r="G61" s="62" t="s">
+        <v>302</v>
+      </c>
+      <c r="H61" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="I60" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="J60" s="66" t="s">
-        <v>259</v>
-      </c>
-      <c r="K60" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="L60" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="M60" s="136"/>
-      <c r="N60" s="145">
-        <v>0.74199999999999999</v>
-      </c>
-      <c r="O60" s="145">
-        <v>0.748</v>
-      </c>
-      <c r="P60" s="19"/>
-      <c r="Q60" s="19"/>
-      <c r="R60" s="19"/>
-      <c r="S60" s="19"/>
-    </row>
-    <row r="61" spans="1:19" ht="75">
-      <c r="A61" s="80" t="s">
-        <v>241</v>
-      </c>
-      <c r="B61" s="98" t="s">
-        <v>260</v>
-      </c>
-      <c r="C61" s="126" t="s">
-        <v>261</v>
-      </c>
-      <c r="D61" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="E61" s="17"/>
-      <c r="F61" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="G61" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="H61" s="73" t="s">
-        <v>41</v>
-      </c>
-      <c r="I61" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="J61" s="66" t="s">
-        <v>263</v>
-      </c>
-      <c r="K61" s="19"/>
-      <c r="L61" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="M61" s="127" t="s">
-        <v>265</v>
-      </c>
-      <c r="N61" s="66"/>
-      <c r="O61" s="19"/>
-      <c r="P61" s="19"/>
-      <c r="Q61" s="19"/>
-      <c r="R61" s="19"/>
-      <c r="S61" s="19"/>
-    </row>
-    <row r="62" spans="1:19" ht="120.6">
-      <c r="A62" s="93" t="s">
+      <c r="I61" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J61" s="63" t="s">
+        <v>280</v>
+      </c>
+      <c r="K61" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="L61" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="M61" s="94"/>
+      <c r="N61" s="63"/>
+      <c r="O61" s="122">
+        <v>0.09</v>
+      </c>
+      <c r="P61" s="29"/>
+      <c r="Q61" s="29"/>
+      <c r="R61" s="29"/>
+      <c r="S61" s="29"/>
+    </row>
+    <row r="62" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="80" t="s">
         <v>266</v>
       </c>
-      <c r="B62" s="117" t="s">
-        <v>267</v>
-      </c>
-      <c r="C62" s="93" t="s">
-        <v>268</v>
-      </c>
-      <c r="D62" s="26" t="s">
-        <v>269</v>
+      <c r="B62" s="98" t="s">
+        <v>281</v>
+      </c>
+      <c r="C62" s="80" t="s">
+        <v>282</v>
+      </c>
+      <c r="D62" s="17" t="s">
+        <v>290</v>
       </c>
       <c r="E62" s="17">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F62" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="G62" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="H62" s="27" t="s">
+      <c r="G62" s="73"/>
+      <c r="H62" s="73" t="s">
         <v>55</v>
       </c>
       <c r="I62" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J62" s="28" t="s">
-        <v>270</v>
-      </c>
-      <c r="K62" s="29" t="s">
+      <c r="J62" s="66" t="s">
+        <v>303</v>
+      </c>
+      <c r="K62" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="L62" s="29" t="s">
+      <c r="L62" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="M62" s="94"/>
-      <c r="N62" s="138" t="s">
-        <v>272</v>
-      </c>
-      <c r="O62" s="122">
-        <v>1</v>
-      </c>
-      <c r="P62" s="122">
-        <v>1</v>
-      </c>
-      <c r="Q62" s="122">
-        <v>1</v>
-      </c>
-      <c r="R62" s="122">
-        <v>1</v>
-      </c>
-      <c r="S62" s="122">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" ht="70.95" customHeight="1">
-      <c r="A63" s="93" t="s">
-        <v>266</v>
-      </c>
-      <c r="B63" s="117" t="s">
-        <v>273</v>
-      </c>
-      <c r="C63" s="93" t="s">
-        <v>274</v>
-      </c>
-      <c r="D63" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="E63" s="17">
-        <v>542</v>
-      </c>
-      <c r="F63" s="134" t="s">
-        <v>24</v>
-      </c>
-      <c r="G63" s="27"/>
-      <c r="H63" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="I63" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="J63" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="K63" s="29"/>
-      <c r="L63" s="29"/>
-      <c r="M63" s="118" t="s">
+      <c r="M62" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="N63" s="63"/>
-      <c r="O63" s="29"/>
-      <c r="P63" s="29"/>
-      <c r="Q63" s="29"/>
-      <c r="R63" s="29"/>
-      <c r="S63" s="29"/>
-    </row>
-    <row r="64" spans="1:19" ht="150">
-      <c r="A64" s="93" t="s">
-        <v>266</v>
-      </c>
-      <c r="B64" s="117" t="s">
-        <v>273</v>
-      </c>
-      <c r="C64" s="93" t="s">
-        <v>277</v>
-      </c>
-      <c r="D64" s="27" t="s">
-        <v>278</v>
-      </c>
-      <c r="E64" s="17">
-        <v>541</v>
-      </c>
-      <c r="F64" s="134" t="s">
-        <v>24</v>
-      </c>
-      <c r="G64" s="62" t="s">
-        <v>311</v>
-      </c>
-      <c r="H64" s="73" t="s">
-        <v>55</v>
-      </c>
-      <c r="I64" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="J64" s="63" t="s">
-        <v>280</v>
-      </c>
-      <c r="K64" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="L64" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="M64" s="94"/>
-      <c r="N64" s="63"/>
-      <c r="O64" s="122">
-        <v>0.09</v>
-      </c>
-      <c r="P64" s="29"/>
-      <c r="Q64" s="29"/>
-      <c r="R64" s="29"/>
-      <c r="S64" s="29"/>
-    </row>
-    <row r="65" spans="1:19" ht="46.8">
-      <c r="A65" s="80" t="s">
-        <v>266</v>
-      </c>
-      <c r="B65" s="98" t="s">
-        <v>281</v>
-      </c>
-      <c r="C65" s="80" t="s">
-        <v>282</v>
-      </c>
-      <c r="D65" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="E65" s="17">
-        <v>547</v>
-      </c>
-      <c r="F65" s="134" t="s">
-        <v>24</v>
-      </c>
-      <c r="G65" s="73"/>
-      <c r="H65" s="73" t="s">
-        <v>55</v>
-      </c>
-      <c r="I65" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="J65" s="66" t="s">
-        <v>312</v>
-      </c>
-      <c r="K65" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="L65" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="M65" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="N65" s="64">
+      <c r="N62" s="64">
         <v>0.8</v>
       </c>
-      <c r="O65" s="64">
+      <c r="O62" s="64">
         <v>0.85</v>
       </c>
-      <c r="P65" s="64"/>
-      <c r="Q65" s="64"/>
-      <c r="R65" s="64"/>
-      <c r="S65" s="64"/>
-    </row>
-    <row r="66" spans="1:19" ht="46.8">
-      <c r="A66" s="56" t="s">
+      <c r="P62" s="64"/>
+      <c r="Q62" s="64"/>
+      <c r="R62" s="64"/>
+      <c r="S62" s="64"/>
+    </row>
+    <row r="63" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="B66" s="70" t="s">
+      <c r="B63" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="C66" s="70" t="s">
+      <c r="C63" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="D66" s="77" t="s">
-        <v>323</v>
-      </c>
-      <c r="E66" s="61"/>
-      <c r="F66" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="G66" s="72"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="19"/>
-      <c r="J66" s="19"/>
-      <c r="K66" s="19"/>
-      <c r="L66" s="21" t="s">
-        <v>322</v>
-      </c>
-      <c r="M66" s="19"/>
-      <c r="N66" s="21">
+      <c r="D63" s="77" t="s">
+        <v>314</v>
+      </c>
+      <c r="E63" s="61"/>
+      <c r="F63" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G63" s="72"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="19"/>
+      <c r="K63" s="19"/>
+      <c r="L63" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="M63" s="19"/>
+      <c r="N63" s="21">
         <v>0.97</v>
       </c>
-      <c r="O66" s="21">
+      <c r="O63" s="21">
         <v>0.97</v>
       </c>
-      <c r="P66" s="21">
+      <c r="P63" s="21">
         <v>0.97</v>
       </c>
     </row>
@@ -5847,7 +5739,7 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:S67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.5546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="30.88671875" style="2" customWidth="1"/>
@@ -5863,7 +5755,7 @@
     <col min="20" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="46.2" customHeight="1">
+    <row r="1" spans="1:19" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5886,7 +5778,7 @@
       <c r="R1" s="147"/>
       <c r="S1" s="147"/>
     </row>
-    <row r="2" spans="1:19" ht="36">
+    <row r="2" spans="1:19" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -5945,7 +5837,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="75" hidden="1">
+    <row r="3" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>20</v>
       </c>
@@ -6001,7 +5893,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="62.4" hidden="1">
+    <row r="4" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>20</v>
       </c>
@@ -6050,7 +5942,7 @@
       <c r="R4" s="21"/>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" spans="1:19" ht="46.8" hidden="1">
+    <row r="5" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>20</v>
       </c>
@@ -6093,7 +5985,7 @@
       <c r="R5" s="29"/>
       <c r="S5" s="31"/>
     </row>
-    <row r="6" spans="1:19" ht="69" hidden="1" customHeight="1">
+    <row r="6" spans="1:19" ht="69" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>20</v>
       </c>
@@ -6136,7 +6028,7 @@
       <c r="R6" s="29"/>
       <c r="S6" s="31"/>
     </row>
-    <row r="7" spans="1:19" ht="62.4" hidden="1">
+    <row r="7" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="32" t="s">
         <v>47</v>
       </c>
@@ -6186,7 +6078,7 @@
       <c r="R7" s="40"/>
       <c r="S7" s="44"/>
     </row>
-    <row r="8" spans="1:19" ht="93.6" hidden="1">
+    <row r="8" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
         <v>47</v>
       </c>
@@ -6223,7 +6115,7 @@
       <c r="R8" s="40"/>
       <c r="S8" s="44"/>
     </row>
-    <row r="9" spans="1:19" ht="75" hidden="1">
+    <row r="9" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="32" t="s">
         <v>47</v>
       </c>
@@ -6282,7 +6174,7 @@
         <v>1.0608333333333333</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="46.8" hidden="1">
+    <row r="10" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
         <v>47</v>
       </c>
@@ -6334,7 +6226,7 @@
       <c r="R10" s="40"/>
       <c r="S10" s="44"/>
     </row>
-    <row r="11" spans="1:19" ht="60" hidden="1">
+    <row r="11" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="32" t="s">
         <v>47</v>
       </c>
@@ -6381,7 +6273,7 @@
       <c r="R11" s="40"/>
       <c r="S11" s="44"/>
     </row>
-    <row r="12" spans="1:19" ht="46.8" hidden="1">
+    <row r="12" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="56" t="s">
         <v>71</v>
       </c>
@@ -6437,7 +6329,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="75" hidden="1">
+    <row r="13" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="56" t="s">
         <v>71</v>
       </c>
@@ -6482,7 +6374,7 @@
       <c r="R13" s="19"/>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" spans="1:19" ht="46.8" hidden="1">
+    <row r="14" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="56" t="s">
         <v>71</v>
       </c>
@@ -6527,7 +6419,7 @@
       <c r="R14" s="68"/>
       <c r="S14" s="69"/>
     </row>
-    <row r="15" spans="1:19" ht="46.8" hidden="1">
+    <row r="15" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="56" t="s">
         <v>71</v>
       </c>
@@ -6570,7 +6462,7 @@
       <c r="R15" s="19"/>
       <c r="S15" s="23"/>
     </row>
-    <row r="16" spans="1:19" ht="31.2" hidden="1">
+    <row r="16" spans="1:19" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="56" t="s">
         <v>71</v>
       </c>
@@ -6611,7 +6503,7 @@
       <c r="R16" s="19"/>
       <c r="S16" s="23"/>
     </row>
-    <row r="17" spans="1:19" ht="62.4" hidden="1">
+    <row r="17" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="56" t="s">
         <v>71</v>
       </c>
@@ -6648,7 +6540,7 @@
       <c r="R17" s="19"/>
       <c r="S17" s="23"/>
     </row>
-    <row r="18" spans="1:19" ht="150" hidden="1">
+    <row r="18" spans="1:19" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="56" t="s">
         <v>71</v>
       </c>
@@ -6689,7 +6581,7 @@
       <c r="R18" s="29"/>
       <c r="S18" s="31"/>
     </row>
-    <row r="19" spans="1:19" ht="120" hidden="1">
+    <row r="19" spans="1:19" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="79" t="s">
         <v>96</v>
       </c>
@@ -6732,7 +6624,7 @@
       <c r="R19" s="19"/>
       <c r="S19" s="23"/>
     </row>
-    <row r="20" spans="1:19" ht="105" hidden="1">
+    <row r="20" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="79" t="s">
         <v>96</v>
       </c>
@@ -6779,7 +6671,7 @@
       <c r="R20" s="21"/>
       <c r="S20" s="22"/>
     </row>
-    <row r="21" spans="1:19" ht="62.4" hidden="1">
+    <row r="21" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="79" t="s">
         <v>96</v>
       </c>
@@ -6824,7 +6716,7 @@
       <c r="R21" s="19"/>
       <c r="S21" s="23"/>
     </row>
-    <row r="22" spans="1:19" ht="60" hidden="1">
+    <row r="22" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="79" t="s">
         <v>96</v>
       </c>
@@ -6875,7 +6767,7 @@
       <c r="R22" s="86"/>
       <c r="S22" s="87"/>
     </row>
-    <row r="23" spans="1:19" ht="62.4">
+    <row r="23" spans="1:19" ht="78" x14ac:dyDescent="0.3">
       <c r="A23" s="79" t="s">
         <v>96</v>
       </c>
@@ -6922,7 +6814,7 @@
       <c r="R23" s="19"/>
       <c r="S23" s="23"/>
     </row>
-    <row r="24" spans="1:19" ht="46.8" hidden="1">
+    <row r="24" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="79" t="s">
         <v>96</v>
       </c>
@@ -6974,7 +6866,7 @@
       <c r="R24" s="19"/>
       <c r="S24" s="23"/>
     </row>
-    <row r="25" spans="1:19" ht="46.8" hidden="1">
+    <row r="25" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="79" t="s">
         <v>96</v>
       </c>
@@ -7033,7 +6925,7 @@
         <v>0.99356223175965663</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="93.6" hidden="1">
+    <row r="26" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="57" t="s">
         <v>130</v>
       </c>
@@ -7072,7 +6964,7 @@
       <c r="R26" s="29"/>
       <c r="S26" s="31"/>
     </row>
-    <row r="27" spans="1:19" ht="93.6" hidden="1">
+    <row r="27" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="79" t="s">
         <v>130</v>
       </c>
@@ -7117,7 +7009,7 @@
       <c r="R27" s="19"/>
       <c r="S27" s="23"/>
     </row>
-    <row r="28" spans="1:19" ht="62.4" hidden="1">
+    <row r="28" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="79" t="s">
         <v>130</v>
       </c>
@@ -7162,7 +7054,7 @@
       <c r="R28" s="19"/>
       <c r="S28" s="23"/>
     </row>
-    <row r="29" spans="1:19" ht="62.4" hidden="1">
+    <row r="29" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="79" t="s">
         <v>130</v>
       </c>
@@ -7217,7 +7109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="62.4" hidden="1">
+    <row r="30" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="79" t="s">
         <v>130</v>
       </c>
@@ -7274,7 +7166,7 @@
         <v>0.14285714285714285</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="75" hidden="1">
+    <row r="31" spans="1:19" ht="78" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33" t="s">
         <v>151</v>
       </c>
@@ -7335,7 +7227,7 @@
         <v>1.02125</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="46.8" hidden="1">
+    <row r="32" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33" t="s">
         <v>151</v>
       </c>
@@ -7382,7 +7274,7 @@
       <c r="R32" s="40"/>
       <c r="S32" s="44"/>
     </row>
-    <row r="33" spans="1:19" ht="105" hidden="1">
+    <row r="33" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33" t="s">
         <v>151</v>
       </c>
@@ -7431,7 +7323,7 @@
       <c r="R33" s="40"/>
       <c r="S33" s="44"/>
     </row>
-    <row r="34" spans="1:19" ht="120" hidden="1">
+    <row r="34" spans="1:19" ht="140.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33" t="s">
         <v>151</v>
       </c>
@@ -7478,7 +7370,7 @@
       <c r="R34" s="108"/>
       <c r="S34" s="109"/>
     </row>
-    <row r="35" spans="1:19" ht="46.8" hidden="1">
+    <row r="35" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33" t="s">
         <v>151</v>
       </c>
@@ -7527,7 +7419,7 @@
       <c r="R35" s="40"/>
       <c r="S35" s="44"/>
     </row>
-    <row r="36" spans="1:19" ht="124.8" hidden="1">
+    <row r="36" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="80" t="s">
         <v>165</v>
       </c>
@@ -7566,7 +7458,7 @@
       <c r="R36" s="19"/>
       <c r="S36" s="23"/>
     </row>
-    <row r="37" spans="1:19" ht="60" hidden="1">
+    <row r="37" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="80" t="s">
         <v>165</v>
       </c>
@@ -7605,7 +7497,7 @@
       <c r="R37" s="19"/>
       <c r="S37" s="23"/>
     </row>
-    <row r="38" spans="1:19" ht="93.6" hidden="1">
+    <row r="38" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="80" t="s">
         <v>165</v>
       </c>
@@ -7644,7 +7536,7 @@
       <c r="R38" s="19"/>
       <c r="S38" s="23"/>
     </row>
-    <row r="39" spans="1:19" ht="46.95" hidden="1" customHeight="1">
+    <row r="39" spans="1:19" ht="46.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="93" t="s">
         <v>177</v>
       </c>
@@ -7703,7 +7595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="62.4" hidden="1">
+    <row r="40" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="93" t="s">
         <v>177</v>
       </c>
@@ -7762,7 +7654,7 @@
         <v>1.099</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="105" hidden="1">
+    <row r="41" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="93" t="s">
         <v>177</v>
       </c>
@@ -7821,7 +7713,7 @@
         <v>0.82269999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="75" hidden="1">
+    <row r="42" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="93" t="s">
         <v>177</v>
       </c>
@@ -7880,7 +7772,7 @@
         <v>1.3244</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="75" hidden="1">
+    <row r="43" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="93" t="s">
         <v>177</v>
       </c>
@@ -7939,7 +7831,7 @@
         <v>1.1175999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="90" hidden="1">
+    <row r="44" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="93" t="s">
         <v>177</v>
       </c>
@@ -7998,7 +7890,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="88.8" hidden="1" customHeight="1">
+    <row r="45" spans="1:19" ht="88.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="93" t="s">
         <v>194</v>
       </c>
@@ -8041,7 +7933,7 @@
       <c r="R45" s="29"/>
       <c r="S45" s="31"/>
     </row>
-    <row r="46" spans="1:19" ht="130.80000000000001" hidden="1" customHeight="1">
+    <row r="46" spans="1:19" ht="130.80000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="80" t="s">
         <v>194</v>
       </c>
@@ -8088,7 +7980,7 @@
       <c r="R46" s="19"/>
       <c r="S46" s="23"/>
     </row>
-    <row r="47" spans="1:19" ht="132.6" hidden="1" customHeight="1">
+    <row r="47" spans="1:19" ht="132.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="93" t="s">
         <v>194</v>
       </c>
@@ -8147,7 +8039,7 @@
         <v>1.1764705882352942</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="132.6" hidden="1" customHeight="1">
+    <row r="48" spans="1:19" ht="132.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="93" t="s">
         <v>194</v>
       </c>
@@ -8204,7 +8096,7 @@
         <v>1.151764705882353</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="93.6" hidden="1">
+    <row r="49" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="80" t="s">
         <v>194</v>
       </c>
@@ -8247,7 +8139,7 @@
       <c r="R49" s="19"/>
       <c r="S49" s="23"/>
     </row>
-    <row r="50" spans="1:19" ht="90" hidden="1">
+    <row r="50" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="80" t="s">
         <v>212</v>
       </c>
@@ -8296,7 +8188,7 @@
       <c r="R50" s="21"/>
       <c r="S50" s="22"/>
     </row>
-    <row r="51" spans="1:19" ht="78" hidden="1" customHeight="1">
+    <row r="51" spans="1:19" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="93" t="s">
         <v>212</v>
       </c>
@@ -8343,7 +8235,7 @@
       <c r="R51" s="29"/>
       <c r="S51" s="31"/>
     </row>
-    <row r="52" spans="1:19" ht="90" hidden="1">
+    <row r="52" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="80" t="s">
         <v>212</v>
       </c>
@@ -8388,7 +8280,7 @@
       <c r="R52" s="131"/>
       <c r="S52" s="23"/>
     </row>
-    <row r="53" spans="1:19" ht="60" hidden="1">
+    <row r="53" spans="1:19" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="80" t="s">
         <v>212</v>
       </c>
@@ -8435,7 +8327,7 @@
       <c r="R53" s="64"/>
       <c r="S53" s="132"/>
     </row>
-    <row r="54" spans="1:19" ht="75" hidden="1">
+    <row r="54" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="80" t="s">
         <v>212</v>
       </c>
@@ -8480,7 +8372,7 @@
       <c r="R54" s="64"/>
       <c r="S54" s="132"/>
     </row>
-    <row r="55" spans="1:19" ht="105" hidden="1">
+    <row r="55" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="80" t="s">
         <v>212</v>
       </c>
@@ -8534,7 +8426,7 @@
       <c r="R55" s="19"/>
       <c r="S55" s="23"/>
     </row>
-    <row r="56" spans="1:19" ht="105" hidden="1">
+    <row r="56" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="80" t="s">
         <v>212</v>
       </c>
@@ -8575,7 +8467,7 @@
       <c r="R56" s="19"/>
       <c r="S56" s="23"/>
     </row>
-    <row r="57" spans="1:19" ht="75" hidden="1">
+    <row r="57" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="80" t="s">
         <v>241</v>
       </c>
@@ -8614,7 +8506,7 @@
       <c r="R57" s="19"/>
       <c r="S57" s="23"/>
     </row>
-    <row r="58" spans="1:19" ht="45" hidden="1">
+    <row r="58" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="80" t="s">
         <v>241</v>
       </c>
@@ -8661,7 +8553,7 @@
       <c r="R58" s="19"/>
       <c r="S58" s="23"/>
     </row>
-    <row r="59" spans="1:19" ht="109.2">
+    <row r="59" spans="1:19" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A59" s="80" t="s">
         <v>241</v>
       </c>
@@ -8718,7 +8610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="109.2" hidden="1">
+    <row r="60" spans="1:19" ht="124.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="80" t="s">
         <v>241</v>
       </c>
@@ -8763,7 +8655,7 @@
       <c r="R60" s="19"/>
       <c r="S60" s="23"/>
     </row>
-    <row r="61" spans="1:19" ht="124.95" hidden="1" customHeight="1">
+    <row r="61" spans="1:19" ht="124.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="93" t="s">
         <v>241</v>
       </c>
@@ -8806,7 +8698,7 @@
       <c r="R61" s="29"/>
       <c r="S61" s="31"/>
     </row>
-    <row r="62" spans="1:19" ht="109.2">
+    <row r="62" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A62" s="80" t="s">
         <v>241</v>
       </c>
@@ -8858,7 +8750,7 @@
       <c r="R62" s="19"/>
       <c r="S62" s="23"/>
     </row>
-    <row r="63" spans="1:19" ht="75" hidden="1">
+    <row r="63" spans="1:19" ht="93.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="80" t="s">
         <v>241</v>
       </c>
@@ -8901,7 +8793,7 @@
       <c r="R63" s="19"/>
       <c r="S63" s="23"/>
     </row>
-    <row r="64" spans="1:19" ht="109.2" hidden="1">
+    <row r="64" spans="1:19" ht="109.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="93" t="s">
         <v>266</v>
       </c>
@@ -8955,7 +8847,7 @@
       <c r="R64" s="29"/>
       <c r="S64" s="31"/>
     </row>
-    <row r="65" spans="1:19" ht="70.95" hidden="1" customHeight="1">
+    <row r="65" spans="1:19" ht="70.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="93" t="s">
         <v>266</v>
       </c>
@@ -8998,7 +8890,7 @@
       <c r="R65" s="29"/>
       <c r="S65" s="31"/>
     </row>
-    <row r="66" spans="1:19" ht="150" hidden="1">
+    <row r="66" spans="1:19" ht="171.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="93" t="s">
         <v>266</v>
       </c>
@@ -9052,7 +8944,7 @@
       <c r="R66" s="29"/>
       <c r="S66" s="31"/>
     </row>
-    <row r="67" spans="1:19" ht="46.8" hidden="1">
+    <row r="67" spans="1:19" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="80" t="s">
         <v>266</v>
       </c>

--- a/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Plan de mejoramiento/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/SGIND/data/raw/Plan de mejoramiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_96787627FCCA1FF109BBA3DFBB87DF7B067D890E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{601E2C10-A0B0-48CC-8748-FF23AB170B8A}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_96787627FCCA1FF109BBA3DFBB87DF7B067D890E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B228315-F04E-49E5-82F1-D90F6E929169}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Indicadores Real" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Indicadores Plan de Mejor'!$A$2:$S$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Indicadores Plan de Mejor'!$A$2:$S$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Indicadores Real'!$A$2:$S$67</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -1064,7 +1064,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2239,7 +2239,7 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:S63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="39.5546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="30.88671875" style="2" customWidth="1"/>
@@ -2256,7 +2256,7 @@
     <col min="21" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="46.2" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2279,7 +2279,7 @@
       <c r="R1" s="148"/>
       <c r="S1" s="148"/>
     </row>
-    <row r="2" spans="1:19" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="31.2" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="78" customHeight="1">
       <c r="A3" s="14" t="s">
         <v>14</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="62.4" customHeight="1">
       <c r="A4" s="14" t="s">
         <v>14</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="46.8" customHeight="1">
       <c r="A5" s="14" t="s">
         <v>14</v>
       </c>
@@ -2489,7 +2489,7 @@
       <c r="R5" s="29"/>
       <c r="S5" s="29"/>
     </row>
-    <row r="6" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="69" customHeight="1">
       <c r="A6" s="14" t="s">
         <v>14</v>
       </c>
@@ -2532,7 +2532,7 @@
       <c r="R6" s="29"/>
       <c r="S6" s="29"/>
     </row>
-    <row r="7" spans="1:19" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="93.6" customHeight="1">
       <c r="A7" s="32" t="s">
         <v>41</v>
       </c>
@@ -2567,7 +2567,7 @@
       <c r="R7" s="40"/>
       <c r="S7" s="40"/>
     </row>
-    <row r="8" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="78" customHeight="1">
       <c r="A8" s="32" t="s">
         <v>41</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="46.8" customHeight="1">
       <c r="A9" s="32" t="s">
         <v>41</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="78" customHeight="1">
       <c r="A10" s="32" t="s">
         <v>41</v>
       </c>
@@ -2726,7 +2726,7 @@
       <c r="R10" s="40"/>
       <c r="S10" s="40"/>
     </row>
-    <row r="11" spans="1:19" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="62.4" customHeight="1">
       <c r="A11" s="56" t="s">
         <v>59</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="62.4" customHeight="1">
       <c r="A12" s="56" t="s">
         <v>59</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="31.2" customHeight="1">
       <c r="A13" s="56" t="s">
         <v>59</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="31.2" customHeight="1">
       <c r="A14" s="56" t="s">
         <v>59</v>
       </c>
@@ -2938,7 +2938,7 @@
       <c r="R14" s="19"/>
       <c r="S14" s="19"/>
     </row>
-    <row r="15" spans="1:19" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="31.2" customHeight="1">
       <c r="A15" s="56" t="s">
         <v>59</v>
       </c>
@@ -2991,7 +2991,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" ht="46.8" customHeight="1">
       <c r="A16" s="56" t="s">
         <v>59</v>
       </c>
@@ -3028,7 +3028,7 @@
       <c r="R16" s="19"/>
       <c r="S16" s="19"/>
     </row>
-    <row r="17" spans="1:19" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="187.2" customHeight="1">
       <c r="A17" s="56" t="s">
         <v>59</v>
       </c>
@@ -3069,7 +3069,7 @@
       <c r="R17" s="29"/>
       <c r="S17" s="29"/>
     </row>
-    <row r="18" spans="1:19" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="140.4" customHeight="1">
       <c r="A18" s="79" t="s">
         <v>83</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="78" customHeight="1">
       <c r="A19" s="79" t="s">
         <v>83</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="78" customHeight="1">
       <c r="A20" s="79" t="s">
         <v>83</v>
       </c>
@@ -3222,7 +3222,7 @@
       <c r="R20" s="19"/>
       <c r="S20" s="19"/>
     </row>
-    <row r="21" spans="1:19" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="62.4" customHeight="1">
       <c r="A21" s="79" t="s">
         <v>83</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="46.8" customHeight="1">
       <c r="A22" s="79" t="s">
         <v>83</v>
       </c>
@@ -3328,7 +3328,7 @@
       <c r="R22" s="19"/>
       <c r="S22" s="19"/>
     </row>
-    <row r="23" spans="1:19" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="62.4" customHeight="1">
       <c r="A23" s="79" t="s">
         <v>83</v>
       </c>
@@ -3377,7 +3377,7 @@
       <c r="R23" s="19"/>
       <c r="S23" s="19"/>
     </row>
-    <row r="24" spans="1:19" ht="218.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="218.4" customHeight="1">
       <c r="A24" s="79" t="s">
         <v>113</v>
       </c>
@@ -3416,7 +3416,7 @@
       <c r="R24" s="29"/>
       <c r="S24" s="29"/>
     </row>
-    <row r="25" spans="1:19" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="140.4" customHeight="1">
       <c r="A25" s="79" t="s">
         <v>113</v>
       </c>
@@ -3455,7 +3455,7 @@
       <c r="R25" s="29"/>
       <c r="S25" s="29"/>
     </row>
-    <row r="26" spans="1:19" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="93.6" customHeight="1">
       <c r="A26" s="79" t="s">
         <v>113</v>
       </c>
@@ -3500,7 +3500,7 @@
       <c r="R26" s="19"/>
       <c r="S26" s="19"/>
     </row>
-    <row r="27" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="78" customHeight="1">
       <c r="A27" s="79" t="s">
         <v>113</v>
       </c>
@@ -3514,8 +3514,8 @@
         <v>129</v>
       </c>
       <c r="E27" s="17"/>
-      <c r="F27" s="62" t="s">
-        <v>34</v>
+      <c r="F27" s="17" t="s">
+        <v>18</v>
       </c>
       <c r="G27" s="73" t="s">
         <v>48</v>
@@ -3553,7 +3553,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="62.4" customHeight="1">
       <c r="A28" s="79" t="s">
         <v>113</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="62.4" customHeight="1">
       <c r="A29" s="79" t="s">
         <v>113</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="78" customHeight="1">
       <c r="A30" s="33" t="s">
         <v>136</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="62.4" customHeight="1">
       <c r="A31" s="33" t="s">
         <v>136</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="124.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="124.8" customHeight="1">
       <c r="A32" s="33" t="s">
         <v>136</v>
       </c>
@@ -3830,7 +3830,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="140.4" customHeight="1">
       <c r="A33" s="33" t="s">
         <v>136</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="62.4" customHeight="1">
       <c r="A34" s="33" t="s">
         <v>136</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="296.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="296.39999999999998" customHeight="1">
       <c r="A35" s="80" t="s">
         <v>151</v>
       </c>
@@ -3977,7 +3977,7 @@
       <c r="R35" s="19"/>
       <c r="S35" s="19"/>
     </row>
-    <row r="36" spans="1:19" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="93.6" customHeight="1">
       <c r="A36" s="80" t="s">
         <v>151</v>
       </c>
@@ -4016,7 +4016,7 @@
       <c r="R36" s="19"/>
       <c r="S36" s="19"/>
     </row>
-    <row r="37" spans="1:19" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="46.95" customHeight="1">
       <c r="A37" s="93" t="s">
         <v>160</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="62.4" customHeight="1">
       <c r="A38" s="93" t="s">
         <v>160</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="109.2" customHeight="1">
       <c r="A39" s="93" t="s">
         <v>160</v>
       </c>
@@ -4189,7 +4189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="93.6" customHeight="1">
       <c r="A40" s="93" t="s">
         <v>160</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="93.6" customHeight="1">
       <c r="A41" s="93" t="s">
         <v>160</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="93.6" customHeight="1">
       <c r="A42" s="93" t="s">
         <v>160</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" ht="88.8" customHeight="1">
       <c r="A43" s="93" t="s">
         <v>178</v>
       </c>
@@ -4401,7 +4401,7 @@
       <c r="R43" s="29"/>
       <c r="S43" s="29"/>
     </row>
-    <row r="44" spans="1:19" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="130.80000000000001" customHeight="1">
       <c r="A44" s="80" t="s">
         <v>178</v>
       </c>
@@ -4446,7 +4446,7 @@
       <c r="R44" s="19"/>
       <c r="S44" s="19"/>
     </row>
-    <row r="45" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="132.6" customHeight="1">
       <c r="A45" s="93" t="s">
         <v>178</v>
       </c>
@@ -4495,7 +4495,7 @@
       <c r="R45" s="29"/>
       <c r="S45" s="29"/>
     </row>
-    <row r="46" spans="1:19" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="132.6" customHeight="1">
       <c r="A46" s="93" t="s">
         <v>178</v>
       </c>
@@ -4542,7 +4542,7 @@
       <c r="R46" s="29"/>
       <c r="S46" s="29"/>
     </row>
-    <row r="47" spans="1:19" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="93.6" customHeight="1">
       <c r="A47" s="80" t="s">
         <v>178</v>
       </c>
@@ -4583,7 +4583,7 @@
       <c r="R47" s="19"/>
       <c r="S47" s="19"/>
     </row>
-    <row r="48" spans="1:19" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="109.2" customHeight="1">
       <c r="A48" s="80" t="s">
         <v>196</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" ht="78" customHeight="1">
       <c r="A49" s="93" t="s">
         <v>196</v>
       </c>
@@ -4695,7 +4695,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="109.2" customHeight="1">
       <c r="A50" s="80" t="s">
         <v>196</v>
       </c>
@@ -4752,7 +4752,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="124.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" ht="124.8" customHeight="1">
       <c r="A51" s="80" t="s">
         <v>196</v>
       </c>
@@ -4793,7 +4793,7 @@
       <c r="R51" s="19"/>
       <c r="S51" s="19"/>
     </row>
-    <row r="52" spans="1:19" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="93.6" customHeight="1">
       <c r="A52" s="80" t="s">
         <v>214</v>
       </c>
@@ -4832,7 +4832,7 @@
       <c r="R52" s="19"/>
       <c r="S52" s="19"/>
     </row>
-    <row r="53" spans="1:19" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="46.8" customHeight="1">
       <c r="A53" s="80" t="s">
         <v>214</v>
       </c>
@@ -4879,7 +4879,7 @@
       <c r="R53" s="19"/>
       <c r="S53" s="19"/>
     </row>
-    <row r="54" spans="1:19" ht="124.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" ht="124.8" customHeight="1">
       <c r="A54" s="80" t="s">
         <v>214</v>
       </c>
@@ -4928,7 +4928,7 @@
       <c r="R54" s="19"/>
       <c r="S54" s="19"/>
     </row>
-    <row r="55" spans="1:19" ht="124.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="124.8" customHeight="1">
       <c r="A55" s="80" t="s">
         <v>214</v>
       </c>
@@ -4973,7 +4973,7 @@
       <c r="R55" s="19"/>
       <c r="S55" s="19"/>
     </row>
-    <row r="56" spans="1:19" ht="124.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" ht="124.95" customHeight="1">
       <c r="A56" s="93" t="s">
         <v>214</v>
       </c>
@@ -5016,7 +5016,7 @@
       <c r="R56" s="29"/>
       <c r="S56" s="29"/>
     </row>
-    <row r="57" spans="1:19" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" ht="109.2" customHeight="1">
       <c r="A57" s="80" t="s">
         <v>214</v>
       </c>
@@ -5063,7 +5063,7 @@
       <c r="R57" s="19"/>
       <c r="S57" s="19"/>
     </row>
-    <row r="58" spans="1:19" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" ht="93.6" customHeight="1">
       <c r="A58" s="80" t="s">
         <v>214</v>
       </c>
@@ -5106,7 +5106,7 @@
       <c r="R58" s="19"/>
       <c r="S58" s="19"/>
     </row>
-    <row r="59" spans="1:19" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" ht="140.4" customHeight="1">
       <c r="A59" s="93" t="s">
         <v>240</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" ht="70.95" customHeight="1">
       <c r="A60" s="93" t="s">
         <v>240</v>
       </c>
@@ -5204,7 +5204,7 @@
       <c r="R60" s="29"/>
       <c r="S60" s="29"/>
     </row>
-    <row r="61" spans="1:19" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" ht="187.2" customHeight="1">
       <c r="A61" s="93" t="s">
         <v>240</v>
       </c>
@@ -5251,7 +5251,7 @@
       <c r="R61" s="29"/>
       <c r="S61" s="29"/>
     </row>
-    <row r="62" spans="1:19" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" ht="46.8" customHeight="1">
       <c r="A62" s="80" t="s">
         <v>240</v>
       </c>
@@ -5300,7 +5300,7 @@
       <c r="R62" s="64"/>
       <c r="S62" s="64"/>
     </row>
-    <row r="63" spans="1:19" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" ht="46.8" customHeight="1">
       <c r="A63" s="56" t="s">
         <v>59</v>
       </c>
@@ -5337,7 +5337,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="N1:S1"/>
     <mergeCell ref="L11:L12"/>
@@ -5353,7 +5352,7 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:S67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="39.5546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="30.88671875" style="2" customWidth="1"/>
@@ -5370,7 +5369,7 @@
     <col min="21" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="46.2" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5393,7 +5392,7 @@
       <c r="R1" s="148"/>
       <c r="S1" s="148"/>
     </row>
-    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="36" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -5452,7 +5451,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="78" hidden="1" customHeight="1">
       <c r="A3" s="14" t="s">
         <v>14</v>
       </c>
@@ -5508,7 +5507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="62.4" hidden="1" customHeight="1">
       <c r="A4" s="14" t="s">
         <v>14</v>
       </c>
@@ -5557,7 +5556,7 @@
       <c r="R4" s="21"/>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" spans="1:19" ht="46.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="46.8" hidden="1" customHeight="1">
       <c r="A5" s="14" t="s">
         <v>14</v>
       </c>
@@ -5600,7 +5599,7 @@
       <c r="R5" s="29"/>
       <c r="S5" s="31"/>
     </row>
-    <row r="6" spans="1:19" ht="69" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="69" hidden="1" customHeight="1">
       <c r="A6" s="14" t="s">
         <v>14</v>
       </c>
@@ -5643,7 +5642,7 @@
       <c r="R6" s="29"/>
       <c r="S6" s="31"/>
     </row>
-    <row r="7" spans="1:19" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="62.4" hidden="1" customHeight="1">
       <c r="A7" s="32" t="s">
         <v>41</v>
       </c>
@@ -5693,7 +5692,7 @@
       <c r="R7" s="40"/>
       <c r="S7" s="44"/>
     </row>
-    <row r="8" spans="1:19" ht="93.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="93.6" hidden="1" customHeight="1">
       <c r="A8" s="32" t="s">
         <v>41</v>
       </c>
@@ -5730,7 +5729,7 @@
       <c r="R8" s="40"/>
       <c r="S8" s="44"/>
     </row>
-    <row r="9" spans="1:19" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="78" hidden="1" customHeight="1">
       <c r="A9" s="32" t="s">
         <v>41</v>
       </c>
@@ -5789,7 +5788,7 @@
         <v>1.0608333333333333</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="46.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="46.8" hidden="1" customHeight="1">
       <c r="A10" s="32" t="s">
         <v>41</v>
       </c>
@@ -5841,7 +5840,7 @@
       <c r="R10" s="40"/>
       <c r="S10" s="44"/>
     </row>
-    <row r="11" spans="1:19" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="78" hidden="1" customHeight="1">
       <c r="A11" s="32" t="s">
         <v>41</v>
       </c>
@@ -5888,7 +5887,7 @@
       <c r="R11" s="40"/>
       <c r="S11" s="44"/>
     </row>
-    <row r="12" spans="1:19" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="62.4" hidden="1" customHeight="1">
       <c r="A12" s="56" t="s">
         <v>59</v>
       </c>
@@ -5944,7 +5943,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="93.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="93.6" hidden="1" customHeight="1">
       <c r="A13" s="56" t="s">
         <v>59</v>
       </c>
@@ -5989,7 +5988,7 @@
       <c r="R13" s="19"/>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" spans="1:19" ht="46.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="46.8" hidden="1" customHeight="1">
       <c r="A14" s="56" t="s">
         <v>59</v>
       </c>
@@ -6034,7 +6033,7 @@
       <c r="R14" s="68"/>
       <c r="S14" s="69"/>
     </row>
-    <row r="15" spans="1:19" ht="46.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="46.8" hidden="1" customHeight="1">
       <c r="A15" s="56" t="s">
         <v>59</v>
       </c>
@@ -6077,7 +6076,7 @@
       <c r="R15" s="19"/>
       <c r="S15" s="23"/>
     </row>
-    <row r="16" spans="1:19" ht="31.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" ht="31.2" hidden="1" customHeight="1">
       <c r="A16" s="56" t="s">
         <v>59</v>
       </c>
@@ -6118,7 +6117,7 @@
       <c r="R16" s="19"/>
       <c r="S16" s="23"/>
     </row>
-    <row r="17" spans="1:19" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="62.4" hidden="1" customHeight="1">
       <c r="A17" s="56" t="s">
         <v>59</v>
       </c>
@@ -6155,7 +6154,7 @@
       <c r="R17" s="19"/>
       <c r="S17" s="23"/>
     </row>
-    <row r="18" spans="1:19" ht="187.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="187.2" hidden="1" customHeight="1">
       <c r="A18" s="56" t="s">
         <v>59</v>
       </c>
@@ -6196,7 +6195,7 @@
       <c r="R18" s="29"/>
       <c r="S18" s="31"/>
     </row>
-    <row r="19" spans="1:19" ht="140.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="140.4" hidden="1" customHeight="1">
       <c r="A19" s="79" t="s">
         <v>83</v>
       </c>
@@ -6239,7 +6238,7 @@
       <c r="R19" s="19"/>
       <c r="S19" s="23"/>
     </row>
-    <row r="20" spans="1:19" ht="109.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="109.2" hidden="1" customHeight="1">
       <c r="A20" s="79" t="s">
         <v>83</v>
       </c>
@@ -6286,7 +6285,7 @@
       <c r="R20" s="21"/>
       <c r="S20" s="22"/>
     </row>
-    <row r="21" spans="1:19" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="78" hidden="1" customHeight="1">
       <c r="A21" s="79" t="s">
         <v>83</v>
       </c>
@@ -6331,7 +6330,7 @@
       <c r="R21" s="19"/>
       <c r="S21" s="23"/>
     </row>
-    <row r="22" spans="1:19" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="62.4" hidden="1" customHeight="1">
       <c r="A22" s="79" t="s">
         <v>83</v>
       </c>
@@ -6382,7 +6381,7 @@
       <c r="R22" s="86"/>
       <c r="S22" s="87"/>
     </row>
-    <row r="23" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="78" customHeight="1">
       <c r="A23" s="79" t="s">
         <v>83</v>
       </c>
@@ -6429,7 +6428,7 @@
       <c r="R23" s="19"/>
       <c r="S23" s="23"/>
     </row>
-    <row r="24" spans="1:19" ht="46.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="46.8" hidden="1" customHeight="1">
       <c r="A24" s="79" t="s">
         <v>83</v>
       </c>
@@ -6481,7 +6480,7 @@
       <c r="R24" s="19"/>
       <c r="S24" s="23"/>
     </row>
-    <row r="25" spans="1:19" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="62.4" hidden="1" customHeight="1">
       <c r="A25" s="79" t="s">
         <v>83</v>
       </c>
@@ -6540,7 +6539,7 @@
         <v>0.99356223175965663</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="109.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="109.2" hidden="1" customHeight="1">
       <c r="A26" s="57" t="s">
         <v>113</v>
       </c>
@@ -6579,7 +6578,7 @@
       <c r="R26" s="29"/>
       <c r="S26" s="31"/>
     </row>
-    <row r="27" spans="1:19" ht="93.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="93.6" hidden="1" customHeight="1">
       <c r="A27" s="79" t="s">
         <v>113</v>
       </c>
@@ -6624,7 +6623,7 @@
       <c r="R27" s="19"/>
       <c r="S27" s="23"/>
     </row>
-    <row r="28" spans="1:19" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="78" hidden="1" customHeight="1">
       <c r="A28" s="79" t="s">
         <v>113</v>
       </c>
@@ -6669,7 +6668,7 @@
       <c r="R28" s="19"/>
       <c r="S28" s="23"/>
     </row>
-    <row r="29" spans="1:19" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="62.4" hidden="1" customHeight="1">
       <c r="A29" s="79" t="s">
         <v>113</v>
       </c>
@@ -6724,7 +6723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="62.4" hidden="1" customHeight="1">
       <c r="A30" s="79" t="s">
         <v>113</v>
       </c>
@@ -6781,7 +6780,7 @@
         <v>0.14285714285714285</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="78" hidden="1" customHeight="1">
       <c r="A31" s="33" t="s">
         <v>136</v>
       </c>
@@ -6842,7 +6841,7 @@
         <v>1.02125</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="62.4" hidden="1" customHeight="1">
       <c r="A32" s="33" t="s">
         <v>136</v>
       </c>
@@ -6889,7 +6888,7 @@
       <c r="R32" s="40"/>
       <c r="S32" s="44"/>
     </row>
-    <row r="33" spans="1:19" ht="124.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="124.8" hidden="1" customHeight="1">
       <c r="A33" s="33" t="s">
         <v>136</v>
       </c>
@@ -6938,7 +6937,7 @@
       <c r="R33" s="40"/>
       <c r="S33" s="44"/>
     </row>
-    <row r="34" spans="1:19" ht="140.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="140.4" hidden="1" customHeight="1">
       <c r="A34" s="33" t="s">
         <v>136</v>
       </c>
@@ -6985,7 +6984,7 @@
       <c r="R34" s="108"/>
       <c r="S34" s="109"/>
     </row>
-    <row r="35" spans="1:19" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="62.4" hidden="1" customHeight="1">
       <c r="A35" s="33" t="s">
         <v>136</v>
       </c>
@@ -7034,7 +7033,7 @@
       <c r="R35" s="40"/>
       <c r="S35" s="44"/>
     </row>
-    <row r="36" spans="1:19" ht="124.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="124.8" hidden="1" customHeight="1">
       <c r="A36" s="80" t="s">
         <v>151</v>
       </c>
@@ -7073,7 +7072,7 @@
       <c r="R36" s="19"/>
       <c r="S36" s="23"/>
     </row>
-    <row r="37" spans="1:19" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="62.4" hidden="1" customHeight="1">
       <c r="A37" s="80" t="s">
         <v>151</v>
       </c>
@@ -7112,7 +7111,7 @@
       <c r="R37" s="19"/>
       <c r="S37" s="23"/>
     </row>
-    <row r="38" spans="1:19" ht="93.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="93.6" hidden="1" customHeight="1">
       <c r="A38" s="80" t="s">
         <v>151</v>
       </c>
@@ -7151,7 +7150,7 @@
       <c r="R38" s="19"/>
       <c r="S38" s="23"/>
     </row>
-    <row r="39" spans="1:19" ht="46.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="46.95" hidden="1" customHeight="1">
       <c r="A39" s="93" t="s">
         <v>160</v>
       </c>
@@ -7210,7 +7209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="62.4" hidden="1" customHeight="1">
       <c r="A40" s="93" t="s">
         <v>160</v>
       </c>
@@ -7269,7 +7268,7 @@
         <v>1.099</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="124.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="124.8" hidden="1" customHeight="1">
       <c r="A41" s="93" t="s">
         <v>160</v>
       </c>
@@ -7328,7 +7327,7 @@
         <v>0.82269999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="93.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="93.6" hidden="1" customHeight="1">
       <c r="A42" s="93" t="s">
         <v>160</v>
       </c>
@@ -7387,7 +7386,7 @@
         <v>1.3244</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="93.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" ht="93.6" hidden="1" customHeight="1">
       <c r="A43" s="93" t="s">
         <v>160</v>
       </c>
@@ -7446,7 +7445,7 @@
         <v>1.1175999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="93.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="93.6" hidden="1" customHeight="1">
       <c r="A44" s="93" t="s">
         <v>160</v>
       </c>
@@ -7505,7 +7504,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="88.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="88.8" hidden="1" customHeight="1">
       <c r="A45" s="93" t="s">
         <v>178</v>
       </c>
@@ -7548,7 +7547,7 @@
       <c r="R45" s="29"/>
       <c r="S45" s="31"/>
     </row>
-    <row r="46" spans="1:19" ht="130.80000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="130.80000000000001" hidden="1" customHeight="1">
       <c r="A46" s="80" t="s">
         <v>178</v>
       </c>
@@ -7595,7 +7594,7 @@
       <c r="R46" s="19"/>
       <c r="S46" s="23"/>
     </row>
-    <row r="47" spans="1:19" ht="132.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="132.6" hidden="1" customHeight="1">
       <c r="A47" s="93" t="s">
         <v>178</v>
       </c>
@@ -7654,7 +7653,7 @@
         <v>1.1764705882352942</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="132.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="132.6" hidden="1" customHeight="1">
       <c r="A48" s="93" t="s">
         <v>178</v>
       </c>
@@ -7711,7 +7710,7 @@
         <v>1.151764705882353</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="93.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" ht="93.6" hidden="1" customHeight="1">
       <c r="A49" s="80" t="s">
         <v>178</v>
       </c>
@@ -7754,7 +7753,7 @@
       <c r="R49" s="19"/>
       <c r="S49" s="23"/>
     </row>
-    <row r="50" spans="1:19" ht="109.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="109.2" hidden="1" customHeight="1">
       <c r="A50" s="80" t="s">
         <v>196</v>
       </c>
@@ -7803,7 +7802,7 @@
       <c r="R50" s="21"/>
       <c r="S50" s="22"/>
     </row>
-    <row r="51" spans="1:19" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" ht="78" hidden="1" customHeight="1">
       <c r="A51" s="93" t="s">
         <v>196</v>
       </c>
@@ -7850,7 +7849,7 @@
       <c r="R51" s="29"/>
       <c r="S51" s="31"/>
     </row>
-    <row r="52" spans="1:19" ht="93.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="93.6" hidden="1" customHeight="1">
       <c r="A52" s="80" t="s">
         <v>196</v>
       </c>
@@ -7895,7 +7894,7 @@
       <c r="R52" s="131"/>
       <c r="S52" s="23"/>
     </row>
-    <row r="53" spans="1:19" ht="62.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="62.4" hidden="1" customHeight="1">
       <c r="A53" s="80" t="s">
         <v>196</v>
       </c>
@@ -7942,7 +7941,7 @@
       <c r="R53" s="64"/>
       <c r="S53" s="132"/>
     </row>
-    <row r="54" spans="1:19" ht="93.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" ht="93.6" hidden="1" customHeight="1">
       <c r="A54" s="80" t="s">
         <v>196</v>
       </c>
@@ -7987,7 +7986,7 @@
       <c r="R54" s="64"/>
       <c r="S54" s="132"/>
     </row>
-    <row r="55" spans="1:19" ht="109.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="109.2" hidden="1" customHeight="1">
       <c r="A55" s="80" t="s">
         <v>196</v>
       </c>
@@ -8041,7 +8040,7 @@
       <c r="R55" s="19"/>
       <c r="S55" s="23"/>
     </row>
-    <row r="56" spans="1:19" ht="124.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" ht="124.8" hidden="1" customHeight="1">
       <c r="A56" s="80" t="s">
         <v>196</v>
       </c>
@@ -8082,7 +8081,7 @@
       <c r="R56" s="19"/>
       <c r="S56" s="23"/>
     </row>
-    <row r="57" spans="1:19" ht="93.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" ht="93.6" hidden="1" customHeight="1">
       <c r="A57" s="80" t="s">
         <v>214</v>
       </c>
@@ -8121,7 +8120,7 @@
       <c r="R57" s="19"/>
       <c r="S57" s="23"/>
     </row>
-    <row r="58" spans="1:19" ht="46.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" ht="46.8" hidden="1" customHeight="1">
       <c r="A58" s="80" t="s">
         <v>214</v>
       </c>
@@ -8168,7 +8167,7 @@
       <c r="R58" s="19"/>
       <c r="S58" s="23"/>
     </row>
-    <row r="59" spans="1:19" ht="124.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" ht="124.8" customHeight="1">
       <c r="A59" s="80" t="s">
         <v>214</v>
       </c>
@@ -8225,7 +8224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="124.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" ht="124.8" hidden="1" customHeight="1">
       <c r="A60" s="80" t="s">
         <v>214</v>
       </c>
@@ -8270,7 +8269,7 @@
       <c r="R60" s="19"/>
       <c r="S60" s="23"/>
     </row>
-    <row r="61" spans="1:19" ht="124.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" ht="124.95" hidden="1" customHeight="1">
       <c r="A61" s="93" t="s">
         <v>214</v>
       </c>
@@ -8313,7 +8312,7 @@
       <c r="R61" s="29"/>
       <c r="S61" s="31"/>
     </row>
-    <row r="62" spans="1:19" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" ht="109.2" customHeight="1">
       <c r="A62" s="80" t="s">
         <v>214</v>
       </c>
@@ -8365,7 +8364,7 @@
       <c r="R62" s="19"/>
       <c r="S62" s="23"/>
     </row>
-    <row r="63" spans="1:19" ht="93.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" ht="93.6" hidden="1" customHeight="1">
       <c r="A63" s="80" t="s">
         <v>214</v>
       </c>
@@ -8408,7 +8407,7 @@
       <c r="R63" s="19"/>
       <c r="S63" s="23"/>
     </row>
-    <row r="64" spans="1:19" ht="109.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" ht="109.2" hidden="1" customHeight="1">
       <c r="A64" s="93" t="s">
         <v>240</v>
       </c>
@@ -8462,7 +8461,7 @@
       <c r="R64" s="29"/>
       <c r="S64" s="31"/>
     </row>
-    <row r="65" spans="1:19" ht="70.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" ht="70.95" hidden="1" customHeight="1">
       <c r="A65" s="93" t="s">
         <v>240</v>
       </c>
@@ -8505,7 +8504,7 @@
       <c r="R65" s="29"/>
       <c r="S65" s="31"/>
     </row>
-    <row r="66" spans="1:19" ht="171.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" ht="171.6" hidden="1" customHeight="1">
       <c r="A66" s="93" t="s">
         <v>240</v>
       </c>
@@ -8559,7 +8558,7 @@
       <c r="R66" s="29"/>
       <c r="S66" s="31"/>
     </row>
-    <row r="67" spans="1:19" ht="46.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" ht="46.8" hidden="1" customHeight="1">
       <c r="A67" s="80" t="s">
         <v>240</v>
       </c>

--- a/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Indicadores Plan de Mejoramiento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/SGIND/data/raw/Plan de mejoramiento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_96787627FCCA1FF109BBA3DFBB87DF7B067D890E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B228315-F04E-49E5-82F1-D90F6E929169}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_96787627FCCA1FF109BBA3DFBB87DF7B067D890E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8D6031E-287D-4852-A40E-E1D83C3DEE8A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
